--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -8,44 +8,45 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B149A3B-6F6F-F44B-9CC5-49E207940F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66872460-D65B-E942-B8DA-CE30F390842E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20900" activeTab="4" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20900" firstSheet="2" activeTab="6" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="maps_OTHER" sheetId="26" r:id="rId1"/>
     <sheet name="maps_sites" sheetId="25" r:id="rId2"/>
     <sheet name="maps_samples" sheetId="24" r:id="rId3"/>
     <sheet name="wide_samples" sheetId="27" r:id="rId4"/>
-    <sheet name="wide_measures" sheetId="7" r:id="rId5"/>
-    <sheet name="enums_samples" sheetId="28" r:id="rId6"/>
-    <sheet name="wide_sampleRelationships" sheetId="29" r:id="rId7"/>
-    <sheet name="maps_repositories" sheetId="23" r:id="rId8"/>
-    <sheet name="wide_repositories" sheetId="6" r:id="rId9"/>
-    <sheet name="maps_qualityReports" sheetId="22" r:id="rId10"/>
-    <sheet name="maps_protocolSteps" sheetId="21" r:id="rId11"/>
-    <sheet name="wide_protocolSteps" sheetId="8" r:id="rId12"/>
-    <sheet name="maps_protocols" sheetId="20" r:id="rId13"/>
-    <sheet name="wide_protocols" sheetId="10" r:id="rId14"/>
-    <sheet name="maps_polygons" sheetId="19" r:id="rId15"/>
-    <sheet name="maps_measures" sheetId="17" r:id="rId16"/>
-    <sheet name="wide_measures2" sheetId="37" r:id="rId17"/>
-    <sheet name="enums_measures" sheetId="30" r:id="rId18"/>
-    <sheet name="enums_measures2" sheetId="36" r:id="rId19"/>
-    <sheet name="maps_instruments" sheetId="16" r:id="rId20"/>
-    <sheet name="maps_datasets" sheetId="15" r:id="rId21"/>
-    <sheet name="wide_datasets" sheetId="34" r:id="rId22"/>
-    <sheet name="wide_contacts" sheetId="11" r:id="rId23"/>
-    <sheet name="maps_addresses" sheetId="13" r:id="rId24"/>
-    <sheet name="enums_addresses" sheetId="33" r:id="rId25"/>
-    <sheet name="maps_accessions" sheetId="12" r:id="rId26"/>
-    <sheet name="PHA4GEVars" sheetId="35" r:id="rId27"/>
+    <sheet name="maps_measures" sheetId="17" r:id="rId5"/>
+    <sheet name="wide_measures" sheetId="7" r:id="rId6"/>
+    <sheet name="wide_measurestest" sheetId="38" r:id="rId7"/>
+    <sheet name="enums_samples" sheetId="28" r:id="rId8"/>
+    <sheet name="wide_sampleRelationships" sheetId="29" r:id="rId9"/>
+    <sheet name="maps_repositories" sheetId="23" r:id="rId10"/>
+    <sheet name="wide_repositories" sheetId="6" r:id="rId11"/>
+    <sheet name="maps_qualityReports" sheetId="22" r:id="rId12"/>
+    <sheet name="maps_protocolSteps" sheetId="21" r:id="rId13"/>
+    <sheet name="wide_protocolSteps" sheetId="8" r:id="rId14"/>
+    <sheet name="maps_protocols" sheetId="20" r:id="rId15"/>
+    <sheet name="wide_protocols" sheetId="10" r:id="rId16"/>
+    <sheet name="maps_polygons" sheetId="19" r:id="rId17"/>
+    <sheet name="wide_measures2" sheetId="37" r:id="rId18"/>
+    <sheet name="enums_measures" sheetId="30" r:id="rId19"/>
+    <sheet name="enums_measures2" sheetId="36" r:id="rId20"/>
+    <sheet name="maps_instruments" sheetId="16" r:id="rId21"/>
+    <sheet name="maps_datasets" sheetId="15" r:id="rId22"/>
+    <sheet name="wide_datasets" sheetId="34" r:id="rId23"/>
+    <sheet name="wide_contacts" sheetId="11" r:id="rId24"/>
+    <sheet name="maps_addresses" sheetId="13" r:id="rId25"/>
+    <sheet name="enums_addresses" sheetId="33" r:id="rId26"/>
+    <sheet name="maps_accessions" sheetId="12" r:id="rId27"/>
+    <sheet name="PHA4GEVars" sheetId="35" r:id="rId28"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId28"/>
+    <externalReference r:id="rId29"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">wide_protocols!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">wide_protocols!$A$1:$G$1</definedName>
     <definedName name="partID">[1]parts!$A:$A</definedName>
     <definedName name="partLabel">[1]parts!$B:$B</definedName>
   </definedNames>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8753" uniqueCount="1990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8593" uniqueCount="1994">
   <si>
     <t>Complete</t>
   </si>
@@ -6110,6 +6111,18 @@
   </si>
   <si>
     <t>match:sampleID</t>
+  </si>
+  <si>
+    <t>match:test</t>
+  </si>
+  <si>
+    <t>"specimen collector project ID"</t>
+  </si>
+  <si>
+    <t>&lt;empty&gt;</t>
+  </si>
+  <si>
+    <t>"specimen collector sample ID"</t>
   </si>
 </sst>
 </file>
@@ -20975,6 +20988,398 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BEACBA-EA3F-A149-88D0-2C7A38DAFA93}">
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="36" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12" style="41" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" style="41" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="32.5" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="29" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>1801</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="29" t="s">
+        <v>1779</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECCAEF06-3FE8-3D4D-A58A-7FC91FF23CF7}">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="28.33203125" customWidth="1"/>
+    <col min="9" max="9" width="38.1640625" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>1749</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B2" t="str">
+        <f>IF(D2&lt;&gt;"",VLOOKUP(D2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H2" s="29"/>
+      <c r="I2" s="28" t="s">
+        <v>1203</v>
+      </c>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B3" t="str">
+        <f>IF(D3&lt;&gt;"",VLOOKUP(D3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="28" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J3" s="29"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B4" t="e">
+        <f>IF(D4&lt;&gt;"",VLOOKUP(D4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H4" s="29"/>
+      <c r="I4" s="28" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J4" s="29"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B5" t="str">
+        <f>IF(D5&lt;&gt;"",VLOOKUP(D5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H5" s="29"/>
+      <c r="I5" s="28" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J5" s="29"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B6" t="str">
+        <f>IF(D6&lt;&gt;"",VLOOKUP(D6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H6" s="29"/>
+      <c r="I6" s="28" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J6" s="29"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B7" t="str">
+        <f>IF(D7&lt;&gt;"",VLOOKUP(D7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="28" t="s">
+        <v>1208</v>
+      </c>
+      <c r="J7" s="29"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" t="str">
+        <f>IF(D8&lt;&gt;"",VLOOKUP(D8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="28" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J8" s="29"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" t="str">
+        <f>IF(D9&lt;&gt;"",VLOOKUP(D9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>1764</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" t="str">
+        <f>IF(D10&lt;&gt;"",VLOOKUP(D10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H10" s="29"/>
+      <c r="I10" s="28" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J10" s="29"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" t="str">
+        <f>IF(D11&lt;&gt;"",VLOOKUP(D11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H11" s="29"/>
+      <c r="I11" s="28" t="s">
+        <v>1212</v>
+      </c>
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12" t="str">
+        <f>IF(D12&lt;&gt;"",VLOOKUP(D12,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>1201</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="28" t="s">
+        <v>1213</v>
+      </c>
+      <c r="J12" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B0FFD5-92F3-FD4F-93FB-9D30DA340366}">
   <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -21422,7 +21827,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C778103B-7A37-1241-A771-EA2606C94ABC}">
   <dimension ref="A1:P64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -23931,7 +24336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19831EB-F90F-BD49-AC5C-0138EB88F455}">
   <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -26085,7 +26490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D465418-9499-EC46-ADC6-7D5629AAF05F}">
   <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -26414,7 +26819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE9D052-A03C-584F-93BD-DC4A71C1C4C3}">
   <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -27101,7 +27506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25523FD1-8CD6-6D41-ABDB-B5E20FE87318}">
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -27308,1287 +27713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0110218-B628-454F-9157-D1743325AF42}">
-  <dimension ref="A1:Q34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="6" width="38.1640625" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="62" customWidth="1"/>
-    <col min="9" max="9" width="53.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10.1640625" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="40" customWidth="1"/>
-    <col min="17" max="17" width="163.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>1443</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>1772</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>1982</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>1883</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>1801</v>
-      </c>
-      <c r="L1" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="29" t="s">
-        <v>1779</v>
-      </c>
-      <c r="O1" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" s="29" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29">
-        <v>1</v>
-      </c>
-      <c r="B2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>1981</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F2" s="30" t="str">
-        <f>IF(H2&lt;&gt;"",VLOOKUP(H2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>AMR detection information</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>1142</v>
-      </c>
-      <c r="I2" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>1711</v>
-      </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="35" t="s">
-        <v>1712</v>
-      </c>
-      <c r="Q2" s="34" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="30" t="str">
-        <f>IF(H3&lt;&gt;"",VLOOKUP(H3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="34"/>
-    </row>
-    <row r="4" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29">
-        <v>26</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="30" t="str">
-        <f>IF(H4&lt;&gt;"",VLOOKUP(H4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Bioinformatics and QC metrics</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29" t="s">
-        <v>1297</v>
-      </c>
-      <c r="M4" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="34"/>
-    </row>
-    <row r="5" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="29">
-        <v>27</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="30" t="str">
-        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Bioinformatics and QC metrics</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>439</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29" t="s">
-        <v>1297</v>
-      </c>
-      <c r="M5" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="35" t="s">
-        <v>1298</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="29">
-        <v>28</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="30" t="str">
-        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Bioinformatics and QC metrics</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>440</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29" t="s">
-        <v>1297</v>
-      </c>
-      <c r="M6" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="35" t="s">
-        <v>1298</v>
-      </c>
-      <c r="Q6" s="29" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29">
-        <v>29</v>
-      </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="30" t="str">
-        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Bioinformatics and QC metrics</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>441</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29" t="s">
-        <v>1297</v>
-      </c>
-      <c r="M7" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="35" t="s">
-        <v>1299</v>
-      </c>
-      <c r="Q7" s="29" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29">
-        <v>30</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="30" t="str">
-        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Bioinformatics and QC metrics</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29" t="s">
-        <v>1297</v>
-      </c>
-      <c r="M8" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="35" t="s">
-        <v>1299</v>
-      </c>
-      <c r="Q8" s="29" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29">
-        <v>31</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="30" t="str">
-        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Bioinformatics and QC metrics</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>443</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29" t="s">
-        <v>1297</v>
-      </c>
-      <c r="M9" s="29" t="s">
-        <v>1080</v>
-      </c>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="35" t="s">
-        <v>1298</v>
-      </c>
-      <c r="Q9" s="29" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="30" t="str">
-        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="29"/>
-    </row>
-    <row r="11" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="29">
-        <v>247</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="30" t="str">
-        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Pathogen diagnostic testing</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29" t="s">
-        <v>1043</v>
-      </c>
-      <c r="M11" s="29" t="s">
-        <v>1424</v>
-      </c>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="35" t="s">
-        <v>1423</v>
-      </c>
-      <c r="Q11" s="37" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="29">
-        <v>248</v>
-      </c>
-      <c r="B12" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="30" t="str">
-        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="I12" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="J12" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29" t="s">
-        <v>1229</v>
-      </c>
-      <c r="M12" s="29" t="s">
-        <v>1334</v>
-      </c>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="35" t="s">
-        <v>1423</v>
-      </c>
-      <c r="Q12" s="34" t="s">
-        <v>1792</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="29">
-        <v>266</v>
-      </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" s="30" t="str">
-        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>1114</v>
-      </c>
-      <c r="I13" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="J13" s="40" t="s">
-        <v>974</v>
-      </c>
-      <c r="K13" s="40" t="s">
-        <v>1061</v>
-      </c>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="35" t="s">
-        <v>1624</v>
-      </c>
-      <c r="Q13" s="29" t="s">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="29">
-        <v>610</v>
-      </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="30" t="str">
-        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="G14" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H14" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="48" t="s">
-        <v>458</v>
-      </c>
-      <c r="J14" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29" t="s">
-        <v>1229</v>
-      </c>
-      <c r="M14" s="29" t="s">
-        <v>1334</v>
-      </c>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="35" t="s">
-        <v>1336</v>
-      </c>
-      <c r="Q14" s="34" t="s">
-        <v>1793</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="30" t="str">
-        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="29"/>
-    </row>
-    <row r="16" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="29">
-        <v>720</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="30" t="str">
-        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>335</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M16" s="29" t="s">
-        <v>1314</v>
-      </c>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q16" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29">
-        <v>721</v>
-      </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="30" t="str">
-        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I17" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="J17" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M17" s="29" t="s">
-        <v>1315</v>
-      </c>
-      <c r="N17" s="29"/>
-      <c r="O17" s="29"/>
-      <c r="P17" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q17" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29">
-        <v>722</v>
-      </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="30" t="str">
-        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I18" s="29" t="s">
-        <v>337</v>
-      </c>
-      <c r="J18" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M18" s="29" t="s">
-        <v>1316</v>
-      </c>
-      <c r="N18" s="29"/>
-      <c r="O18" s="29"/>
-      <c r="P18" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q18" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="29">
-        <v>723</v>
-      </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="30" t="str">
-        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I19" s="29" t="s">
-        <v>338</v>
-      </c>
-      <c r="J19" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M19" s="29" t="s">
-        <v>1317</v>
-      </c>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q19" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29">
-        <v>724</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="30" t="str">
-        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I20" s="29" t="s">
-        <v>339</v>
-      </c>
-      <c r="J20" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M20" s="29" t="s">
-        <v>1318</v>
-      </c>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q20" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29">
-        <v>725</v>
-      </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="30" t="str">
-        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I21" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="J21" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M21" s="29" t="s">
-        <v>1319</v>
-      </c>
-      <c r="N21" s="29"/>
-      <c r="O21" s="29"/>
-      <c r="P21" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q21" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="29">
-        <v>726</v>
-      </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="30" t="str">
-        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G22" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H22" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I22" s="29" t="s">
-        <v>341</v>
-      </c>
-      <c r="J22" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M22" s="29" t="s">
-        <v>1320</v>
-      </c>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29"/>
-      <c r="P22" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q22" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="29">
-        <v>727</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="30" t="str">
-        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I23" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M23" s="29" t="s">
-        <v>1312</v>
-      </c>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q23" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="29">
-        <v>728</v>
-      </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="30" t="str">
-        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H24" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I24" s="29" t="s">
-        <v>342</v>
-      </c>
-      <c r="J24" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M24" s="29" t="s">
-        <v>1321</v>
-      </c>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q24" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="29">
-        <v>729</v>
-      </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="30" t="str">
-        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="I25" s="29" t="s">
-        <v>343</v>
-      </c>
-      <c r="J25" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29" t="s">
-        <v>1303</v>
-      </c>
-      <c r="M25" s="29" t="s">
-        <v>1308</v>
-      </c>
-      <c r="N25" s="29"/>
-      <c r="O25" s="29"/>
-      <c r="P25" s="35" t="s">
-        <v>1305</v>
-      </c>
-      <c r="Q25" s="37" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30" t="str">
-        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="37"/>
-    </row>
-    <row r="27" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="29">
-        <v>730</v>
-      </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="30" t="str">
-        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G27" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H27" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="M27" s="29" t="s">
-        <v>1301</v>
-      </c>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="35" t="s">
-        <v>1302</v>
-      </c>
-      <c r="Q27" s="37" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29">
-        <v>848</v>
-      </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F28" s="30" t="str">
-        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Taxonomic identification information</v>
-      </c>
-      <c r="G28" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>1135</v>
-      </c>
-      <c r="I28" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="J28" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="M28" s="29" t="s">
-        <v>1713</v>
-      </c>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="35" t="s">
-        <v>1714</v>
-      </c>
-      <c r="Q28" s="29"/>
-    </row>
-    <row r="29" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="F29" s="30" t="str">
-        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="F30" s="30" t="str">
-        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="G30" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H30" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="J30" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>1220</v>
-      </c>
-      <c r="M30" s="29" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="29">
-        <v>648</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="F32" s="30" t="str">
-        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="G32" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H32" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="I32" s="48" t="s">
-        <v>458</v>
-      </c>
-      <c r="J32" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29" t="s">
-        <v>1511</v>
-      </c>
-      <c r="M32" s="29" t="s">
-        <v>1333</v>
-      </c>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="39" t="s">
-        <v>1644</v>
-      </c>
-      <c r="Q32" s="29"/>
-    </row>
-    <row r="33" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="29">
-        <v>741</v>
-      </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="30" t="str">
-        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H33" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="J33" s="29" t="s">
-        <v>974</v>
-      </c>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29" t="s">
-        <v>1511</v>
-      </c>
-      <c r="M33" s="29" t="s">
-        <v>1512</v>
-      </c>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29"/>
-      <c r="P33" s="35" t="s">
-        <v>1514</v>
-      </c>
-      <c r="Q33" s="34" t="s">
-        <v>1774</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="29">
-        <v>847</v>
-      </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F34" s="30" t="str">
-        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Taxonomic identification information</v>
-      </c>
-      <c r="G34" s="29" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>1136</v>
-      </c>
-      <c r="I34" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="J34" s="43" t="s">
-        <v>974</v>
-      </c>
-      <c r="K34" s="40"/>
-      <c r="L34" s="29" t="s">
-        <v>1511</v>
-      </c>
-      <c r="M34" s="29" t="s">
-        <v>1698</v>
-      </c>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29"/>
-      <c r="P34" s="29"/>
-      <c r="Q34" s="29"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE02BE1C-61A4-D443-B791-F703172E9F72}">
   <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -28703,7 +27828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96A8578-AB00-374B-A6A4-431F9C79C5B4}">
   <dimension ref="A1:N132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -32788,319 +31913,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EEA163-F56B-CB4C-9B49-2D95046BEE78}">
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
-        <v>1443</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>1883</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="30" t="s">
-        <v>1786</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>650</v>
-      </c>
-      <c r="B2" t="b">
-        <f t="shared" ref="B2:B8" si="0">IF(OR(G2="NA",H2="wide_value"),"",TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" t="str">
-        <f>IF(F2&lt;&gt;"",VLOOKUP(F2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H2" t="s">
-        <v>974</v>
-      </c>
-      <c r="I2" t="s">
-        <v>994</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1230</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>651</v>
-      </c>
-      <c r="B3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" t="str">
-        <f>IF(F3&lt;&gt;"",VLOOKUP(F3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H3" t="s">
-        <v>974</v>
-      </c>
-      <c r="I3" t="s">
-        <v>994</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>652</v>
-      </c>
-      <c r="B4" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" t="str">
-        <f>IF(F4&lt;&gt;"",VLOOKUP(F4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" t="s">
-        <v>974</v>
-      </c>
-      <c r="I4" t="s">
-        <v>994</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>653</v>
-      </c>
-      <c r="B5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" t="str">
-        <f>IF(F5&lt;&gt;"",VLOOKUP(F5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" t="s">
-        <v>185</v>
-      </c>
-      <c r="H5" t="s">
-        <v>974</v>
-      </c>
-      <c r="I5" t="s">
-        <v>994</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1233</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>654</v>
-      </c>
-      <c r="B6" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="str">
-        <f>IF(F6&lt;&gt;"",VLOOKUP(F6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F6" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" t="s">
-        <v>186</v>
-      </c>
-      <c r="H6" t="s">
-        <v>974</v>
-      </c>
-      <c r="I6" t="s">
-        <v>994</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1236</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>655</v>
-      </c>
-      <c r="B7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" t="str">
-        <f>IF(F7&lt;&gt;"",VLOOKUP(F7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G7" t="s">
-        <v>187</v>
-      </c>
-      <c r="H7" t="s">
-        <v>974</v>
-      </c>
-      <c r="I7" t="s">
-        <v>994</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1234</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>656</v>
-      </c>
-      <c r="B8" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" t="str">
-        <f>IF(F8&lt;&gt;"",VLOOKUP(F8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1869</v>
-      </c>
-      <c r="F8" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" t="s">
-        <v>188</v>
-      </c>
-      <c r="H8" t="s">
-        <v>974</v>
-      </c>
-      <c r="I8" t="s">
-        <v>994</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1235</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -35284,6 +34096,319 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2EEA163-F56B-CB4C-9B49-2D95046BEE78}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>1883</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>650</v>
+      </c>
+      <c r="B2" t="b">
+        <f t="shared" ref="B2:B8" si="0">IF(OR(G2="NA",H2="wide_value"),"",TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" t="str">
+        <f>IF(F2&lt;&gt;"",VLOOKUP(F2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" t="s">
+        <v>974</v>
+      </c>
+      <c r="I2" t="s">
+        <v>994</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>651</v>
+      </c>
+      <c r="B3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" t="str">
+        <f>IF(F3&lt;&gt;"",VLOOKUP(F3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H3" t="s">
+        <v>974</v>
+      </c>
+      <c r="I3" t="s">
+        <v>994</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>652</v>
+      </c>
+      <c r="B4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="str">
+        <f>IF(F4&lt;&gt;"",VLOOKUP(F4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" t="s">
+        <v>184</v>
+      </c>
+      <c r="H4" t="s">
+        <v>974</v>
+      </c>
+      <c r="I4" t="s">
+        <v>994</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>653</v>
+      </c>
+      <c r="B5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" t="str">
+        <f>IF(F5&lt;&gt;"",VLOOKUP(F5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" t="s">
+        <v>185</v>
+      </c>
+      <c r="H5" t="s">
+        <v>974</v>
+      </c>
+      <c r="I5" t="s">
+        <v>994</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>654</v>
+      </c>
+      <c r="B6" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" t="str">
+        <f>IF(F6&lt;&gt;"",VLOOKUP(F6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" t="s">
+        <v>974</v>
+      </c>
+      <c r="I6" t="s">
+        <v>994</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1236</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>655</v>
+      </c>
+      <c r="B7" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(F7&lt;&gt;"",VLOOKUP(F7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" t="s">
+        <v>187</v>
+      </c>
+      <c r="H7" t="s">
+        <v>974</v>
+      </c>
+      <c r="I7" t="s">
+        <v>994</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>656</v>
+      </c>
+      <c r="B8" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" t="str">
+        <f>IF(F8&lt;&gt;"",VLOOKUP(F8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" t="s">
+        <v>188</v>
+      </c>
+      <c r="H8" t="s">
+        <v>974</v>
+      </c>
+      <c r="I8" t="s">
+        <v>994</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1235</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB75FE4-77C5-3B48-8438-CF28555CD51A}">
   <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -39084,7 +38209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCE1AF9-53D8-3941-B1D1-62DBC57C6BFA}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -39203,7 +38328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94BF087D-05B8-484D-8712-2C5B4B568867}">
   <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -39321,7 +38446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903503FA-19AE-C146-9865-7A1697985DDA}">
   <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -39505,7 +38630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA0FBE-662C-E84E-B01A-37A99B13F6CC}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -39831,7 +38956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4655D1A3-5738-7443-A984-3973687D3D7B}">
   <dimension ref="A1:N272"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -50812,7 +49937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415EE50B-63F5-1546-AAB5-076951D43503}">
   <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -51113,7 +50238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61AACA08-9138-E54D-BAC1-6C74392A11F1}">
   <dimension ref="A1:B1173"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -57923,6 +57048,1354 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0110218-B628-454F-9157-D1743325AF42}">
+  <dimension ref="A1:R37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="6" width="38.1640625" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="62" customWidth="1"/>
+    <col min="9" max="9" width="53.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="14" width="28" customWidth="1"/>
+    <col min="15" max="15" width="18.6640625" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" customWidth="1"/>
+    <col min="17" max="17" width="40" customWidth="1"/>
+    <col min="18" max="18" width="163.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="29" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>1883</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>1801</v>
+      </c>
+      <c r="L1" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>1839</v>
+      </c>
+      <c r="O1" s="29" t="s">
+        <v>1779</v>
+      </c>
+      <c r="P1" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="29" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="29">
+        <v>1</v>
+      </c>
+      <c r="B2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F2" s="30" t="str">
+        <f>IF(H2&lt;&gt;"",VLOOKUP(H2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>AMR detection information</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="29" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="35" t="s">
+        <v>1712</v>
+      </c>
+      <c r="R2" s="34" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="30" t="str">
+        <f>IF(H3&lt;&gt;"",VLOOKUP(H3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="34"/>
+    </row>
+    <row r="4" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="29">
+        <v>26</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="30" t="str">
+        <f>IF(H4&lt;&gt;"",VLOOKUP(H4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Bioinformatics and QC metrics</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M4" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="34"/>
+    </row>
+    <row r="5" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="29">
+        <v>27</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="30" t="str">
+        <f>IF(H5&lt;&gt;"",VLOOKUP(H5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Bioinformatics and QC metrics</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M5" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="35" t="s">
+        <v>1298</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="29">
+        <v>28</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="30" t="str">
+        <f>IF(H6&lt;&gt;"",VLOOKUP(H6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Bioinformatics and QC metrics</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>440</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M6" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="35" t="s">
+        <v>1298</v>
+      </c>
+      <c r="R6" s="29" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="29">
+        <v>29</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="30" t="str">
+        <f>IF(H7&lt;&gt;"",VLOOKUP(H7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Bioinformatics and QC metrics</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>441</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M7" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="35" t="s">
+        <v>1299</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="29">
+        <v>30</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="30" t="str">
+        <f>IF(H8&lt;&gt;"",VLOOKUP(H8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Bioinformatics and QC metrics</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M8" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="35" t="s">
+        <v>1299</v>
+      </c>
+      <c r="R8" s="29" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="29">
+        <v>31</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="30" t="str">
+        <f>IF(H9&lt;&gt;"",VLOOKUP(H9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Bioinformatics and QC metrics</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29" t="s">
+        <v>1297</v>
+      </c>
+      <c r="M9" s="29" t="s">
+        <v>1080</v>
+      </c>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="35" t="s">
+        <v>1298</v>
+      </c>
+      <c r="R9" s="29" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="30" t="str">
+        <f>IF(H10&lt;&gt;"",VLOOKUP(H10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="29"/>
+    </row>
+    <row r="11" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="29">
+        <v>247</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F11" s="30" t="str">
+        <f>IF(H11&lt;&gt;"",VLOOKUP(H11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Pathogen diagnostic testing</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29" t="s">
+        <v>1043</v>
+      </c>
+      <c r="M11" s="29" t="s">
+        <v>1424</v>
+      </c>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="35" t="s">
+        <v>1423</v>
+      </c>
+      <c r="R11" s="37" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="29">
+        <v>248</v>
+      </c>
+      <c r="B12" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="30" t="str">
+        <f>IF(H12&lt;&gt;"",VLOOKUP(H12,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M12" s="29" t="s">
+        <v>1334</v>
+      </c>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="35" t="s">
+        <v>1423</v>
+      </c>
+      <c r="R12" s="34" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="29">
+        <v>266</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="30" t="str">
+        <f>IF(H13&lt;&gt;"",VLOOKUP(H13,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="J13" s="40" t="s">
+        <v>974</v>
+      </c>
+      <c r="K13" s="40" t="s">
+        <v>1061</v>
+      </c>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="35" t="s">
+        <v>1624</v>
+      </c>
+      <c r="R13" s="29" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="29">
+        <v>610</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="30" t="str">
+        <f>IF(H14&lt;&gt;"",VLOOKUP(H14,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="48" t="s">
+        <v>458</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M14" s="29" t="s">
+        <v>1334</v>
+      </c>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="35" t="s">
+        <v>1336</v>
+      </c>
+      <c r="R14" s="34" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="30" t="str">
+        <f>IF(H15&lt;&gt;"",VLOOKUP(H15,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="29"/>
+    </row>
+    <row r="16" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="29">
+        <v>720</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="30" t="str">
+        <f>IF(H16&lt;&gt;"",VLOOKUP(H16,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>1314</v>
+      </c>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R16" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="29">
+        <v>721</v>
+      </c>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="30" t="str">
+        <f>IF(H17&lt;&gt;"",VLOOKUP(H17,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="J17" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M17" s="29" t="s">
+        <v>1315</v>
+      </c>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R17" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="29">
+        <v>722</v>
+      </c>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="30" t="str">
+        <f>IF(H18&lt;&gt;"",VLOOKUP(H18,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="J18" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M18" s="29" t="s">
+        <v>1316</v>
+      </c>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R18" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="29">
+        <v>723</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="30" t="str">
+        <f>IF(H19&lt;&gt;"",VLOOKUP(H19,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I19" s="29" t="s">
+        <v>338</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M19" s="29" t="s">
+        <v>1317</v>
+      </c>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R19" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="29">
+        <v>724</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="30" t="str">
+        <f>IF(H20&lt;&gt;"",VLOOKUP(H20,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I20" s="29" t="s">
+        <v>339</v>
+      </c>
+      <c r="J20" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M20" s="29" t="s">
+        <v>1318</v>
+      </c>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R20" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="29">
+        <v>725</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="30" t="str">
+        <f>IF(H21&lt;&gt;"",VLOOKUP(H21,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M21" s="29" t="s">
+        <v>1319</v>
+      </c>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R21" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="29">
+        <v>726</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="30" t="str">
+        <f>IF(H22&lt;&gt;"",VLOOKUP(H22,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M22" s="29" t="s">
+        <v>1320</v>
+      </c>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R22" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="29">
+        <v>727</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="30" t="str">
+        <f>IF(H23&lt;&gt;"",VLOOKUP(H23,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M23" s="29" t="s">
+        <v>1312</v>
+      </c>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R23" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="29">
+        <v>728</v>
+      </c>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="30" t="str">
+        <f>IF(H24&lt;&gt;"",VLOOKUP(H24,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="J24" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M24" s="29" t="s">
+        <v>1321</v>
+      </c>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R24" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="29">
+        <v>729</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="30" t="str">
+        <f>IF(H25&lt;&gt;"",VLOOKUP(H25,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="J25" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29" t="s">
+        <v>1303</v>
+      </c>
+      <c r="M25" s="29" t="s">
+        <v>1308</v>
+      </c>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="35" t="s">
+        <v>1305</v>
+      </c>
+      <c r="R25" s="37" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="30" t="str">
+        <f>IF(H26&lt;&gt;"",VLOOKUP(H26,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="37"/>
+    </row>
+    <row r="27" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="29">
+        <v>730</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="30" t="str">
+        <f>IF(H27&lt;&gt;"",VLOOKUP(H27,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H27" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M27" s="29" t="s">
+        <v>1301</v>
+      </c>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="35" t="s">
+        <v>1302</v>
+      </c>
+      <c r="R27" s="37" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="29">
+        <v>848</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F28" s="30" t="str">
+        <f>IF(H28&lt;&gt;"",VLOOKUP(H28,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Taxonomic identification information</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="J28" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="M28" s="29" t="s">
+        <v>1713</v>
+      </c>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="35" t="s">
+        <v>1714</v>
+      </c>
+      <c r="R28" s="29"/>
+    </row>
+    <row r="29" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F29" s="30" t="str">
+        <f>IF(H29&lt;&gt;"",VLOOKUP(H29,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F30" s="30" t="str">
+        <f>IF(H30&lt;&gt;"",VLOOKUP(H30,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Database identifiers</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="L30" s="29" t="s">
+        <v>1220</v>
+      </c>
+      <c r="M30" s="29" t="s">
+        <v>1221</v>
+      </c>
+      <c r="N30" s="29"/>
+    </row>
+    <row r="32" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="29">
+        <v>648</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="30" t="str">
+        <f>IF(H32&lt;&gt;"",VLOOKUP(H32,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="I32" s="48" t="s">
+        <v>458</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29" t="s">
+        <v>1511</v>
+      </c>
+      <c r="M32" s="29" t="s">
+        <v>1333</v>
+      </c>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="39" t="s">
+        <v>1644</v>
+      </c>
+      <c r="R32" s="29"/>
+    </row>
+    <row r="33" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="29">
+        <v>741</v>
+      </c>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="30" t="str">
+        <f>IF(H33&lt;&gt;"",VLOOKUP(H33,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="J33" s="29" t="s">
+        <v>974</v>
+      </c>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29" t="s">
+        <v>1511</v>
+      </c>
+      <c r="M33" s="29" t="s">
+        <v>1512</v>
+      </c>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="35" t="s">
+        <v>1514</v>
+      </c>
+      <c r="R33" s="34" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="29">
+        <v>847</v>
+      </c>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F34" s="30" t="str">
+        <f>IF(H34&lt;&gt;"",VLOOKUP(H34,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Taxonomic identification information</v>
+      </c>
+      <c r="G34" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="J34" s="43" t="s">
+        <v>974</v>
+      </c>
+      <c r="K34" s="40"/>
+      <c r="L34" s="29" t="s">
+        <v>1511</v>
+      </c>
+      <c r="M34" s="29" t="s">
+        <v>1698</v>
+      </c>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="J36" t="s">
+        <v>974</v>
+      </c>
+      <c r="L36" s="30" t="s">
+        <v>1988</v>
+      </c>
+      <c r="N36" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>1869</v>
+      </c>
+      <c r="J37" t="s">
+        <v>974</v>
+      </c>
+      <c r="L37" s="29" t="s">
+        <v>1989</v>
+      </c>
+      <c r="N37" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA8EF7F3-EB33-C64C-8956-945FAC941EB4}">
   <dimension ref="A1:V125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -58027,12 +58500,6 @@
       <c r="G2" t="s">
         <v>974</v>
       </c>
-      <c r="J2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1102</v>
-      </c>
       <c r="N2" t="s">
         <v>976</v>
       </c>
@@ -58075,12 +58542,6 @@
       <c r="G3" t="s">
         <v>974</v>
       </c>
-      <c r="J3" t="s">
-        <v>151</v>
-      </c>
-      <c r="K3" t="s">
-        <v>1102</v>
-      </c>
       <c r="N3" t="s">
         <v>980</v>
       </c>
@@ -58123,12 +58584,6 @@
       <c r="G4" t="s">
         <v>974</v>
       </c>
-      <c r="J4" t="s">
-        <v>151</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1102</v>
-      </c>
       <c r="N4" t="s">
         <v>981</v>
       </c>
@@ -58170,12 +58625,6 @@
       </c>
       <c r="G5" t="s">
         <v>974</v>
-      </c>
-      <c r="J5" t="s">
-        <v>151</v>
-      </c>
-      <c r="K5" t="s">
-        <v>1102</v>
       </c>
       <c r="N5" t="s">
         <v>983</v>
@@ -58231,12 +58680,6 @@
       <c r="H7" t="s">
         <v>273</v>
       </c>
-      <c r="J7" t="s">
-        <v>151</v>
-      </c>
-      <c r="K7" t="s">
-        <v>1102</v>
-      </c>
       <c r="O7" t="s">
         <v>1052</v>
       </c>
@@ -58279,12 +58722,6 @@
       <c r="H8" t="s">
         <v>274</v>
       </c>
-      <c r="J8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1102</v>
-      </c>
       <c r="O8" t="s">
         <v>1052</v>
       </c>
@@ -58326,12 +58763,6 @@
       </c>
       <c r="H9" t="s">
         <v>275</v>
-      </c>
-      <c r="J9" t="s">
-        <v>151</v>
-      </c>
-      <c r="K9" t="s">
-        <v>1102</v>
       </c>
       <c r="O9" t="s">
         <v>1052</v>
@@ -58375,12 +58806,6 @@
       <c r="G11" t="s">
         <v>974</v>
       </c>
-      <c r="J11" t="s">
-        <v>151</v>
-      </c>
-      <c r="K11" t="s">
-        <v>1102</v>
-      </c>
       <c r="N11" t="s">
         <v>985</v>
       </c>
@@ -58419,12 +58844,6 @@
       </c>
       <c r="G13" t="s">
         <v>974</v>
-      </c>
-      <c r="J13" t="s">
-        <v>151</v>
-      </c>
-      <c r="K13" t="s">
-        <v>1102</v>
       </c>
       <c r="N13" t="s">
         <v>986</v>
@@ -58477,12 +58896,6 @@
       <c r="H15" t="s">
         <v>1067</v>
       </c>
-      <c r="J15" t="s">
-        <v>151</v>
-      </c>
-      <c r="K15" t="s">
-        <v>1102</v>
-      </c>
       <c r="O15" t="s">
         <v>1052</v>
       </c>
@@ -58528,12 +58941,6 @@
       <c r="H16" t="s">
         <v>1068</v>
       </c>
-      <c r="J16" t="s">
-        <v>151</v>
-      </c>
-      <c r="K16" t="s">
-        <v>1102</v>
-      </c>
       <c r="O16" t="s">
         <v>1052</v>
       </c>
@@ -58579,12 +58986,6 @@
       <c r="H17" t="s">
         <v>1069</v>
       </c>
-      <c r="J17" t="s">
-        <v>151</v>
-      </c>
-      <c r="K17" t="s">
-        <v>1102</v>
-      </c>
       <c r="O17" t="s">
         <v>1052</v>
       </c>
@@ -58630,12 +59031,6 @@
       <c r="H18" t="s">
         <v>1070</v>
       </c>
-      <c r="J18" t="s">
-        <v>151</v>
-      </c>
-      <c r="K18" t="s">
-        <v>1102</v>
-      </c>
       <c r="O18" t="s">
         <v>1052</v>
       </c>
@@ -58681,12 +59076,6 @@
       <c r="H19" t="s">
         <v>1071</v>
       </c>
-      <c r="J19" t="s">
-        <v>151</v>
-      </c>
-      <c r="K19" t="s">
-        <v>1102</v>
-      </c>
       <c r="O19" t="s">
         <v>1052</v>
       </c>
@@ -58732,12 +59121,6 @@
       <c r="H20" t="s">
         <v>1072</v>
       </c>
-      <c r="J20" t="s">
-        <v>151</v>
-      </c>
-      <c r="K20" t="s">
-        <v>1102</v>
-      </c>
       <c r="O20" t="s">
         <v>1052</v>
       </c>
@@ -58782,12 +59165,6 @@
       </c>
       <c r="H21" t="s">
         <v>1073</v>
-      </c>
-      <c r="J21" t="s">
-        <v>151</v>
-      </c>
-      <c r="K21" t="s">
-        <v>1102</v>
       </c>
       <c r="O21" t="s">
         <v>1052</v>
@@ -58834,12 +59211,6 @@
       <c r="G23" t="s">
         <v>974</v>
       </c>
-      <c r="J23" t="s">
-        <v>151</v>
-      </c>
-      <c r="K23" t="s">
-        <v>1102</v>
-      </c>
       <c r="N23" t="s">
         <v>1928</v>
       </c>
@@ -58894,12 +59265,6 @@
       <c r="H25" t="s">
         <v>1085</v>
       </c>
-      <c r="J25" t="s">
-        <v>151</v>
-      </c>
-      <c r="K25" t="s">
-        <v>1102</v>
-      </c>
       <c r="O25" t="s">
         <v>1052</v>
       </c>
@@ -58942,12 +59307,6 @@
       <c r="H26" t="s">
         <v>1085</v>
       </c>
-      <c r="J26" t="s">
-        <v>151</v>
-      </c>
-      <c r="K26" t="s">
-        <v>1102</v>
-      </c>
       <c r="O26" t="s">
         <v>1052</v>
       </c>
@@ -58990,12 +59349,6 @@
       <c r="H27" t="s">
         <v>1087</v>
       </c>
-      <c r="J27" t="s">
-        <v>151</v>
-      </c>
-      <c r="K27" t="s">
-        <v>1102</v>
-      </c>
       <c r="O27" t="s">
         <v>1052</v>
       </c>
@@ -59038,12 +59391,6 @@
       <c r="H28" t="s">
         <v>1086</v>
       </c>
-      <c r="J28" t="s">
-        <v>151</v>
-      </c>
-      <c r="K28" t="s">
-        <v>1102</v>
-      </c>
       <c r="O28" t="s">
         <v>1052</v>
       </c>
@@ -59086,12 +59433,6 @@
       <c r="H29" t="s">
         <v>1087</v>
       </c>
-      <c r="J29" t="s">
-        <v>151</v>
-      </c>
-      <c r="K29" t="s">
-        <v>1102</v>
-      </c>
       <c r="O29" t="s">
         <v>1052</v>
       </c>
@@ -59134,12 +59475,6 @@
       <c r="H30" t="s">
         <v>1088</v>
       </c>
-      <c r="J30" t="s">
-        <v>151</v>
-      </c>
-      <c r="K30" t="s">
-        <v>1102</v>
-      </c>
       <c r="O30" t="s">
         <v>1052</v>
       </c>
@@ -59182,12 +59517,6 @@
       <c r="H31" t="s">
         <v>1090</v>
       </c>
-      <c r="J31" t="s">
-        <v>151</v>
-      </c>
-      <c r="K31" t="s">
-        <v>1102</v>
-      </c>
       <c r="O31" t="s">
         <v>1052</v>
       </c>
@@ -59229,12 +59558,6 @@
       </c>
       <c r="H32" t="s">
         <v>1089</v>
-      </c>
-      <c r="J32" t="s">
-        <v>151</v>
-      </c>
-      <c r="K32" t="s">
-        <v>1102</v>
       </c>
       <c r="O32" t="s">
         <v>1052</v>
@@ -59284,12 +59607,6 @@
       <c r="H34" t="s">
         <v>1085</v>
       </c>
-      <c r="J34" t="s">
-        <v>151</v>
-      </c>
-      <c r="K34" t="s">
-        <v>1102</v>
-      </c>
       <c r="O34" t="s">
         <v>1052</v>
       </c>
@@ -59332,12 +59649,6 @@
       <c r="H35" t="s">
         <v>1085</v>
       </c>
-      <c r="J35" t="s">
-        <v>151</v>
-      </c>
-      <c r="K35" t="s">
-        <v>1102</v>
-      </c>
       <c r="O35" t="s">
         <v>1052</v>
       </c>
@@ -59380,12 +59691,6 @@
       <c r="H36" t="s">
         <v>1087</v>
       </c>
-      <c r="J36" t="s">
-        <v>151</v>
-      </c>
-      <c r="K36" t="s">
-        <v>1102</v>
-      </c>
       <c r="O36" t="s">
         <v>1052</v>
       </c>
@@ -59428,12 +59733,6 @@
       <c r="H37" t="s">
         <v>1086</v>
       </c>
-      <c r="J37" t="s">
-        <v>151</v>
-      </c>
-      <c r="K37" t="s">
-        <v>1102</v>
-      </c>
       <c r="O37" t="s">
         <v>1052</v>
       </c>
@@ -59476,12 +59775,6 @@
       <c r="H38" t="s">
         <v>1087</v>
       </c>
-      <c r="J38" t="s">
-        <v>151</v>
-      </c>
-      <c r="K38" t="s">
-        <v>1102</v>
-      </c>
       <c r="O38" t="s">
         <v>1052</v>
       </c>
@@ -59524,12 +59817,6 @@
       <c r="H39" t="s">
         <v>1088</v>
       </c>
-      <c r="J39" t="s">
-        <v>151</v>
-      </c>
-      <c r="K39" t="s">
-        <v>1102</v>
-      </c>
       <c r="O39" t="s">
         <v>1052</v>
       </c>
@@ -59572,12 +59859,6 @@
       <c r="H40" t="s">
         <v>1090</v>
       </c>
-      <c r="J40" t="s">
-        <v>151</v>
-      </c>
-      <c r="K40" t="s">
-        <v>1102</v>
-      </c>
       <c r="O40" t="s">
         <v>1052</v>
       </c>
@@ -59619,12 +59900,6 @@
       </c>
       <c r="H41" t="s">
         <v>1089</v>
-      </c>
-      <c r="J41" t="s">
-        <v>151</v>
-      </c>
-      <c r="K41" t="s">
-        <v>1102</v>
       </c>
       <c r="O41" t="s">
         <v>1052</v>
@@ -59668,12 +59943,6 @@
       <c r="G43" t="s">
         <v>974</v>
       </c>
-      <c r="J43" t="s">
-        <v>151</v>
-      </c>
-      <c r="K43" t="s">
-        <v>1102</v>
-      </c>
       <c r="N43" t="s">
         <v>1513</v>
       </c>
@@ -59713,12 +59982,6 @@
       <c r="G44" t="s">
         <v>974</v>
       </c>
-      <c r="J44" t="s">
-        <v>151</v>
-      </c>
-      <c r="K44" t="s">
-        <v>1102</v>
-      </c>
       <c r="N44" t="s">
         <v>1513</v>
       </c>
@@ -59758,12 +60021,6 @@
       <c r="G45" t="s">
         <v>974</v>
       </c>
-      <c r="J45" t="s">
-        <v>151</v>
-      </c>
-      <c r="K45" t="s">
-        <v>1102</v>
-      </c>
       <c r="N45" t="s">
         <v>1513</v>
       </c>
@@ -59803,12 +60060,6 @@
       <c r="G46" t="s">
         <v>974</v>
       </c>
-      <c r="J46" t="s">
-        <v>151</v>
-      </c>
-      <c r="K46" t="s">
-        <v>1102</v>
-      </c>
       <c r="N46" t="s">
         <v>1513</v>
       </c>
@@ -59848,12 +60099,6 @@
       <c r="G47" t="s">
         <v>974</v>
       </c>
-      <c r="J47" t="s">
-        <v>151</v>
-      </c>
-      <c r="K47" t="s">
-        <v>1102</v>
-      </c>
       <c r="N47" t="s">
         <v>1513</v>
       </c>
@@ -59896,12 +60141,6 @@
       <c r="G48" t="s">
         <v>974</v>
       </c>
-      <c r="J48" t="s">
-        <v>151</v>
-      </c>
-      <c r="K48" t="s">
-        <v>1102</v>
-      </c>
       <c r="N48" t="s">
         <v>1513</v>
       </c>
@@ -59941,12 +60180,6 @@
       <c r="G49" t="s">
         <v>974</v>
       </c>
-      <c r="J49" t="s">
-        <v>151</v>
-      </c>
-      <c r="K49" t="s">
-        <v>1102</v>
-      </c>
       <c r="N49" t="s">
         <v>1513</v>
       </c>
@@ -59986,12 +60219,6 @@
       <c r="G50" t="s">
         <v>974</v>
       </c>
-      <c r="J50" t="s">
-        <v>151</v>
-      </c>
-      <c r="K50" t="s">
-        <v>1102</v>
-      </c>
       <c r="N50" t="s">
         <v>1513</v>
       </c>
@@ -60031,12 +60258,6 @@
       <c r="G51" t="s">
         <v>974</v>
       </c>
-      <c r="J51" t="s">
-        <v>151</v>
-      </c>
-      <c r="K51" t="s">
-        <v>1102</v>
-      </c>
       <c r="N51" t="s">
         <v>1513</v>
       </c>
@@ -60076,12 +60297,6 @@
       <c r="G52" t="s">
         <v>974</v>
       </c>
-      <c r="J52" t="s">
-        <v>151</v>
-      </c>
-      <c r="K52" t="s">
-        <v>1102</v>
-      </c>
       <c r="N52" t="s">
         <v>1513</v>
       </c>
@@ -60121,12 +60336,6 @@
       <c r="G53" t="s">
         <v>974</v>
       </c>
-      <c r="J53" t="s">
-        <v>151</v>
-      </c>
-      <c r="K53" t="s">
-        <v>1102</v>
-      </c>
       <c r="N53" t="s">
         <v>1513</v>
       </c>
@@ -60166,12 +60375,6 @@
       <c r="G54" t="s">
         <v>974</v>
       </c>
-      <c r="J54" t="s">
-        <v>151</v>
-      </c>
-      <c r="K54" t="s">
-        <v>1102</v>
-      </c>
       <c r="N54" t="s">
         <v>1513</v>
       </c>
@@ -60211,12 +60414,6 @@
       <c r="G55" t="s">
         <v>974</v>
       </c>
-      <c r="J55" t="s">
-        <v>151</v>
-      </c>
-      <c r="K55" t="s">
-        <v>1102</v>
-      </c>
       <c r="N55" t="s">
         <v>1513</v>
       </c>
@@ -60256,12 +60453,6 @@
       <c r="G56" t="s">
         <v>974</v>
       </c>
-      <c r="J56" t="s">
-        <v>151</v>
-      </c>
-      <c r="K56" t="s">
-        <v>1102</v>
-      </c>
       <c r="N56" t="s">
         <v>1513</v>
       </c>
@@ -60310,12 +60501,6 @@
       <c r="G57" t="s">
         <v>974</v>
       </c>
-      <c r="J57" t="s">
-        <v>151</v>
-      </c>
-      <c r="K57" t="s">
-        <v>1102</v>
-      </c>
       <c r="N57" t="s">
         <v>1513</v>
       </c>
@@ -60364,12 +60549,6 @@
       <c r="G58" t="s">
         <v>974</v>
       </c>
-      <c r="J58" t="s">
-        <v>151</v>
-      </c>
-      <c r="K58" t="s">
-        <v>1102</v>
-      </c>
       <c r="N58" t="s">
         <v>982</v>
       </c>
@@ -60409,12 +60588,6 @@
       <c r="G59" t="s">
         <v>974</v>
       </c>
-      <c r="J59" t="s">
-        <v>151</v>
-      </c>
-      <c r="K59" t="s">
-        <v>1102</v>
-      </c>
       <c r="N59" t="s">
         <v>991</v>
       </c>
@@ -60454,12 +60627,6 @@
       <c r="G60" t="s">
         <v>974</v>
       </c>
-      <c r="J60" t="s">
-        <v>151</v>
-      </c>
-      <c r="K60" t="s">
-        <v>1102</v>
-      </c>
       <c r="O60" t="s">
         <v>1052</v>
       </c>
@@ -60499,12 +60666,6 @@
       <c r="G61" t="s">
         <v>974</v>
       </c>
-      <c r="J61" t="s">
-        <v>151</v>
-      </c>
-      <c r="K61" t="s">
-        <v>1102</v>
-      </c>
       <c r="N61" t="s">
         <v>993</v>
       </c>
@@ -60544,12 +60705,6 @@
       <c r="G62" t="s">
         <v>974</v>
       </c>
-      <c r="J62" t="s">
-        <v>151</v>
-      </c>
-      <c r="K62" t="s">
-        <v>1102</v>
-      </c>
       <c r="O62" t="s">
         <v>1053</v>
       </c>
@@ -60586,12 +60741,6 @@
       <c r="G63" t="s">
         <v>974</v>
       </c>
-      <c r="J63" t="s">
-        <v>151</v>
-      </c>
-      <c r="K63" t="s">
-        <v>1102</v>
-      </c>
       <c r="O63" t="s">
         <v>1053</v>
       </c>
@@ -60628,12 +60777,6 @@
       <c r="G64" t="s">
         <v>974</v>
       </c>
-      <c r="J64" t="s">
-        <v>151</v>
-      </c>
-      <c r="K64" t="s">
-        <v>1102</v>
-      </c>
       <c r="O64" t="s">
         <v>1052</v>
       </c>
@@ -60670,12 +60813,6 @@
       <c r="G65" t="s">
         <v>974</v>
       </c>
-      <c r="J65" t="s">
-        <v>151</v>
-      </c>
-      <c r="K65" t="s">
-        <v>1102</v>
-      </c>
       <c r="N65" t="s">
         <v>984</v>
       </c>
@@ -60715,12 +60852,6 @@
       <c r="G66" t="s">
         <v>974</v>
       </c>
-      <c r="J66" t="s">
-        <v>151</v>
-      </c>
-      <c r="K66" t="s">
-        <v>1102</v>
-      </c>
       <c r="N66" t="s">
         <v>977</v>
       </c>
@@ -60760,12 +60891,6 @@
       <c r="G67" t="s">
         <v>974</v>
       </c>
-      <c r="J67" t="s">
-        <v>151</v>
-      </c>
-      <c r="K67" t="s">
-        <v>1102</v>
-      </c>
       <c r="N67" t="s">
         <v>978</v>
       </c>
@@ -60805,12 +60930,6 @@
       <c r="G68" t="s">
         <v>974</v>
       </c>
-      <c r="J68" t="s">
-        <v>151</v>
-      </c>
-      <c r="K68" t="s">
-        <v>1102</v>
-      </c>
       <c r="N68" t="s">
         <v>979</v>
       </c>
@@ -60850,12 +60969,6 @@
       <c r="G69" t="s">
         <v>974</v>
       </c>
-      <c r="J69" t="s">
-        <v>151</v>
-      </c>
-      <c r="K69" t="s">
-        <v>1102</v>
-      </c>
       <c r="N69" t="s">
         <v>1851</v>
       </c>
@@ -60898,12 +61011,6 @@
       <c r="G70" t="s">
         <v>974</v>
       </c>
-      <c r="J70" t="s">
-        <v>151</v>
-      </c>
-      <c r="K70" t="s">
-        <v>1102</v>
-      </c>
       <c r="N70" t="s">
         <v>1852</v>
       </c>
@@ -60946,12 +61053,6 @@
       <c r="G71" t="s">
         <v>974</v>
       </c>
-      <c r="J71" t="s">
-        <v>151</v>
-      </c>
-      <c r="K71" t="s">
-        <v>1102</v>
-      </c>
       <c r="N71" t="s">
         <v>988</v>
       </c>
@@ -60991,12 +61092,6 @@
       <c r="G72" t="s">
         <v>974</v>
       </c>
-      <c r="J72" t="s">
-        <v>151</v>
-      </c>
-      <c r="K72" t="s">
-        <v>1102</v>
-      </c>
       <c r="N72" t="s">
         <v>987</v>
       </c>
@@ -61036,12 +61131,6 @@
       <c r="G73" t="s">
         <v>974</v>
       </c>
-      <c r="J73" t="s">
-        <v>151</v>
-      </c>
-      <c r="K73" t="s">
-        <v>1102</v>
-      </c>
       <c r="N73" t="s">
         <v>989</v>
       </c>
@@ -61081,12 +61170,6 @@
       <c r="G74" t="s">
         <v>974</v>
       </c>
-      <c r="J74" t="s">
-        <v>151</v>
-      </c>
-      <c r="K74" t="s">
-        <v>1102</v>
-      </c>
       <c r="N74" t="s">
         <v>1853</v>
       </c>
@@ -61125,12 +61208,6 @@
       </c>
       <c r="G75" t="s">
         <v>974</v>
-      </c>
-      <c r="J75" t="s">
-        <v>151</v>
-      </c>
-      <c r="K75" t="s">
-        <v>1102</v>
       </c>
       <c r="N75" t="s">
         <v>990</v>
@@ -61186,12 +61263,6 @@
       <c r="I77" t="s">
         <v>1925</v>
       </c>
-      <c r="J77" t="s">
-        <v>151</v>
-      </c>
-      <c r="K77" t="s">
-        <v>1102</v>
-      </c>
       <c r="O77" t="s">
         <v>1053</v>
       </c>
@@ -61242,12 +61313,6 @@
       </c>
       <c r="I78" t="s">
         <v>1925</v>
-      </c>
-      <c r="J78" t="s">
-        <v>151</v>
-      </c>
-      <c r="K78" t="s">
-        <v>1102</v>
       </c>
       <c r="O78" t="s">
         <v>1053</v>
@@ -61301,12 +61366,6 @@
       <c r="I80" t="s">
         <v>1925</v>
       </c>
-      <c r="J80" t="s">
-        <v>151</v>
-      </c>
-      <c r="K80" t="s">
-        <v>1102</v>
-      </c>
       <c r="O80" t="s">
         <v>1053</v>
       </c>
@@ -61358,12 +61417,6 @@
       <c r="G82" t="s">
         <v>974</v>
       </c>
-      <c r="J82" t="s">
-        <v>151</v>
-      </c>
-      <c r="K82" t="s">
-        <v>1102</v>
-      </c>
       <c r="L82" t="s">
         <v>1333</v>
       </c>
@@ -61408,12 +61461,6 @@
       </c>
       <c r="G84" t="s">
         <v>974</v>
-      </c>
-      <c r="J84" t="s">
-        <v>151</v>
-      </c>
-      <c r="K84" t="s">
-        <v>1102</v>
       </c>
       <c r="L84" s="30" t="s">
         <v>1333</v>
@@ -61470,12 +61517,6 @@
       <c r="H86" t="s">
         <v>1539</v>
       </c>
-      <c r="J86" t="s">
-        <v>151</v>
-      </c>
-      <c r="K86" t="s">
-        <v>1102</v>
-      </c>
       <c r="L86" t="s">
         <v>1333</v>
       </c>
@@ -61521,12 +61562,6 @@
       <c r="H87" t="s">
         <v>1540</v>
       </c>
-      <c r="J87" t="s">
-        <v>151</v>
-      </c>
-      <c r="K87" t="s">
-        <v>1102</v>
-      </c>
       <c r="L87" t="s">
         <v>1333</v>
       </c>
@@ -61572,12 +61607,6 @@
       <c r="H88" t="s">
         <v>1541</v>
       </c>
-      <c r="J88" t="s">
-        <v>151</v>
-      </c>
-      <c r="K88" t="s">
-        <v>1102</v>
-      </c>
       <c r="L88" t="s">
         <v>1333</v>
       </c>
@@ -61623,12 +61652,6 @@
       <c r="H89" t="s">
         <v>1542</v>
       </c>
-      <c r="J89" t="s">
-        <v>151</v>
-      </c>
-      <c r="K89" t="s">
-        <v>1102</v>
-      </c>
       <c r="L89" t="s">
         <v>1333</v>
       </c>
@@ -61674,12 +61697,6 @@
       <c r="H90" t="s">
         <v>1543</v>
       </c>
-      <c r="J90" t="s">
-        <v>151</v>
-      </c>
-      <c r="K90" t="s">
-        <v>1102</v>
-      </c>
       <c r="L90" t="s">
         <v>1333</v>
       </c>
@@ -61725,12 +61742,6 @@
       <c r="H91" t="s">
         <v>1544</v>
       </c>
-      <c r="J91" t="s">
-        <v>151</v>
-      </c>
-      <c r="K91" t="s">
-        <v>1102</v>
-      </c>
       <c r="L91" t="s">
         <v>1333</v>
       </c>
@@ -61776,12 +61787,6 @@
       <c r="H92" t="s">
         <v>1545</v>
       </c>
-      <c r="J92" t="s">
-        <v>151</v>
-      </c>
-      <c r="K92" t="s">
-        <v>1102</v>
-      </c>
       <c r="L92" t="s">
         <v>1333</v>
       </c>
@@ -61827,12 +61832,6 @@
       <c r="H93" t="s">
         <v>1546</v>
       </c>
-      <c r="J93" t="s">
-        <v>151</v>
-      </c>
-      <c r="K93" t="s">
-        <v>1102</v>
-      </c>
       <c r="L93" t="s">
         <v>1333</v>
       </c>
@@ -61878,12 +61877,6 @@
       <c r="H94" t="s">
         <v>1547</v>
       </c>
-      <c r="J94" t="s">
-        <v>151</v>
-      </c>
-      <c r="K94" t="s">
-        <v>1102</v>
-      </c>
       <c r="L94" t="s">
         <v>1333</v>
       </c>
@@ -61929,12 +61922,6 @@
       <c r="H95" t="s">
         <v>1548</v>
       </c>
-      <c r="J95" t="s">
-        <v>151</v>
-      </c>
-      <c r="K95" t="s">
-        <v>1102</v>
-      </c>
       <c r="L95" t="s">
         <v>1333</v>
       </c>
@@ -61979,12 +61966,6 @@
       </c>
       <c r="H96" t="s">
         <v>1549</v>
-      </c>
-      <c r="J96" t="s">
-        <v>151</v>
-      </c>
-      <c r="K96" t="s">
-        <v>1102</v>
       </c>
       <c r="L96" t="s">
         <v>1333</v>
@@ -62040,12 +62021,6 @@
       <c r="I98" t="s">
         <v>1882</v>
       </c>
-      <c r="J98" t="s">
-        <v>151</v>
-      </c>
-      <c r="K98" t="s">
-        <v>1102</v>
-      </c>
       <c r="L98" t="s">
         <v>1333</v>
       </c>
@@ -62097,12 +62072,6 @@
       <c r="I99" t="s">
         <v>1882</v>
       </c>
-      <c r="J99" t="s">
-        <v>151</v>
-      </c>
-      <c r="K99" t="s">
-        <v>1102</v>
-      </c>
       <c r="L99" t="s">
         <v>1333</v>
       </c>
@@ -62154,12 +62123,6 @@
       <c r="I100" t="s">
         <v>1882</v>
       </c>
-      <c r="J100" t="s">
-        <v>151</v>
-      </c>
-      <c r="K100" t="s">
-        <v>1102</v>
-      </c>
       <c r="L100" t="s">
         <v>1333</v>
       </c>
@@ -62211,12 +62174,6 @@
       <c r="I101" t="s">
         <v>1882</v>
       </c>
-      <c r="J101" t="s">
-        <v>151</v>
-      </c>
-      <c r="K101" t="s">
-        <v>1102</v>
-      </c>
       <c r="L101" t="s">
         <v>1333</v>
       </c>
@@ -62268,12 +62225,6 @@
       <c r="I102" t="s">
         <v>1882</v>
       </c>
-      <c r="J102" t="s">
-        <v>151</v>
-      </c>
-      <c r="K102" t="s">
-        <v>1102</v>
-      </c>
       <c r="L102" t="s">
         <v>1333</v>
       </c>
@@ -62325,12 +62276,6 @@
       <c r="I103" t="s">
         <v>1882</v>
       </c>
-      <c r="J103" t="s">
-        <v>151</v>
-      </c>
-      <c r="K103" t="s">
-        <v>1102</v>
-      </c>
       <c r="L103" t="s">
         <v>1333</v>
       </c>
@@ -62382,12 +62327,6 @@
       <c r="I104" t="s">
         <v>1882</v>
       </c>
-      <c r="J104" t="s">
-        <v>151</v>
-      </c>
-      <c r="K104" t="s">
-        <v>1102</v>
-      </c>
       <c r="L104" t="s">
         <v>1333</v>
       </c>
@@ -62439,12 +62378,6 @@
       <c r="I105" t="s">
         <v>1882</v>
       </c>
-      <c r="J105" t="s">
-        <v>151</v>
-      </c>
-      <c r="K105" t="s">
-        <v>1102</v>
-      </c>
       <c r="L105" t="s">
         <v>1333</v>
       </c>
@@ -62496,12 +62429,6 @@
       <c r="I106" t="s">
         <v>1882</v>
       </c>
-      <c r="J106" t="s">
-        <v>151</v>
-      </c>
-      <c r="K106" t="s">
-        <v>1102</v>
-      </c>
       <c r="L106" t="s">
         <v>1333</v>
       </c>
@@ -62552,12 +62479,6 @@
       </c>
       <c r="I107" t="s">
         <v>1882</v>
-      </c>
-      <c r="J107" t="s">
-        <v>151</v>
-      </c>
-      <c r="K107" t="s">
-        <v>1102</v>
       </c>
       <c r="L107" t="s">
         <v>1333</v>
@@ -62607,12 +62528,8 @@
       <c r="I109" s="30" t="s">
         <v>1762</v>
       </c>
-      <c r="J109" t="s">
-        <v>151</v>
-      </c>
-      <c r="K109" t="s">
-        <v>1102</v>
-      </c>
+      <c r="J109"/>
+      <c r="K109"/>
       <c r="L109" t="s">
         <v>1333</v>
       </c>
@@ -62656,12 +62573,8 @@
       <c r="I110" s="30" t="s">
         <v>1762</v>
       </c>
-      <c r="J110" t="s">
-        <v>151</v>
-      </c>
-      <c r="K110" t="s">
-        <v>1102</v>
-      </c>
+      <c r="J110"/>
+      <c r="K110"/>
       <c r="L110" t="s">
         <v>1333</v>
       </c>
@@ -62711,12 +62624,6 @@
       <c r="G112" t="s">
         <v>974</v>
       </c>
-      <c r="J112" t="s">
-        <v>151</v>
-      </c>
-      <c r="K112" t="s">
-        <v>1102</v>
-      </c>
       <c r="L112" t="s">
         <v>1333</v>
       </c>
@@ -62775,12 +62682,6 @@
       <c r="H114" t="s">
         <v>1654</v>
       </c>
-      <c r="J114" t="s">
-        <v>151</v>
-      </c>
-      <c r="K114" t="s">
-        <v>1102</v>
-      </c>
       <c r="L114" t="s">
         <v>1333</v>
       </c>
@@ -62823,12 +62724,6 @@
       <c r="H115" t="s">
         <v>1653</v>
       </c>
-      <c r="J115" t="s">
-        <v>151</v>
-      </c>
-      <c r="K115" t="s">
-        <v>1102</v>
-      </c>
       <c r="L115" t="s">
         <v>1333</v>
       </c>
@@ -62870,12 +62765,6 @@
       </c>
       <c r="H116" t="s">
         <v>1652</v>
-      </c>
-      <c r="J116" t="s">
-        <v>151</v>
-      </c>
-      <c r="K116" t="s">
-        <v>1102</v>
       </c>
       <c r="L116" t="s">
         <v>1333</v>
@@ -62919,12 +62808,6 @@
       <c r="G118" t="s">
         <v>974</v>
       </c>
-      <c r="J118" t="s">
-        <v>151</v>
-      </c>
-      <c r="K118" t="s">
-        <v>1102</v>
-      </c>
       <c r="M118" t="s">
         <v>1667</v>
       </c>
@@ -62966,12 +62849,6 @@
       </c>
       <c r="G119" t="s">
         <v>974</v>
-      </c>
-      <c r="J119" t="s">
-        <v>151</v>
-      </c>
-      <c r="K119" t="s">
-        <v>1102</v>
       </c>
       <c r="M119" t="s">
         <v>1667</v>
@@ -63021,9 +62898,6 @@
       <c r="G121" t="s">
         <v>974</v>
       </c>
-      <c r="J121" t="s">
-        <v>151</v>
-      </c>
       <c r="K121" t="s">
         <v>1124</v>
       </c>
@@ -63069,9 +62943,6 @@
       <c r="G122" t="s">
         <v>974</v>
       </c>
-      <c r="J122" t="s">
-        <v>151</v>
-      </c>
       <c r="K122" t="s">
         <v>1124</v>
       </c>
@@ -63116,9 +62987,6 @@
       </c>
       <c r="G123" t="s">
         <v>974</v>
-      </c>
-      <c r="J123" t="s">
-        <v>151</v>
       </c>
       <c r="K123" t="s">
         <v>1124</v>
@@ -63173,12 +63041,6 @@
       </c>
       <c r="I125" t="s">
         <v>1881</v>
-      </c>
-      <c r="J125" t="s">
-        <v>151</v>
-      </c>
-      <c r="K125" t="s">
-        <v>1102</v>
       </c>
       <c r="O125" t="s">
         <v>1053</v>
@@ -63208,7 +63070,163 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3BE894F-42DE-5B49-8310-51E399280776}">
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.1640625" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="30" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>1042</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>1989</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>1988</v>
+      </c>
+      <c r="L1" s="30" t="s">
+        <v>1990</v>
+      </c>
+      <c r="M1" s="30" t="s">
+        <v>1918</v>
+      </c>
+      <c r="N1" s="30" t="s">
+        <v>1866</v>
+      </c>
+      <c r="O1" s="30" t="s">
+        <v>1849</v>
+      </c>
+      <c r="P1" s="29" t="s">
+        <v>1753</v>
+      </c>
+      <c r="Q1" s="29" t="s">
+        <v>1752</v>
+      </c>
+      <c r="R1" s="29" t="s">
+        <v>1939</v>
+      </c>
+      <c r="S1" s="29" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T1" s="29" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U1" s="29" t="s">
+        <v>1751</v>
+      </c>
+      <c r="V1" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="W1" s="29" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <f>IF(E2&lt;&gt;"",VLOOKUP(E2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Environmental conditions and measurements</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" t="s">
+        <v>974</v>
+      </c>
+      <c r="J2" t="s">
+        <v>151</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="O2" t="s">
+        <v>976</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52CAD1A-92FF-3346-8108-2C4AA07D2B2C}">
   <dimension ref="A1:AD42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -64694,7 +64712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A11C28-487C-5043-9CF2-96D54102B26B}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -64955,396 +64973,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55BEACBA-EA3F-A149-88D0-2C7A38DAFA93}">
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="8" max="8" width="12" style="41" customWidth="1"/>
-    <col min="9" max="9" width="10.1640625" style="41" customWidth="1"/>
-    <col min="10" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="7.5" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="32.5" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
-        <v>1443</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>1772</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>1801</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="29" t="s">
-        <v>1779</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="29" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECCAEF06-3FE8-3D4D-A58A-7FC91FF23CF7}">
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="15.5" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="28.33203125" customWidth="1"/>
-    <col min="9" max="9" width="38.1640625" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>1883</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>1042</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>1749</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B2" t="str">
-        <f>IF(D2&lt;&gt;"",VLOOKUP(D2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>1193</v>
-      </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="28" t="s">
-        <v>1203</v>
-      </c>
-      <c r="J2" s="29"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B3" t="str">
-        <f>IF(D3&lt;&gt;"",VLOOKUP(D3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>1193</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="28" t="s">
-        <v>1204</v>
-      </c>
-      <c r="J3" s="29"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B4" t="e">
-        <f>IF(D4&lt;&gt;"",VLOOKUP(D4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="28" t="s">
-        <v>1205</v>
-      </c>
-      <c r="J4" s="29"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" t="str">
-        <f>IF(D5&lt;&gt;"",VLOOKUP(D5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>1195</v>
-      </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="28" t="s">
-        <v>1206</v>
-      </c>
-      <c r="J5" s="29"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B6" t="str">
-        <f>IF(D6&lt;&gt;"",VLOOKUP(D6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>1196</v>
-      </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="28" t="s">
-        <v>1207</v>
-      </c>
-      <c r="J6" s="29"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" t="str">
-        <f>IF(D7&lt;&gt;"",VLOOKUP(D7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>1197</v>
-      </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="28" t="s">
-        <v>1208</v>
-      </c>
-      <c r="J7" s="29"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B8" t="str">
-        <f>IF(D8&lt;&gt;"",VLOOKUP(D8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>1198</v>
-      </c>
-      <c r="H8" s="29"/>
-      <c r="I8" s="28" t="s">
-        <v>1209</v>
-      </c>
-      <c r="J8" s="29"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B9" t="str">
-        <f>IF(D9&lt;&gt;"",VLOOKUP(D9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>1199</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>1764</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>1210</v>
-      </c>
-      <c r="J9" s="29"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B10" t="str">
-        <f>IF(D10&lt;&gt;"",VLOOKUP(D10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>1200</v>
-      </c>
-      <c r="H10" s="29"/>
-      <c r="I10" s="28" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J10" s="29"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B11" t="str">
-        <f>IF(D11&lt;&gt;"",VLOOKUP(D11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>1202</v>
-      </c>
-      <c r="H11" s="29"/>
-      <c r="I11" s="28" t="s">
-        <v>1212</v>
-      </c>
-      <c r="J11" s="29"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B12" t="str">
-        <f>IF(D12&lt;&gt;"",VLOOKUP(D12,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Database identifiers</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>1869</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>1890</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>1201</v>
-      </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="28" t="s">
-        <v>1213</v>
-      </c>
-      <c r="J12" s="29"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B93460-2AAF-184D-90E5-3DC96730B86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2059E499-1196-2945-ABF6-C0E11981D210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="40720" windowHeight="20600" firstSheet="8" activeTab="10" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="40720" windowHeight="20600" firstSheet="7" activeTab="14" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="accessions_maps" sheetId="12" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9227" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9237" uniqueCount="2093">
   <si>
     <t>Complete</t>
   </si>
@@ -6757,7 +6757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6911,19 +6911,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -30250,10 +30237,10 @@
       <c r="G85" t="s">
         <v>958</v>
       </c>
-      <c r="K85" s="78" t="s">
+      <c r="K85" t="s">
         <v>1115</v>
       </c>
-      <c r="L85" s="78" t="s">
+      <c r="L85" t="s">
         <v>1115</v>
       </c>
       <c r="O85" t="s">
@@ -30307,10 +30294,10 @@
       <c r="G86" t="s">
         <v>958</v>
       </c>
-      <c r="K86" s="78" t="s">
+      <c r="K86" t="s">
         <v>1115</v>
       </c>
-      <c r="L86" s="78" t="s">
+      <c r="L86" t="s">
         <v>1115</v>
       </c>
       <c r="O86" t="s">
@@ -30364,10 +30351,10 @@
       <c r="G87" t="s">
         <v>958</v>
       </c>
-      <c r="K87" s="78" t="s">
+      <c r="K87" t="s">
         <v>1115</v>
       </c>
-      <c r="L87" s="78" t="s">
+      <c r="L87" t="s">
         <v>1115</v>
       </c>
       <c r="O87" t="s">
@@ -32797,17 +32784,18 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0435B3-2676-7B49-A30C-B02B45DA7889}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" customWidth="1"/>
+    <col min="12" max="12" width="29.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>1721</v>
       </c>
@@ -32838,11 +32826,14 @@
       <c r="J1" s="18" t="s">
         <v>1806</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="K1" s="18" t="s">
+        <v>1791</v>
+      </c>
+      <c r="L1" s="25" t="s">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B2" t="b">
         <v>1</v>
       </c>
@@ -32865,10 +32856,17 @@
       <c r="K2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B3" t="b">
         <v>1</v>
+      </c>
+      <c r="C3" t="str">
+        <f>IF(E3&lt;&gt;"",VLOOKUP(E3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
       </c>
       <c r="D3" t="s">
         <v>1809</v>
@@ -32885,10 +32883,17 @@
       <c r="K3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" t="b">
         <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <f>IF(E4&lt;&gt;"",VLOOKUP(E4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sequence information</v>
       </c>
       <c r="D4" t="s">
         <v>1809</v>
@@ -32905,10 +32910,17 @@
       <c r="K4" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L4" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5" t="b">
         <v>1</v>
+      </c>
+      <c r="C5" t="str">
+        <f>IF(E5&lt;&gt;"",VLOOKUP(E5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Strain and isolation information</v>
       </c>
       <c r="D5" t="s">
         <v>1809</v>
@@ -32923,6 +32935,9 @@
         <v>1476</v>
       </c>
       <c r="K5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="L5" t="s">
         <v>1107</v>
       </c>
     </row>
@@ -33186,446 +33201,444 @@
   <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="82" customWidth="1"/>
-    <col min="2" max="6" width="25.33203125" style="82"/>
-    <col min="7" max="7" width="44" style="82" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="25.33203125" style="82"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="84" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>1411</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="24" t="s">
         <v>1721</v>
       </c>
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="83" t="s">
+      <c r="E1" s="24" t="s">
         <v>1821</v>
       </c>
-      <c r="F1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="83" t="s">
+      <c r="F1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="83" t="s">
+      <c r="H1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="83" t="s">
+      <c r="I1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="83" t="s">
+      <c r="J1" s="24" t="s">
         <v>1742</v>
       </c>
-      <c r="K1" s="83" t="s">
+      <c r="K1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="83" t="s">
+      <c r="L1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="83" t="s">
+      <c r="M1" s="24" t="s">
         <v>1728</v>
       </c>
-      <c r="N1" s="83" t="s">
+      <c r="N1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="83" t="s">
+      <c r="O1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="83" t="s">
+      <c r="P1" s="24" t="s">
         <v>1719</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="81">
+      <c r="A2" s="23">
         <v>3</v>
       </c>
-      <c r="B2" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="81" t="s">
+      <c r="B2" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>1121</v>
       </c>
-      <c r="E2" s="82" t="str">
+      <c r="E2" t="str">
         <f>IF(G2&lt;&gt;"",VLOOKUP(G2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>AMR detection information</v>
       </c>
-      <c r="F2" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G2" s="81" t="s">
+      <c r="F2" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G2" s="23" t="s">
         <v>1123</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81" t="s">
+      <c r="J2" s="23"/>
+      <c r="K2" s="23" t="s">
         <v>1564</v>
       </c>
-      <c r="L2" s="81" t="s">
+      <c r="L2" s="23" t="s">
         <v>1693</v>
       </c>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81" t="s">
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23" t="s">
         <v>1565</v>
       </c>
-      <c r="P2" s="81" t="s">
+      <c r="P2" s="23" t="s">
         <v>1720</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="81">
+      <c r="A3" s="23">
         <v>10</v>
       </c>
-      <c r="B3" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="81" t="s">
+      <c r="B3" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="82" t="str">
+      <c r="E3" t="str">
         <f>IF(G3&lt;&gt;"",VLOOKUP(G3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F3" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G3" s="81" t="s">
+      <c r="F3" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="81" t="s">
+      <c r="H3" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81" t="s">
+      <c r="J3" s="23"/>
+      <c r="K3" s="23" t="s">
         <v>1564</v>
       </c>
-      <c r="L3" s="81" t="s">
+      <c r="L3" s="23" t="s">
         <v>1697</v>
       </c>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81" t="s">
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23" t="s">
         <v>1573</v>
       </c>
-      <c r="P3" s="81"/>
+      <c r="P3" s="23"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="81">
+      <c r="A4" s="23">
         <v>46</v>
       </c>
-      <c r="B4" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="81" t="s">
+      <c r="B4" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="82" t="str">
+      <c r="E4" t="str">
         <f>IF(G4&lt;&gt;"",VLOOKUP(G4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F4" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G4" s="81" t="s">
+      <c r="F4" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="H4" s="81" t="s">
+      <c r="H4" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I4" s="81" t="s">
+      <c r="I4" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81" t="s">
+      <c r="J4" s="23"/>
+      <c r="K4" s="23" t="s">
         <v>1564</v>
       </c>
-      <c r="L4" s="81" t="s">
+      <c r="L4" s="23" t="s">
         <v>1679</v>
       </c>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="81" t="s">
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23" t="s">
         <v>1580</v>
       </c>
-      <c r="P4" s="81"/>
+      <c r="P4" s="23"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="81">
+      <c r="A5" s="23">
         <v>227</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="81" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>1127</v>
       </c>
-      <c r="E5" s="82" t="str">
+      <c r="E5" t="str">
         <f>IF(G5&lt;&gt;"",VLOOKUP(G5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Lineage/clade information</v>
       </c>
-      <c r="F5" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G5" s="81" t="s">
+      <c r="F5" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G5" s="23" t="s">
         <v>1130</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I5" s="81" t="s">
+      <c r="I5" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81" t="s">
+      <c r="J5" s="23"/>
+      <c r="K5" s="23" t="s">
         <v>1564</v>
       </c>
-      <c r="L5" s="81" t="s">
+      <c r="L5" s="23" t="s">
         <v>1680</v>
       </c>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81" t="s">
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23" t="s">
         <v>1582</v>
       </c>
-      <c r="P5" s="81" t="s">
+      <c r="P5" s="23" t="s">
         <v>1729</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="81">
+      <c r="A6" s="23">
         <v>330</v>
       </c>
-      <c r="B6" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81" t="s">
+      <c r="B6" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="E6" s="82" t="e">
+      <c r="E6" t="e">
         <f>IF(G6&lt;&gt;"",VLOOKUP(G6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="F6" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G6" s="81" t="s">
+      <c r="F6" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G6" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="H6" s="81" t="s">
+      <c r="H6" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I6" s="81" t="s">
+      <c r="I6" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81" t="s">
+      <c r="J6" s="23"/>
+      <c r="K6" s="23" t="s">
         <v>1486</v>
       </c>
-      <c r="L6" s="81" t="s">
+      <c r="L6" s="23" t="s">
         <v>1592</v>
       </c>
-      <c r="M6" s="81"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="81" t="s">
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23" t="s">
         <v>1591</v>
       </c>
-      <c r="P6" s="81"/>
+      <c r="P6" s="23"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="81">
+      <c r="A7" s="23">
         <v>331</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="81" t="s">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="82" t="str">
+      <c r="E7" t="str">
         <f>IF(G7&lt;&gt;"",VLOOKUP(G7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="F7" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G7" s="81" t="s">
+      <c r="F7" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>1100</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I7" s="81" t="s">
+      <c r="I7" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81" t="s">
+      <c r="J7" s="23"/>
+      <c r="K7" s="23" t="s">
         <v>1486</v>
       </c>
-      <c r="L7" s="81" t="s">
+      <c r="L7" s="23" t="s">
         <v>1595</v>
       </c>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="81" t="s">
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23" t="s">
         <v>1596</v>
       </c>
-      <c r="P7" s="81" t="s">
+      <c r="P7" s="23" t="s">
         <v>1732</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="81">
+      <c r="A8" s="23">
         <v>659</v>
       </c>
-      <c r="B8" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="81" t="s">
+      <c r="B8" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="82" t="str">
+      <c r="E8" t="str">
         <f>IF(G8&lt;&gt;"",VLOOKUP(G8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="F8" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G8" s="85" t="s">
+      <c r="F8" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G8" s="77" t="s">
         <v>1839</v>
       </c>
-      <c r="H8" s="86" t="s">
+      <c r="H8" s="40" t="s">
         <v>442</v>
       </c>
-      <c r="I8" s="81" t="s">
+      <c r="I8" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81" t="s">
+      <c r="J8" s="23"/>
+      <c r="K8" s="23" t="s">
         <v>1486</v>
       </c>
-      <c r="L8" s="81" t="s">
+      <c r="L8" s="23" t="s">
         <v>1308</v>
       </c>
-      <c r="M8" s="81"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81" t="s">
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23" t="s">
         <v>1604</v>
       </c>
-      <c r="P8" s="81"/>
+      <c r="P8" s="23"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" s="81">
+      <c r="A9" s="23">
         <v>717</v>
       </c>
-      <c r="B9" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="81" t="s">
+      <c r="B9" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="82" t="str">
+      <c r="E9" t="str">
         <f>IF(G9&lt;&gt;"",VLOOKUP(G9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="F9" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G9" s="81" t="s">
+      <c r="F9" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="H9" s="81" t="s">
+      <c r="H9" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I9" s="81" t="s">
+      <c r="I9" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81" t="s">
+      <c r="J9" s="23"/>
+      <c r="K9" s="23" t="s">
         <v>1486</v>
       </c>
-      <c r="L9" s="81" t="s">
+      <c r="L9" s="23" t="s">
         <v>1485</v>
       </c>
-      <c r="M9" s="81"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="81" t="s">
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23" t="s">
         <v>1484</v>
       </c>
-      <c r="P9" s="81"/>
+      <c r="P9" s="23"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" s="81">
+      <c r="A10" s="23">
         <v>846</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" s="81" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="23" t="s">
         <v>1118</v>
       </c>
-      <c r="E10" s="82" t="str">
+      <c r="E10" t="str">
         <f>IF(G10&lt;&gt;"",VLOOKUP(G10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Taxonomic identification information</v>
       </c>
-      <c r="F10" s="81" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G10" s="81" t="s">
+      <c r="F10" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="81" t="s">
+      <c r="H10" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I10" s="81" t="s">
+      <c r="I10" s="23" t="s">
         <v>1237</v>
       </c>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81" t="s">
+      <c r="J10" s="23"/>
+      <c r="K10" s="23" t="s">
         <v>1564</v>
       </c>
-      <c r="L10" s="81" t="s">
+      <c r="L10" s="23" t="s">
         <v>1650</v>
       </c>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81" t="s">
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23" t="s">
         <v>1649</v>
       </c>
-      <c r="P10" s="81"/>
+      <c r="P10" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -49142,554 +49155,551 @@
   <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="80" customWidth="1"/>
-    <col min="2" max="2" width="15" style="80" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="80" customWidth="1"/>
-    <col min="4" max="5" width="26.1640625" style="80" customWidth="1"/>
-    <col min="6" max="6" width="13" style="80" customWidth="1"/>
-    <col min="7" max="7" width="25" style="80" customWidth="1"/>
-    <col min="8" max="8" width="34.5" style="80" customWidth="1"/>
-    <col min="9" max="9" width="13" style="80" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" style="80" customWidth="1"/>
-    <col min="11" max="11" width="10.5" style="80" customWidth="1"/>
-    <col min="12" max="13" width="20.83203125" style="80" customWidth="1"/>
-    <col min="14" max="14" width="7.5" style="80" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" style="80" customWidth="1"/>
-    <col min="16" max="16" width="62.33203125" style="80" customWidth="1"/>
-    <col min="17" max="17" width="13" style="80" customWidth="1"/>
-    <col min="18" max="16384" width="10.83203125" style="80"/>
+    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="4" max="5" width="26.1640625" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="34.5" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" customWidth="1"/>
+    <col min="11" max="11" width="10.5" customWidth="1"/>
+    <col min="12" max="13" width="20.83203125" customWidth="1"/>
+    <col min="14" max="14" width="7.5" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" customWidth="1"/>
+    <col min="16" max="16" width="62.33203125" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="84" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:17" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>1411</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="24" t="s">
         <v>1721</v>
       </c>
-      <c r="C1" s="83" t="s">
+      <c r="C1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="83" t="s">
+      <c r="E1" s="24" t="s">
         <v>1821</v>
       </c>
-      <c r="F1" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="83" t="s">
+      <c r="F1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="83" t="s">
+      <c r="H1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="83" t="s">
+      <c r="I1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="83" t="s">
+      <c r="J1" s="24" t="s">
         <v>1742</v>
       </c>
-      <c r="K1" s="83" t="s">
+      <c r="K1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="83" t="s">
+      <c r="L1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="83" t="s">
+      <c r="M1" s="24" t="s">
         <v>1780</v>
       </c>
-      <c r="N1" s="83" t="s">
+      <c r="N1" s="24" t="s">
         <v>1728</v>
       </c>
-      <c r="O1" s="83" t="s">
+      <c r="O1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="83" t="s">
+      <c r="P1" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="83" t="s">
+      <c r="Q1" s="24" t="s">
         <v>1719</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="79">
+      <c r="A2" s="23">
         <v>25</v>
       </c>
-      <c r="B2" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="79" t="s">
+      <c r="B2" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="80" t="str">
+      <c r="E2" t="str">
         <f>IF(G2&lt;&gt;"",VLOOKUP(G2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F2" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G2" s="79" t="s">
+      <c r="F2" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G2" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="I2" s="79" t="s">
+      <c r="I2" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79" t="s">
+      <c r="J2" s="23"/>
+      <c r="K2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="79" t="s">
+      <c r="L2" s="23" t="s">
         <v>1274</v>
       </c>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79" t="s">
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q2" s="79" t="s">
+      <c r="Q2" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="79">
+      <c r="A3" s="23">
         <v>32</v>
       </c>
-      <c r="B3" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="79" t="s">
+      <c r="B3" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="80" t="str">
+      <c r="E3" t="str">
         <f>IF(G3&lt;&gt;"",VLOOKUP(G3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F3" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G3" s="79" t="s">
+      <c r="F3" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="23" t="s">
         <v>2075</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79" t="s">
+      <c r="J3" s="23"/>
+      <c r="K3" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L3" s="79" t="s">
+      <c r="L3" s="23" t="s">
         <v>1262</v>
       </c>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="79" t="s">
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q3" s="79" t="s">
+      <c r="Q3" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="79">
+      <c r="A4" s="23">
         <v>33</v>
       </c>
-      <c r="B4" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="79" t="s">
+      <c r="B4" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="80" t="str">
+      <c r="E4" t="str">
         <f>IF(G4&lt;&gt;"",VLOOKUP(G4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F4" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G4" s="79" t="s">
+      <c r="F4" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="23" t="s">
         <v>2076</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79" t="s">
+      <c r="J4" s="23"/>
+      <c r="K4" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L4" s="79" t="s">
+      <c r="L4" s="23" t="s">
         <v>1263</v>
       </c>
-      <c r="M4" s="79"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79" t="s">
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q4" s="79" t="s">
+      <c r="Q4" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="79">
+      <c r="A5" s="23">
         <v>34</v>
       </c>
-      <c r="B5" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C5" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="79" t="s">
+      <c r="B5" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="80" t="str">
+      <c r="E5" t="str">
         <f>IF(G5&lt;&gt;"",VLOOKUP(G5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F5" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G5" s="79" t="s">
+      <c r="F5" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G5" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="H5" s="23" t="s">
         <v>2077</v>
       </c>
-      <c r="I5" s="79" t="s">
+      <c r="I5" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79" t="s">
+      <c r="J5" s="23"/>
+      <c r="K5" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="23" t="s">
         <v>1264</v>
       </c>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79" t="s">
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q5" s="79" t="s">
+      <c r="Q5" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="79">
+      <c r="A6" s="23">
         <v>35</v>
       </c>
-      <c r="B6" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="79" t="s">
+      <c r="B6" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="80" t="str">
+      <c r="E6" t="str">
         <f>IF(G6&lt;&gt;"",VLOOKUP(G6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F6" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G6" s="79" t="s">
+      <c r="F6" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G6" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="23" t="s">
         <v>2078</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79" t="s">
+      <c r="J6" s="23"/>
+      <c r="K6" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="23" t="s">
         <v>1265</v>
       </c>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79" t="s">
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q6" s="79" t="s">
+      <c r="Q6" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="79">
+      <c r="A7" s="23">
         <v>36</v>
       </c>
-      <c r="B7" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="79" t="s">
+      <c r="B7" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="80" t="str">
+      <c r="E7" t="str">
         <f>IF(G7&lt;&gt;"",VLOOKUP(G7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F7" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G7" s="79" t="s">
+      <c r="F7" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="79" t="s">
+      <c r="H7" s="23" t="s">
         <v>2079</v>
       </c>
-      <c r="I7" s="79" t="s">
+      <c r="I7" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79" t="s">
+      <c r="J7" s="23"/>
+      <c r="K7" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L7" s="79" t="s">
+      <c r="L7" s="23" t="s">
         <v>1266</v>
       </c>
-      <c r="M7" s="79"/>
-      <c r="N7" s="79"/>
-      <c r="O7" s="79"/>
-      <c r="P7" s="79" t="s">
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q7" s="79" t="s">
+      <c r="Q7" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="79">
+      <c r="A8" s="23">
         <v>37</v>
       </c>
-      <c r="B8" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="79" t="s">
+      <c r="B8" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="80" t="str">
+      <c r="E8" t="str">
         <f>IF(G8&lt;&gt;"",VLOOKUP(G8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F8" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G8" s="79" t="s">
+      <c r="F8" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="79" t="s">
+      <c r="H8" s="23" t="s">
         <v>2080</v>
       </c>
-      <c r="I8" s="79" t="s">
+      <c r="I8" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79" t="s">
+      <c r="J8" s="23"/>
+      <c r="K8" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L8" s="79" t="s">
+      <c r="L8" s="23" t="s">
         <v>1267</v>
       </c>
-      <c r="M8" s="79"/>
-      <c r="N8" s="79"/>
-      <c r="O8" s="79"/>
-      <c r="P8" s="79" t="s">
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q8" s="79" t="s">
+      <c r="Q8" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="79">
+      <c r="A9" s="23">
         <v>38</v>
       </c>
-      <c r="B9" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="79" t="s">
+      <c r="B9" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="80" t="str">
+      <c r="E9" t="str">
         <f>IF(G9&lt;&gt;"",VLOOKUP(G9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F9" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G9" s="79" t="s">
+      <c r="F9" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="79" t="s">
+      <c r="H9" s="23" t="s">
         <v>2081</v>
       </c>
-      <c r="I9" s="79" t="s">
+      <c r="I9" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79" t="s">
+      <c r="J9" s="23"/>
+      <c r="K9" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L9" s="79" t="s">
+      <c r="L9" s="23" t="s">
         <v>1268</v>
       </c>
-      <c r="M9" s="79"/>
-      <c r="N9" s="79"/>
-      <c r="O9" s="79"/>
-      <c r="P9" s="79" t="s">
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q9" s="79" t="s">
+      <c r="Q9" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="79">
+      <c r="A10" s="23">
         <v>39</v>
       </c>
-      <c r="B10" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" s="79" t="s">
+      <c r="B10" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="80" t="str">
+      <c r="E10" t="str">
         <f>IF(G10&lt;&gt;"",VLOOKUP(G10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="F10" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="G10" s="79" t="s">
+      <c r="F10" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="79" t="s">
+      <c r="H10" s="23" t="s">
         <v>2082</v>
       </c>
-      <c r="I10" s="79" t="s">
+      <c r="I10" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79" t="s">
+      <c r="J10" s="23"/>
+      <c r="K10" s="23" t="s">
         <v>1260</v>
       </c>
-      <c r="L10" s="79" t="s">
+      <c r="L10" s="23" t="s">
         <v>1269</v>
       </c>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79" t="s">
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23" t="s">
         <v>1270</v>
       </c>
-      <c r="Q10" s="79" t="s">
+      <c r="Q10" s="23" t="s">
         <v>1723</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="D11" s="79"/>
-      <c r="E11" s="80" t="str">
+      <c r="D11" s="23"/>
+      <c r="E11" t="str">
         <f>IF(G11&lt;&gt;"",VLOOKUP(G11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="K11" s="79" t="s">
+      <c r="K11" s="23" t="s">
         <v>1978</v>
       </c>
-      <c r="L11" s="79" t="s">
+      <c r="L11" s="23" t="s">
         <v>1979</v>
       </c>
-      <c r="M11" s="79"/>
+      <c r="M11" s="23"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B12" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="80" t="str">
+      <c r="B12" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" t="str">
         <f>IF(G12&lt;&gt;"",VLOOKUP(G12,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F12" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="I12" s="79" t="s">
+      <c r="F12" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I12" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="K12" s="79" t="s">
+      <c r="K12" s="23" t="s">
         <v>2092</v>
       </c>
-      <c r="L12"/>
-      <c r="M12" s="79" t="s">
+      <c r="M12" s="23" t="s">
         <v>2091</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="C13" s="79" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="80" t="str">
+      <c r="B13" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" t="str">
         <f>IF(G13&lt;&gt;"",VLOOKUP(G13,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F13" s="79" t="s">
-        <v>1809</v>
-      </c>
-      <c r="I13" s="79" t="s">
+      <c r="F13" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I13" s="23" t="s">
         <v>1261</v>
       </c>
-      <c r="K13" s="79" t="s">
+      <c r="K13" s="23" t="s">
         <v>2059</v>
       </c>
-      <c r="L13"/>
-      <c r="M13" s="79" t="s">
+      <c r="M13" s="23" t="s">
         <v>2087</v>
       </c>
     </row>
@@ -55931,7 +55941,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="78" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B68" s="23" t="b">
         <v>1</v>
       </c>
@@ -55947,11 +55957,11 @@
       <c r="K68" s="23" t="s">
         <v>2055</v>
       </c>
-      <c r="M68" s="78" t="s">
+      <c r="M68" t="s">
         <v>2087</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="78" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B69" s="23" t="b">
         <v>1</v>
       </c>
@@ -55967,7 +55977,7 @@
       <c r="K69" s="23" t="s">
         <v>2058</v>
       </c>
-      <c r="M69" s="78" t="s">
+      <c r="M69" t="s">
         <v>2087</v>
       </c>
     </row>
@@ -62314,7 +62324,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903503FA-19AE-C146-9865-7A1697985DDA}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.83203125" bestFit="1" customWidth="1"/>
@@ -62326,12 +62336,13 @@
     <col min="8" max="8" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="23.1640625" customWidth="1"/>
     <col min="11" max="11" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" customWidth="1"/>
-    <col min="13" max="13" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+    <col min="12" max="12" width="32.33203125" customWidth="1"/>
+    <col min="13" max="13" width="19" customWidth="1"/>
+    <col min="14" max="14" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="25" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -62366,16 +62377,19 @@
         <v>1803</v>
       </c>
       <c r="L1" s="18" t="s">
+        <v>1791</v>
+      </c>
+      <c r="M1" s="18" t="s">
         <v>1804</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="N1" s="18" t="s">
         <v>1805</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="O1" s="18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
         <f>IF(D2&lt;&gt;"",VLOOKUP(D2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
@@ -62384,7 +62398,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="320" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="320" x14ac:dyDescent="0.2">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -62413,14 +62427,17 @@
       <c r="K3" t="s">
         <v>1305</v>
       </c>
-      <c r="L3" s="38" t="s">
+      <c r="L3" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3" s="38" t="s">
         <v>1876</v>
       </c>
-      <c r="M3" s="38" t="s">
+      <c r="N3" s="38" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="b">
         <v>1</v>
       </c>
@@ -62449,8 +62466,11 @@
       <c r="K4" t="s">
         <v>1474</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="304" x14ac:dyDescent="0.2">
+      <c r="L4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="304" x14ac:dyDescent="0.2">
       <c r="A5" t="b">
         <v>1</v>
       </c>
@@ -62479,14 +62499,17 @@
       <c r="K5" t="s">
         <v>1479</v>
       </c>
-      <c r="L5" s="38" t="s">
+      <c r="L5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="M5" s="38" t="s">
         <v>1878</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="N5" s="38" t="s">
         <v>1879</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="304" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="304" x14ac:dyDescent="0.2">
       <c r="A6" t="b">
         <v>1</v>
       </c>
@@ -62515,10 +62538,13 @@
       <c r="K6" t="s">
         <v>1478</v>
       </c>
-      <c r="L6" s="38" t="s">
+      <c r="L6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="M6" s="38" t="s">
         <v>1880</v>
       </c>
-      <c r="M6" s="38" t="s">
+      <c r="N6" s="38" t="s">
         <v>1881</v>
       </c>
     </row>

--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2059E499-1196-2945-ABF6-C0E11981D210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E013D3E-3AD5-6340-A899-4B406D44141F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="40720" windowHeight="20600" firstSheet="7" activeTab="14" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="40720" windowHeight="20600" firstSheet="11" activeTab="20" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="accessions_maps" sheetId="12" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9237" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9241" uniqueCount="2093">
   <si>
     <t>Complete</t>
   </si>
@@ -49152,7 +49152,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B0FFD5-92F3-FD4F-93FB-9D30DA340366}">
   <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -49700,6 +49700,31 @@
         <v>2059</v>
       </c>
       <c r="M13" s="23" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B14" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" t="str">
+        <f>IF(G14&lt;&gt;"",VLOOKUP(G14,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>1261</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>2044</v>
+      </c>
+      <c r="M14" s="23" t="s">
         <v>2087</v>
       </c>
     </row>

--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363CEB8E-614E-244F-A6B8-F79EC44FB5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBC2099-3C9C-2D4B-9593-D5444C5C86CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="40800" windowHeight="20740" firstSheet="13" activeTab="16" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="40800" windowHeight="20740" activeTab="3" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="accessions_maps" sheetId="12" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9398" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9398" uniqueCount="2090">
   <si>
     <t>Complete</t>
   </si>
@@ -6412,6 +6412,9 @@
   </si>
   <si>
     <t>blank</t>
+  </si>
+  <si>
+    <t>notes_value_UNUSED</t>
   </si>
 </sst>
 </file>
@@ -6746,7 +6749,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6900,15 +6903,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -32825,7 +32822,7 @@
         <v>1806</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>1791</v>
+        <v>2089</v>
       </c>
       <c r="L1" s="24" t="s">
         <v>2032</v>
@@ -33207,7 +33204,7 @@
     <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="46.6640625" customWidth="1"/>
     <col min="10" max="10" width="54.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" style="78" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="54.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -33242,7 +33239,7 @@
       <c r="J1" s="24" t="s">
         <v>2084</v>
       </c>
-      <c r="K1" s="77" t="s">
+      <c r="K1" s="24" t="s">
         <v>1784</v>
       </c>
       <c r="L1" s="24" t="s">
@@ -33272,7 +33269,7 @@
       <c r="J2" t="s">
         <v>124</v>
       </c>
-      <c r="K2" s="78" t="s">
+      <c r="K2" t="s">
         <v>2081</v>
       </c>
       <c r="L2" t="s">
@@ -33299,7 +33296,7 @@
       <c r="J3" t="s">
         <v>1991</v>
       </c>
-      <c r="K3" s="78" t="s">
+      <c r="K3" t="s">
         <v>2081</v>
       </c>
       <c r="L3" t="s">
@@ -33326,7 +33323,7 @@
       <c r="J4" t="s">
         <v>1992</v>
       </c>
-      <c r="K4" s="78" t="s">
+      <c r="K4" t="s">
         <v>2081</v>
       </c>
       <c r="L4" t="s">
@@ -33353,7 +33350,7 @@
       <c r="J5" t="s">
         <v>1993</v>
       </c>
-      <c r="K5" s="78" t="s">
+      <c r="K5" t="s">
         <v>2081</v>
       </c>
       <c r="L5" t="s">
@@ -33380,7 +33377,7 @@
       <c r="J6" t="s">
         <v>84</v>
       </c>
-      <c r="K6" s="78" t="s">
+      <c r="K6" t="s">
         <v>2081</v>
       </c>
       <c r="L6" t="s">
@@ -33407,7 +33404,7 @@
       <c r="J7" t="s">
         <v>128</v>
       </c>
-      <c r="K7" s="78" t="s">
+      <c r="K7" t="s">
         <v>2081</v>
       </c>
       <c r="L7" t="s">
@@ -33434,7 +33431,7 @@
       <c r="J8" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="78" t="s">
+      <c r="K8" t="s">
         <v>2081</v>
       </c>
       <c r="L8" t="s">
@@ -33461,7 +33458,7 @@
       <c r="J9" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="78" t="s">
+      <c r="K9" t="s">
         <v>2081</v>
       </c>
       <c r="L9" t="s">
@@ -33488,7 +33485,7 @@
       <c r="J10" t="s">
         <v>18</v>
       </c>
-      <c r="K10" s="78" t="s">
+      <c r="K10" t="s">
         <v>2081</v>
       </c>
       <c r="L10" t="s">
@@ -33515,7 +33512,7 @@
       <c r="J11" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="78" t="s">
+      <c r="K11" t="s">
         <v>2081</v>
       </c>
       <c r="L11" t="s">
@@ -33542,7 +33539,7 @@
       <c r="J12" t="s">
         <v>95</v>
       </c>
-      <c r="K12" s="78" t="s">
+      <c r="K12" t="s">
         <v>2081</v>
       </c>
       <c r="L12" t="s">
@@ -33569,7 +33566,7 @@
       <c r="J13" t="s">
         <v>1129</v>
       </c>
-      <c r="K13" s="78" t="s">
+      <c r="K13" t="s">
         <v>2081</v>
       </c>
       <c r="L13" t="s">
@@ -33596,7 +33593,7 @@
       <c r="J14" t="s">
         <v>1843</v>
       </c>
-      <c r="K14" s="78" t="s">
+      <c r="K14" t="s">
         <v>2081</v>
       </c>
       <c r="L14" t="s">
@@ -33623,7 +33620,7 @@
       <c r="J15" t="s">
         <v>125</v>
       </c>
-      <c r="K15" s="78" t="s">
+      <c r="K15" t="s">
         <v>2081</v>
       </c>
       <c r="L15" t="s">
@@ -33650,7 +33647,7 @@
       <c r="J16" t="s">
         <v>89</v>
       </c>
-      <c r="K16" s="78" t="s">
+      <c r="K16" t="s">
         <v>2081</v>
       </c>
       <c r="L16" t="s">
@@ -33677,7 +33674,7 @@
       <c r="J17" t="s">
         <v>1117</v>
       </c>
-      <c r="K17" s="78" t="s">
+      <c r="K17" t="s">
         <v>2081</v>
       </c>
       <c r="L17" t="s">
@@ -33704,7 +33701,7 @@
       <c r="J18" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="78" t="s">
+      <c r="K18" t="s">
         <v>2081</v>
       </c>
       <c r="L18" t="s">
@@ -33731,7 +33728,7 @@
       <c r="J20" t="s">
         <v>1846</v>
       </c>
-      <c r="K20" s="78" t="s">
+      <c r="K20" t="s">
         <v>2081</v>
       </c>
       <c r="L20" t="s">
@@ -33758,7 +33755,7 @@
       <c r="J22" t="s">
         <v>1122</v>
       </c>
-      <c r="K22" s="78" t="s">
+      <c r="K22" t="s">
         <v>2081</v>
       </c>
       <c r="L22" t="s">
@@ -33785,7 +33782,7 @@
       <c r="J24" t="s">
         <v>1113</v>
       </c>
-      <c r="K24" s="78" t="s">
+      <c r="K24" t="s">
         <v>2081</v>
       </c>
       <c r="L24" t="s">
@@ -33804,23 +33801,20 @@
   <dimension ref="A1:T74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="81"/>
-    <col min="2" max="2" width="39" style="81" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="81"/>
-    <col min="4" max="4" width="54.83203125" style="81" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.6640625" style="81" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.5" style="81" customWidth="1"/>
-    <col min="7" max="7" width="51" style="81" customWidth="1"/>
-    <col min="8" max="9" width="71" style="81" customWidth="1"/>
-    <col min="10" max="10" width="36.5" style="81" customWidth="1"/>
-    <col min="11" max="12" width="35.5" style="81" customWidth="1"/>
-    <col min="13" max="13" width="51" style="81" customWidth="1"/>
-    <col min="14" max="14" width="21.83203125" style="81" customWidth="1"/>
-    <col min="15" max="15" width="16.83203125" style="81" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" style="81" customWidth="1"/>
-    <col min="17" max="17" width="14.5" style="81" customWidth="1"/>
-    <col min="18" max="18" width="51" style="81" customWidth="1"/>
-    <col min="19" max="16384" width="10.83203125" style="81"/>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.5" customWidth="1"/>
+    <col min="7" max="7" width="51" customWidth="1"/>
+    <col min="8" max="9" width="71" customWidth="1"/>
+    <col min="10" max="10" width="36.5" customWidth="1"/>
+    <col min="11" max="12" width="35.5" customWidth="1"/>
+    <col min="13" max="13" width="51" customWidth="1"/>
+    <col min="14" max="14" width="21.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
+    <col min="18" max="18" width="51" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -33842,43 +33836,43 @@
       <c r="F1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="79" t="s">
+      <c r="G1" s="77" t="s">
         <v>1025</v>
       </c>
-      <c r="H1" s="79" t="s">
+      <c r="H1" s="77" t="s">
         <v>1026</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="77" t="s">
         <v>2068</v>
       </c>
-      <c r="J1" s="79" t="s">
+      <c r="J1" s="77" t="s">
         <v>2032</v>
       </c>
-      <c r="K1" s="79" t="s">
+      <c r="K1" s="77" t="s">
         <v>2039</v>
       </c>
-      <c r="L1" s="79" t="s">
+      <c r="L1" s="77" t="s">
         <v>2085</v>
       </c>
-      <c r="M1" s="79" t="s">
+      <c r="M1" s="77" t="s">
         <v>2022</v>
       </c>
-      <c r="N1" s="79" t="s">
+      <c r="N1" s="77" t="s">
         <v>1985</v>
       </c>
-      <c r="O1" s="79" t="s">
+      <c r="O1" s="77" t="s">
         <v>2023</v>
       </c>
-      <c r="P1" s="79" t="s">
+      <c r="P1" s="77" t="s">
         <v>1703</v>
       </c>
-      <c r="Q1" s="79" t="s">
+      <c r="Q1" s="77" t="s">
         <v>1699</v>
       </c>
-      <c r="R1" s="79" t="s">
+      <c r="R1" s="77" t="s">
         <v>1700</v>
       </c>
-      <c r="S1" s="80" t="s">
+      <c r="S1" s="78" t="s">
         <v>9</v>
       </c>
       <c r="T1" s="17" t="s">
@@ -33886,3084 +33880,3084 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2" s="81" t="str">
+      <c r="A2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
         <f>IF(D2&lt;&gt;"",VLOOKUP(D2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C2" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D2" s="82" t="s">
+      <c r="C2" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="82" t="s">
+      <c r="E2" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="F2" s="82" t="s">
+      <c r="F2" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G2" s="82" t="s">
+      <c r="G2" s="6" t="s">
         <v>1215</v>
       </c>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K2" s="82" t="s">
+      <c r="K2" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L2" s="82" t="s">
+      <c r="L2" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M2" s="82" t="s">
+      <c r="M2" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N2" s="82"/>
-      <c r="O2" s="82"/>
-      <c r="P2" s="82" t="s">
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q2" s="82" t="s">
+      <c r="Q2" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R2" s="82" t="s">
+      <c r="R2" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S2" s="82"/>
+      <c r="S2" s="6"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B3" s="81" t="str">
+      <c r="A3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" t="str">
         <f>IF(D3&lt;&gt;"",VLOOKUP(D3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C3" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D3" s="82" t="s">
+      <c r="C3" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="G3" s="6" t="s">
         <v>1216</v>
       </c>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K3" s="82" t="s">
+      <c r="K3" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L3" s="82" t="s">
+      <c r="L3" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M3" s="82" t="s">
+      <c r="M3" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N3" s="82"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="82" t="s">
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q3" s="82" t="s">
+      <c r="Q3" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R3" s="82" t="s">
+      <c r="R3" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S3" s="82"/>
+      <c r="S3" s="6"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4" s="81" t="str">
+      <c r="A4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
         <f>IF(D4&lt;&gt;"",VLOOKUP(D4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C4" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D4" s="82" t="s">
+      <c r="C4" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="82" t="s">
+      <c r="E4" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="F4" s="82" t="s">
+      <c r="F4" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G4" s="82" t="s">
+      <c r="G4" s="6" t="s">
         <v>1235</v>
       </c>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K4" s="82" t="s">
+      <c r="K4" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L4" s="82" t="s">
+      <c r="L4" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M4" s="82" t="s">
+      <c r="M4" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N4" s="82"/>
-      <c r="O4" s="82"/>
-      <c r="P4" s="82" t="s">
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q4" s="82" t="s">
+      <c r="Q4" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R4" s="82" t="s">
+      <c r="R4" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S4" s="82"/>
+      <c r="S4" s="6"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B5" s="81" t="str">
+      <c r="A5" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" t="str">
         <f>IF(D5&lt;&gt;"",VLOOKUP(D5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C5" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D5" s="82" t="s">
+      <c r="C5" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="F5" s="82" t="s">
+      <c r="F5" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G5" s="82" t="s">
+      <c r="G5" s="6" t="s">
         <v>1236</v>
       </c>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="82" t="s">
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K5" s="82" t="s">
+      <c r="K5" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L5" s="82" t="s">
+      <c r="L5" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="82" t="s">
+      <c r="M5" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82" t="s">
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q5" s="82" t="s">
+      <c r="Q5" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R5" s="82" t="s">
+      <c r="R5" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S5" s="82"/>
+      <c r="S5" s="6"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" s="81" t="str">
+      <c r="A6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
         <f>IF(D6&lt;&gt;"",VLOOKUP(D6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C6" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D6" s="82" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="82" t="s">
+      <c r="E6" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G6" s="82" t="s">
+      <c r="G6" s="6" t="s">
         <v>1217</v>
       </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K6" s="82" t="s">
+      <c r="K6" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L6" s="82" t="s">
+      <c r="L6" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M6" s="82" t="s">
+      <c r="M6" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N6" s="82"/>
-      <c r="O6" s="82"/>
-      <c r="P6" s="82" t="s">
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q6" s="82" t="s">
+      <c r="Q6" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R6" s="82" t="s">
+      <c r="R6" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S6" s="82"/>
+      <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B7" s="81" t="str">
+      <c r="A7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" t="str">
         <f>IF(D7&lt;&gt;"",VLOOKUP(D7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C7" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D7" s="82" t="s">
+      <c r="C7" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="F7" s="82" t="s">
+      <c r="F7" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G7" s="82" t="s">
+      <c r="G7" s="6" t="s">
         <v>1218</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82" t="s">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K7" s="82" t="s">
+      <c r="K7" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L7" s="82" t="s">
+      <c r="L7" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M7" s="82" t="s">
+      <c r="M7" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="82" t="s">
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q7" s="82" t="s">
+      <c r="Q7" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R7" s="82" t="s">
+      <c r="R7" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S7" s="82"/>
+      <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B8" s="81" t="str">
+      <c r="A8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B8" t="str">
         <f>IF(D8&lt;&gt;"",VLOOKUP(D8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C8" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D8" s="82" t="s">
+      <c r="C8" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="82" t="s">
+      <c r="E8" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="F8" s="82" t="s">
+      <c r="F8" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G8" s="82" t="s">
+      <c r="G8" s="6" t="s">
         <v>1219</v>
       </c>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82" t="s">
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K8" s="82" t="s">
+      <c r="K8" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L8" s="82" t="s">
+      <c r="L8" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M8" s="82" t="s">
+      <c r="M8" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N8" s="82"/>
-      <c r="O8" s="82"/>
-      <c r="P8" s="82" t="s">
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q8" s="82" t="s">
+      <c r="Q8" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R8" s="82" t="s">
+      <c r="R8" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S8" s="82"/>
+      <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="81" t="str">
+      <c r="A9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="str">
         <f>IF(D9&lt;&gt;"",VLOOKUP(D9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C9" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D9" s="82" t="s">
+      <c r="C9" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="82" t="s">
+      <c r="E9" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="F9" s="82" t="s">
+      <c r="F9" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G9" s="82" t="s">
+      <c r="G9" s="6" t="s">
         <v>1220</v>
       </c>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K9" s="82" t="s">
+      <c r="K9" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L9" s="82" t="s">
+      <c r="L9" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M9" s="82" t="s">
+      <c r="M9" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N9" s="82"/>
-      <c r="O9" s="82"/>
-      <c r="P9" s="82" t="s">
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q9" s="82" t="s">
+      <c r="Q9" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R9" s="82" t="s">
+      <c r="R9" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S9" s="82"/>
+      <c r="S9" s="6"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="81" t="str">
+      <c r="A10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="str">
         <f>IF(D10&lt;&gt;"",VLOOKUP(D10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C10" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D10" s="82" t="s">
+      <c r="C10" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E10" s="82" t="s">
+      <c r="E10" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="F10" s="82" t="s">
+      <c r="F10" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G10" s="82" t="s">
+      <c r="G10" s="6" t="s">
         <v>1221</v>
       </c>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82" t="s">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K10" s="82" t="s">
+      <c r="K10" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L10" s="82" t="s">
+      <c r="L10" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M10" s="82" t="s">
+      <c r="M10" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N10" s="82"/>
-      <c r="O10" s="82"/>
-      <c r="P10" s="82" t="s">
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q10" s="82" t="s">
+      <c r="Q10" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R10" s="82" t="s">
+      <c r="R10" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S10" s="82"/>
+      <c r="S10" s="6"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="81" t="str">
+      <c r="A11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="str">
         <f>IF(D11&lt;&gt;"",VLOOKUP(D11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C11" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D11" s="82" t="s">
+      <c r="C11" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="82" t="s">
+      <c r="E11" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="F11" s="82" t="s">
+      <c r="F11" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G11" s="82" t="s">
+      <c r="G11" s="6" t="s">
         <v>1222</v>
       </c>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82" t="s">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K11" s="82" t="s">
+      <c r="K11" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L11" s="82" t="s">
+      <c r="L11" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M11" s="82" t="s">
+      <c r="M11" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N11" s="82"/>
-      <c r="O11" s="82"/>
-      <c r="P11" s="82" t="s">
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q11" s="82" t="s">
+      <c r="Q11" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R11" s="82" t="s">
+      <c r="R11" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S11" s="82"/>
+      <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" s="81" t="str">
+      <c r="A12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" t="str">
         <f>IF(D12&lt;&gt;"",VLOOKUP(D12,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C12" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D12" s="82" t="s">
+      <c r="C12" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="82" t="s">
+      <c r="E12" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G12" s="82" t="s">
+      <c r="G12" s="6" t="s">
         <v>1223</v>
       </c>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82" t="s">
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K12" s="82" t="s">
+      <c r="K12" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L12" s="82" t="s">
+      <c r="L12" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M12" s="82" t="s">
+      <c r="M12" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N12" s="82"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82" t="s">
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q12" s="82" t="s">
+      <c r="Q12" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R12" s="82" t="s">
+      <c r="R12" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S12" s="82"/>
+      <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" s="81" t="str">
+      <c r="A13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="str">
         <f>IF(D13&lt;&gt;"",VLOOKUP(D13,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C13" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D13" s="82" t="s">
+      <c r="C13" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="82" t="s">
+      <c r="E13" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G13" s="82" t="s">
+      <c r="G13" s="6" t="s">
         <v>1224</v>
       </c>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82" t="s">
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K13" s="82" t="s">
+      <c r="K13" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L13" s="82" t="s">
+      <c r="L13" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M13" s="82" t="s">
+      <c r="M13" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N13" s="82"/>
-      <c r="O13" s="82"/>
-      <c r="P13" s="82" t="s">
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q13" s="82" t="s">
+      <c r="Q13" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R13" s="82" t="s">
+      <c r="R13" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S13" s="82"/>
+      <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" s="81" t="str">
+      <c r="A14" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" t="str">
         <f>IF(D14&lt;&gt;"",VLOOKUP(D14,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C14" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D14" s="82" t="s">
+      <c r="C14" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="82" t="s">
+      <c r="E14" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="F14" s="82" t="s">
+      <c r="F14" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G14" s="82" t="s">
+      <c r="G14" s="6" t="s">
         <v>1225</v>
       </c>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82" t="s">
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K14" s="82" t="s">
+      <c r="K14" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L14" s="82" t="s">
+      <c r="L14" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M14" s="82" t="s">
+      <c r="M14" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N14" s="82"/>
-      <c r="O14" s="82"/>
-      <c r="P14" s="82" t="s">
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q14" s="82" t="s">
+      <c r="Q14" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R14" s="82" t="s">
+      <c r="R14" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S14" s="82"/>
+      <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A15" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" s="81" t="str">
+      <c r="A15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="str">
         <f>IF(D15&lt;&gt;"",VLOOKUP(D15,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C15" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D15" s="82" t="s">
+      <c r="C15" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E15" s="82" t="s">
+      <c r="E15" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="F15" s="82" t="s">
+      <c r="F15" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G15" s="82" t="s">
+      <c r="G15" s="6" t="s">
         <v>1226</v>
       </c>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82" t="s">
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K15" s="82" t="s">
+      <c r="K15" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L15" s="82" t="s">
+      <c r="L15" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M15" s="82" t="s">
+      <c r="M15" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82"/>
-      <c r="P15" s="82" t="s">
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q15" s="82" t="s">
+      <c r="Q15" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R15" s="82" t="s">
+      <c r="R15" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S15" s="82"/>
+      <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A16" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" s="81" t="str">
+      <c r="A16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="str">
         <f>IF(D16&lt;&gt;"",VLOOKUP(D16,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C16" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D16" s="82" t="s">
+      <c r="C16" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="82" t="s">
+      <c r="E16" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G16" s="82" t="s">
+      <c r="G16" s="6" t="s">
         <v>1227</v>
       </c>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
-      <c r="J16" s="82" t="s">
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K16" s="82" t="s">
+      <c r="K16" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L16" s="82" t="s">
+      <c r="L16" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M16" s="82" t="s">
+      <c r="M16" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="82" t="s">
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q16" s="82" t="s">
+      <c r="Q16" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R16" s="82" t="s">
+      <c r="R16" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S16" s="82"/>
+      <c r="S16" s="6"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" s="81" t="str">
+      <c r="A17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="str">
         <f>IF(D17&lt;&gt;"",VLOOKUP(D17,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C17" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D17" s="82" t="s">
+      <c r="C17" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="82" t="s">
+      <c r="E17" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="F17" s="82" t="s">
+      <c r="F17" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G17" s="82" t="s">
+      <c r="G17" s="6" t="s">
         <v>1228</v>
       </c>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82" t="s">
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K17" s="82" t="s">
+      <c r="K17" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L17" s="82" t="s">
+      <c r="L17" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M17" s="82" t="s">
+      <c r="M17" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82"/>
-      <c r="P17" s="82" t="s">
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q17" s="82" t="s">
+      <c r="Q17" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R17" s="82" t="s">
+      <c r="R17" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S17" s="82"/>
+      <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" s="81" t="str">
+      <c r="A18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" t="str">
         <f>IF(D18&lt;&gt;"",VLOOKUP(D18,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C18" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D18" s="82" t="s">
+      <c r="C18" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="82" t="s">
+      <c r="E18" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="F18" s="82" t="s">
+      <c r="F18" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G18" s="82" t="s">
+      <c r="G18" s="6" t="s">
         <v>1229</v>
       </c>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82" t="s">
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K18" s="82" t="s">
+      <c r="K18" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L18" s="82" t="s">
+      <c r="L18" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M18" s="82" t="s">
+      <c r="M18" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N18" s="82"/>
-      <c r="O18" s="82"/>
-      <c r="P18" s="82" t="s">
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q18" s="82" t="s">
+      <c r="Q18" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R18" s="82" t="s">
+      <c r="R18" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S18" s="82"/>
+      <c r="S18" s="6"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B19" s="81" t="str">
+      <c r="A19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" t="str">
         <f>IF(D19&lt;&gt;"",VLOOKUP(D19,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C19" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D19" s="82" t="s">
+      <c r="C19" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="82" t="s">
+      <c r="E19" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="F19" s="82" t="s">
+      <c r="F19" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G19" s="82" t="s">
+      <c r="G19" s="6" t="s">
         <v>1230</v>
       </c>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82" t="s">
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K19" s="82" t="s">
+      <c r="K19" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L19" s="82" t="s">
+      <c r="L19" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M19" s="82" t="s">
+      <c r="M19" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N19" s="82"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="82" t="s">
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q19" s="82" t="s">
+      <c r="Q19" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R19" s="82" t="s">
+      <c r="R19" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S19" s="82"/>
+      <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B20" s="81" t="str">
+      <c r="A20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" t="str">
         <f>IF(D20&lt;&gt;"",VLOOKUP(D20,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C20" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D20" s="82" t="s">
+      <c r="C20" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E20" s="82" t="s">
+      <c r="E20" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="F20" s="82" t="s">
+      <c r="F20" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G20" s="82" t="s">
+      <c r="G20" s="6" t="s">
         <v>1231</v>
       </c>
-      <c r="H20" s="82"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="82" t="s">
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K20" s="82" t="s">
+      <c r="K20" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L20" s="82" t="s">
+      <c r="L20" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M20" s="82" t="s">
+      <c r="M20" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N20" s="82"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82" t="s">
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q20" s="82" t="s">
+      <c r="Q20" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R20" s="82" t="s">
+      <c r="R20" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S20" s="82"/>
+      <c r="S20" s="6"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B21" s="81" t="str">
+      <c r="A21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" t="str">
         <f>IF(D21&lt;&gt;"",VLOOKUP(D21,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C21" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D21" s="82" t="s">
+      <c r="C21" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="82" t="s">
+      <c r="E21" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="F21" s="82" t="s">
+      <c r="F21" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G21" s="82" t="s">
+      <c r="G21" s="6" t="s">
         <v>1232</v>
       </c>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82"/>
-      <c r="J21" s="82" t="s">
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K21" s="82" t="s">
+      <c r="K21" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L21" s="82" t="s">
+      <c r="L21" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M21" s="82" t="s">
+      <c r="M21" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N21" s="82"/>
-      <c r="O21" s="82"/>
-      <c r="P21" s="82" t="s">
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q21" s="82" t="s">
+      <c r="Q21" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R21" s="82" t="s">
+      <c r="R21" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S21" s="82"/>
+      <c r="S21" s="6"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B22" s="81" t="str">
+      <c r="A22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" t="str">
         <f>IF(D22&lt;&gt;"",VLOOKUP(D22,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C22" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D22" s="82" t="s">
+      <c r="C22" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E22" s="82" t="s">
+      <c r="E22" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G22" s="82" t="s">
+      <c r="G22" s="6" t="s">
         <v>1233</v>
       </c>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82" t="s">
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K22" s="82" t="s">
+      <c r="K22" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L22" s="82" t="s">
+      <c r="L22" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M22" s="82" t="s">
+      <c r="M22" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N22" s="82"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="82" t="s">
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q22" s="82" t="s">
+      <c r="Q22" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R22" s="82" t="s">
+      <c r="R22" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S22" s="82"/>
+      <c r="S22" s="6"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B23" s="81" t="str">
+      <c r="A23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" t="str">
         <f>IF(D23&lt;&gt;"",VLOOKUP(D23,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C23" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D23" s="82" t="s">
+      <c r="C23" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="82" t="s">
+      <c r="E23" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="F23" s="82" t="s">
+      <c r="F23" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G23" s="82" t="s">
+      <c r="G23" s="6" t="s">
         <v>1234</v>
       </c>
-      <c r="H23" s="82"/>
-      <c r="I23" s="82"/>
-      <c r="J23" s="82" t="s">
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K23" s="82" t="s">
+      <c r="K23" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L23" s="82" t="s">
+      <c r="L23" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="M23" s="82" t="s">
+      <c r="M23" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N23" s="82"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="82" t="s">
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="Q23" s="82" t="s">
+      <c r="Q23" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="R23" s="82" t="s">
+      <c r="R23" s="6" t="s">
         <v>1698</v>
       </c>
-      <c r="S23" s="82"/>
+      <c r="S23" s="6"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B24" s="81" t="str">
+      <c r="B24" t="str">
         <f>IF(D24&lt;&gt;"",VLOOKUP(D24,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" s="81" t="str">
+      <c r="A25" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" t="str">
         <f>IF(D25&lt;&gt;"",VLOOKUP(D25,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Environmental conditions and measurements</v>
       </c>
-      <c r="C25" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D25" s="82" t="s">
+      <c r="C25" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>1846</v>
       </c>
-      <c r="E25" s="82"/>
-      <c r="F25" s="82" t="s">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G25" s="82"/>
-      <c r="H25" s="82"/>
-      <c r="I25" s="82"/>
-      <c r="J25" s="82" t="s">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K25" s="82" t="s">
+      <c r="K25" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L25" s="82" t="s">
+      <c r="L25" s="6" t="s">
         <v>1846</v>
       </c>
-      <c r="M25" s="82" t="s">
+      <c r="M25" s="6" t="s">
         <v>1988</v>
       </c>
-      <c r="N25" s="82"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="82"/>
-      <c r="Q25" s="82" t="s">
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6" t="s">
         <v>1396</v>
       </c>
-      <c r="R25" s="82" t="s">
+      <c r="R25" s="6" t="s">
         <v>1865</v>
       </c>
-      <c r="S25" s="83" t="s">
+      <c r="S25" s="5" t="s">
         <v>1397</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B26" s="81" t="str">
+      <c r="B26" t="str">
         <f>IF(D26&lt;&gt;"",VLOOKUP(D26,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B27" s="81" t="e">
+      <c r="A27" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" t="e">
         <f>IF(D27&lt;&gt;"",VLOOKUP(D27,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C27" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D27" s="82" t="s">
+      <c r="C27" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>1991</v>
       </c>
-      <c r="E27" s="82" t="s">
+      <c r="E27" s="6" t="s">
         <v>1999</v>
       </c>
-      <c r="F27" s="82" t="s">
+      <c r="F27" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G27" s="82" t="s">
+      <c r="G27" s="6" t="s">
         <v>1412</v>
       </c>
-      <c r="H27" s="82"/>
-      <c r="I27" s="82"/>
-      <c r="J27" s="82"/>
-      <c r="K27" s="82"/>
-      <c r="L27" s="82" t="s">
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6" t="s">
         <v>1991</v>
       </c>
-      <c r="M27" s="82" t="s">
+      <c r="M27" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N27" s="82"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="82"/>
-      <c r="Q27" s="82" t="s">
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6" t="s">
         <v>1414</v>
       </c>
-      <c r="R27" s="82" t="s">
+      <c r="R27" s="6" t="s">
         <v>1994</v>
       </c>
-      <c r="S27" s="82"/>
+      <c r="S27" s="6"/>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A28" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B28" s="81" t="e">
+      <c r="A28" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" t="e">
         <f>IF(D28&lt;&gt;"",VLOOKUP(D28,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C28" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D28" s="82" t="s">
+      <c r="C28" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>1991</v>
       </c>
-      <c r="E28" s="82" t="s">
+      <c r="E28" s="6" t="s">
         <v>1998</v>
       </c>
-      <c r="F28" s="82" t="s">
+      <c r="F28" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G28" s="82" t="s">
+      <c r="G28" s="6" t="s">
         <v>1413</v>
       </c>
-      <c r="H28" s="82"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="82"/>
-      <c r="L28" s="82" t="s">
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6" t="s">
         <v>1991</v>
       </c>
-      <c r="M28" s="82" t="s">
+      <c r="M28" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N28" s="82"/>
-      <c r="O28" s="82"/>
-      <c r="P28" s="82"/>
-      <c r="Q28" s="82" t="s">
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6" t="s">
         <v>1414</v>
       </c>
-      <c r="R28" s="82" t="s">
+      <c r="R28" s="6" t="s">
         <v>1994</v>
       </c>
-      <c r="S28" s="82"/>
+      <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A29" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B29" s="81" t="e">
+      <c r="A29" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" t="e">
         <f>IF(D29&lt;&gt;"",VLOOKUP(D29,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C29" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D29" s="82" t="s">
+      <c r="C29" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>1991</v>
       </c>
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="6" t="s">
         <v>1997</v>
       </c>
-      <c r="F29" s="82" t="s">
+      <c r="F29" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G29" s="82" t="s">
+      <c r="G29" s="6" t="s">
         <v>1415</v>
       </c>
-      <c r="H29" s="82"/>
-      <c r="I29" s="82"/>
-      <c r="J29" s="82"/>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82" t="s">
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6" t="s">
         <v>1991</v>
       </c>
-      <c r="M29" s="82" t="s">
+      <c r="M29" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N29" s="82"/>
-      <c r="O29" s="82"/>
-      <c r="P29" s="82"/>
-      <c r="Q29" s="82" t="s">
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6" t="s">
         <v>1416</v>
       </c>
-      <c r="R29" s="82" t="s">
+      <c r="R29" s="6" t="s">
         <v>1994</v>
       </c>
-      <c r="S29" s="82"/>
+      <c r="S29" s="6"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B30" s="81" t="str">
+      <c r="B30" t="str">
         <f>IF(D30&lt;&gt;"",VLOOKUP(D30,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A31" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B31" s="81" t="e">
+      <c r="A31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" t="e">
         <f>IF(D31&lt;&gt;"",VLOOKUP(D31,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C31" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D31" s="82" t="s">
+      <c r="C31" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>1992</v>
       </c>
-      <c r="E31" s="82" t="s">
+      <c r="E31" s="6" t="s">
         <v>1999</v>
       </c>
-      <c r="F31" s="82" t="s">
+      <c r="F31" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G31" s="82" t="s">
+      <c r="G31" s="6" t="s">
         <v>1412</v>
       </c>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82" t="s">
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6" t="s">
         <v>1992</v>
       </c>
-      <c r="M31" s="82" t="s">
+      <c r="M31" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N31" s="82"/>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82" t="s">
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6" t="s">
         <v>1414</v>
       </c>
-      <c r="R31" s="82" t="s">
+      <c r="R31" s="6" t="s">
         <v>1995</v>
       </c>
-      <c r="S31" s="82"/>
+      <c r="S31" s="6"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A32" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B32" s="81" t="e">
+      <c r="A32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" t="e">
         <f>IF(D32&lt;&gt;"",VLOOKUP(D32,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C32" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D32" s="82" t="s">
+      <c r="C32" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>1992</v>
       </c>
-      <c r="E32" s="82" t="s">
+      <c r="E32" s="6" t="s">
         <v>1998</v>
       </c>
-      <c r="F32" s="82" t="s">
+      <c r="F32" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G32" s="82" t="s">
+      <c r="G32" s="6" t="s">
         <v>1413</v>
       </c>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82" t="s">
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6" t="s">
         <v>1992</v>
       </c>
-      <c r="M32" s="82" t="s">
+      <c r="M32" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N32" s="82"/>
-      <c r="O32" s="82"/>
-      <c r="P32" s="82"/>
-      <c r="Q32" s="82" t="s">
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6" t="s">
         <v>1414</v>
       </c>
-      <c r="R32" s="82" t="s">
+      <c r="R32" s="6" t="s">
         <v>1995</v>
       </c>
-      <c r="S32" s="82"/>
+      <c r="S32" s="6"/>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A33" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B33" s="81" t="e">
+      <c r="A33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" t="e">
         <f>IF(D33&lt;&gt;"",VLOOKUP(D33,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C33" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D33" s="82" t="s">
+      <c r="C33" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>1992</v>
       </c>
-      <c r="E33" s="82" t="s">
+      <c r="E33" s="6" t="s">
         <v>1997</v>
       </c>
-      <c r="F33" s="82" t="s">
+      <c r="F33" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G33" s="82" t="s">
+      <c r="G33" s="6" t="s">
         <v>1415</v>
       </c>
-      <c r="H33" s="82"/>
-      <c r="I33" s="82"/>
-      <c r="J33" s="82"/>
-      <c r="K33" s="82"/>
-      <c r="L33" s="82" t="s">
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6" t="s">
         <v>1992</v>
       </c>
-      <c r="M33" s="82" t="s">
+      <c r="M33" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N33" s="82"/>
-      <c r="O33" s="82"/>
-      <c r="P33" s="82"/>
-      <c r="Q33" s="82" t="s">
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6" t="s">
         <v>1416</v>
       </c>
-      <c r="R33" s="82" t="s">
+      <c r="R33" s="6" t="s">
         <v>1995</v>
       </c>
-      <c r="S33" s="82"/>
+      <c r="S33" s="6"/>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B34" s="81" t="str">
+      <c r="B34" t="str">
         <f>IF(D34&lt;&gt;"",VLOOKUP(D34,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A35" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B35" s="81" t="e">
+      <c r="A35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" t="e">
         <f>IF(D35&lt;&gt;"",VLOOKUP(D35,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C35" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D35" s="82" t="s">
+      <c r="C35" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>1993</v>
       </c>
-      <c r="E35" s="82" t="s">
+      <c r="E35" s="6" t="s">
         <v>1999</v>
       </c>
-      <c r="F35" s="82" t="s">
+      <c r="F35" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G35" s="82" t="s">
+      <c r="G35" s="6" t="s">
         <v>1412</v>
       </c>
-      <c r="H35" s="82"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82" t="s">
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6" t="s">
         <v>1993</v>
       </c>
-      <c r="M35" s="82" t="s">
+      <c r="M35" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N35" s="82"/>
-      <c r="O35" s="82"/>
-      <c r="P35" s="82"/>
-      <c r="Q35" s="82" t="s">
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6" t="s">
         <v>1414</v>
       </c>
-      <c r="R35" s="82" t="s">
+      <c r="R35" s="6" t="s">
         <v>1996</v>
       </c>
-      <c r="S35" s="82"/>
+      <c r="S35" s="6"/>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A36" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B36" s="81" t="e">
+      <c r="A36" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" t="e">
         <f>IF(D36&lt;&gt;"",VLOOKUP(D36,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C36" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D36" s="82" t="s">
+      <c r="C36" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>1993</v>
       </c>
-      <c r="E36" s="82" t="s">
+      <c r="E36" s="6" t="s">
         <v>1998</v>
       </c>
-      <c r="F36" s="82" t="s">
+      <c r="F36" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G36" s="82" t="s">
+      <c r="G36" s="6" t="s">
         <v>1413</v>
       </c>
-      <c r="H36" s="82"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="82"/>
-      <c r="K36" s="82"/>
-      <c r="L36" s="82" t="s">
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6" t="s">
         <v>1993</v>
       </c>
-      <c r="M36" s="82" t="s">
+      <c r="M36" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N36" s="82"/>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="82" t="s">
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6" t="s">
         <v>1414</v>
       </c>
-      <c r="R36" s="82" t="s">
+      <c r="R36" s="6" t="s">
         <v>1996</v>
       </c>
-      <c r="S36" s="82"/>
+      <c r="S36" s="6"/>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A37" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B37" s="81" t="e">
+      <c r="A37" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B37" t="e">
         <f>IF(D37&lt;&gt;"",VLOOKUP(D37,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C37" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D37" s="82" t="s">
+      <c r="C37" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>1993</v>
       </c>
-      <c r="E37" s="82" t="s">
+      <c r="E37" s="6" t="s">
         <v>1997</v>
       </c>
-      <c r="F37" s="82" t="s">
+      <c r="F37" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G37" s="82" t="s">
+      <c r="G37" s="6" t="s">
         <v>1415</v>
       </c>
-      <c r="H37" s="82"/>
-      <c r="I37" s="82"/>
-      <c r="J37" s="82"/>
-      <c r="K37" s="82"/>
-      <c r="L37" s="82" t="s">
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6" t="s">
         <v>1993</v>
       </c>
-      <c r="M37" s="82" t="s">
+      <c r="M37" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N37" s="82"/>
-      <c r="O37" s="82"/>
-      <c r="P37" s="82"/>
-      <c r="Q37" s="82" t="s">
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6" t="s">
         <v>1416</v>
       </c>
-      <c r="R37" s="82" t="s">
+      <c r="R37" s="6" t="s">
         <v>1996</v>
       </c>
-      <c r="S37" s="82"/>
+      <c r="S37" s="6"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B38" s="81" t="str">
+      <c r="B38" t="str">
         <f>IF(D38&lt;&gt;"",VLOOKUP(D38,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="86" t="b">
+      <c r="A39" s="80" t="b">
         <v>0</v>
       </c>
       <c r="B39" s="24" t="str">
         <f>IF(D39&lt;&gt;"",VLOOKUP(D39,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C39" s="86" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D39" s="86" t="s">
+      <c r="C39" s="80" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D39" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="E39" s="86" t="s">
+      <c r="E39" s="80" t="s">
         <v>1159</v>
       </c>
-      <c r="F39" s="86" t="s">
+      <c r="F39" s="80" t="s">
         <v>1237</v>
       </c>
-      <c r="G39" s="86" t="s">
+      <c r="G39" s="80" t="s">
         <v>1487</v>
       </c>
-      <c r="H39" s="86" t="s">
+      <c r="H39" s="80" t="s">
         <v>1740</v>
       </c>
-      <c r="I39" s="86"/>
-      <c r="J39" s="86" t="s">
+      <c r="I39" s="80"/>
+      <c r="J39" s="80" t="s">
         <v>1115</v>
       </c>
-      <c r="K39" s="86" t="s">
+      <c r="K39" s="80" t="s">
         <v>1115</v>
       </c>
-      <c r="L39" s="86" t="s">
+      <c r="L39" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="M39" s="86" t="s">
+      <c r="M39" s="80" t="s">
         <v>2075</v>
       </c>
-      <c r="N39" s="86"/>
-      <c r="O39" s="86" t="s">
+      <c r="N39" s="80"/>
+      <c r="O39" s="80" t="s">
         <v>1037</v>
       </c>
-      <c r="P39" s="86"/>
-      <c r="Q39" s="86" t="s">
+      <c r="P39" s="80"/>
+      <c r="Q39" s="80" t="s">
         <v>1489</v>
       </c>
-      <c r="R39" s="86" t="s">
+      <c r="R39" s="80" t="s">
         <v>1705</v>
       </c>
-      <c r="S39" s="86"/>
-      <c r="T39" s="86" t="s">
+      <c r="S39" s="80"/>
+      <c r="T39" s="80" t="s">
         <v>2000</v>
       </c>
     </row>
     <row r="40" spans="1:20" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="86" t="b">
+      <c r="A40" s="80" t="b">
         <v>0</v>
       </c>
       <c r="B40" s="24" t="str">
         <f>IF(D40&lt;&gt;"",VLOOKUP(D40,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C40" s="86" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D40" s="86" t="s">
+      <c r="C40" s="80" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D40" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="E40" s="86" t="s">
+      <c r="E40" s="80" t="s">
         <v>1160</v>
       </c>
-      <c r="F40" s="86" t="s">
+      <c r="F40" s="80" t="s">
         <v>1237</v>
       </c>
-      <c r="G40" s="86" t="s">
+      <c r="G40" s="80" t="s">
         <v>1488</v>
       </c>
-      <c r="H40" s="86" t="s">
+      <c r="H40" s="80" t="s">
         <v>1740</v>
       </c>
-      <c r="I40" s="86"/>
-      <c r="J40" s="86" t="s">
+      <c r="I40" s="80"/>
+      <c r="J40" s="80" t="s">
         <v>1115</v>
       </c>
-      <c r="K40" s="86" t="s">
+      <c r="K40" s="80" t="s">
         <v>1115</v>
       </c>
-      <c r="L40" s="86" t="s">
+      <c r="L40" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="M40" s="86" t="s">
+      <c r="M40" s="80" t="s">
         <v>2075</v>
       </c>
-      <c r="N40" s="86"/>
-      <c r="O40" s="86" t="s">
+      <c r="N40" s="80"/>
+      <c r="O40" s="80" t="s">
         <v>1037</v>
       </c>
-      <c r="P40" s="86"/>
-      <c r="Q40" s="86" t="s">
+      <c r="P40" s="80"/>
+      <c r="Q40" s="80" t="s">
         <v>1489</v>
       </c>
-      <c r="R40" s="86" t="s">
+      <c r="R40" s="80" t="s">
         <v>1705</v>
       </c>
-      <c r="S40" s="86"/>
-      <c r="T40" s="86" t="s">
+      <c r="S40" s="80"/>
+      <c r="T40" s="80" t="s">
         <v>2000</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B41" s="81" t="str">
+      <c r="B41" t="str">
         <f>IF(D41&lt;&gt;"",VLOOKUP(D41,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A42" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B42" s="81" t="str">
+      <c r="A42" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B42" t="str">
         <f>IF(D42&lt;&gt;"",VLOOKUP(D42,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C42" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D42" s="82" t="s">
+      <c r="C42" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E42" s="82" t="s">
+      <c r="E42" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F42" s="82" t="s">
+      <c r="F42" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G42" s="82" t="s">
+      <c r="G42" s="6" t="s">
         <v>1538</v>
       </c>
-      <c r="H42" s="82"/>
-      <c r="I42" s="82"/>
-      <c r="J42" s="82" t="s">
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K42" s="82" t="s">
+      <c r="K42" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L42" s="82" t="s">
+      <c r="L42" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M42" s="82" t="s">
+      <c r="M42" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N42" s="82" t="s">
+      <c r="N42" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O42" s="82" t="s">
+      <c r="O42" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P42" s="82"/>
+      <c r="P42" s="6"/>
       <c r="Q42" s="12" t="s">
         <v>1538</v>
       </c>
       <c r="R42" s="12" t="s">
         <v>759</v>
       </c>
-      <c r="S42" s="83" t="s">
+      <c r="S42" s="5" t="s">
         <v>1549</v>
       </c>
-      <c r="T42" s="81" t="s">
+      <c r="T42" t="s">
         <v>1539</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A43" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B43" s="81" t="str">
+      <c r="A43" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B43" t="str">
         <f>IF(D43&lt;&gt;"",VLOOKUP(D43,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C43" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D43" s="82" t="s">
+      <c r="C43" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E43" s="82" t="s">
+      <c r="E43" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F43" s="82" t="s">
+      <c r="F43" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G43" s="82" t="s">
+      <c r="G43" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="H43" s="82"/>
-      <c r="I43" s="82"/>
-      <c r="J43" s="82" t="s">
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K43" s="82" t="s">
+      <c r="K43" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L43" s="82" t="s">
+      <c r="L43" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M43" s="82" t="s">
+      <c r="M43" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N43" s="82" t="s">
+      <c r="N43" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O43" s="82" t="s">
+      <c r="O43" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P43" s="82"/>
+      <c r="P43" s="6"/>
       <c r="Q43" s="12" t="s">
         <v>1542</v>
       </c>
       <c r="R43" s="12" t="s">
         <v>1543</v>
       </c>
-      <c r="S43" s="83" t="s">
+      <c r="S43" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A44" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B44" s="81" t="str">
+      <c r="A44" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B44" t="str">
         <f>IF(D44&lt;&gt;"",VLOOKUP(D44,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C44" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D44" s="82" t="s">
+      <c r="C44" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E44" s="82" t="s">
+      <c r="E44" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F44" s="82" t="s">
+      <c r="F44" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G44" s="82" t="s">
+      <c r="G44" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
-      <c r="J44" s="82" t="s">
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K44" s="82" t="s">
+      <c r="K44" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L44" s="82" t="s">
+      <c r="L44" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M44" s="82" t="s">
+      <c r="M44" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N44" s="82" t="s">
+      <c r="N44" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O44" s="82" t="s">
+      <c r="O44" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P44" s="82"/>
+      <c r="P44" s="6"/>
       <c r="Q44" s="12" t="s">
         <v>1542</v>
       </c>
       <c r="R44" s="12" t="s">
         <v>1544</v>
       </c>
-      <c r="S44" s="83" t="s">
+      <c r="S44" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A45" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B45" s="81" t="str">
+      <c r="A45" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B45" t="str">
         <f>IF(D45&lt;&gt;"",VLOOKUP(D45,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C45" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D45" s="82" t="s">
+      <c r="C45" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="82" t="s">
+      <c r="E45" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F45" s="82" t="s">
+      <c r="F45" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G45" s="82" t="s">
+      <c r="G45" s="6" t="s">
         <v>1538</v>
       </c>
-      <c r="H45" s="82"/>
-      <c r="I45" s="82"/>
-      <c r="J45" s="82" t="s">
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K45" s="82" t="s">
+      <c r="K45" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L45" s="82" t="s">
+      <c r="L45" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M45" s="82" t="s">
+      <c r="M45" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N45" s="82" t="s">
+      <c r="N45" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O45" s="82" t="s">
+      <c r="O45" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P45" s="82"/>
+      <c r="P45" s="6"/>
       <c r="Q45" s="12" t="s">
         <v>1538</v>
       </c>
       <c r="R45" s="12" t="s">
         <v>1545</v>
       </c>
-      <c r="S45" s="83" t="s">
+      <c r="S45" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A46" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B46" s="81" t="str">
+      <c r="A46" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B46" t="str">
         <f>IF(D46&lt;&gt;"",VLOOKUP(D46,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C46" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D46" s="82" t="s">
+      <c r="C46" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E46" s="82" t="s">
+      <c r="E46" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F46" s="82" t="s">
+      <c r="F46" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G46" s="82" t="s">
+      <c r="G46" s="6" t="s">
         <v>1538</v>
       </c>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="82" t="s">
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K46" s="82" t="s">
+      <c r="K46" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L46" s="82" t="s">
+      <c r="L46" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M46" s="82" t="s">
+      <c r="M46" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N46" s="82" t="s">
+      <c r="N46" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O46" s="82" t="s">
+      <c r="O46" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P46" s="82"/>
+      <c r="P46" s="6"/>
       <c r="Q46" s="12" t="s">
         <v>1538</v>
       </c>
       <c r="R46" s="12" t="s">
         <v>1546</v>
       </c>
-      <c r="S46" s="83" t="s">
+      <c r="S46" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A47" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B47" s="81" t="str">
+      <c r="A47" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B47" t="str">
         <f>IF(D47&lt;&gt;"",VLOOKUP(D47,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C47" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D47" s="82" t="s">
+      <c r="C47" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E47" s="82" t="s">
+      <c r="E47" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F47" s="82" t="s">
+      <c r="F47" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G47" s="82" t="s">
+      <c r="G47" s="6" t="s">
         <v>1538</v>
       </c>
-      <c r="H47" s="82"/>
-      <c r="I47" s="82"/>
-      <c r="J47" s="82" t="s">
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K47" s="82" t="s">
+      <c r="K47" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L47" s="82" t="s">
+      <c r="L47" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M47" s="82" t="s">
+      <c r="M47" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N47" s="82" t="s">
+      <c r="N47" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O47" s="82" t="s">
+      <c r="O47" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P47" s="82"/>
+      <c r="P47" s="6"/>
       <c r="Q47" s="12" t="s">
         <v>1538</v>
       </c>
       <c r="R47" s="12" t="s">
         <v>1547</v>
       </c>
-      <c r="S47" s="83" t="s">
+      <c r="S47" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A48" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B48" s="81" t="str">
+      <c r="A48" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B48" t="str">
         <f>IF(D48&lt;&gt;"",VLOOKUP(D48,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C48" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D48" s="82" t="s">
+      <c r="C48" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E48" s="82" t="s">
+      <c r="E48" s="6" t="s">
         <v>2005</v>
       </c>
-      <c r="F48" s="82" t="s">
+      <c r="F48" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G48" s="82" t="s">
+      <c r="G48" s="6" t="s">
         <v>1542</v>
       </c>
-      <c r="H48" s="82"/>
-      <c r="I48" s="82"/>
-      <c r="J48" s="82" t="s">
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K48" s="82" t="s">
+      <c r="K48" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L48" s="82" t="s">
+      <c r="L48" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M48" s="82" t="s">
+      <c r="M48" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N48" s="82" t="s">
+      <c r="N48" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O48" s="82" t="s">
+      <c r="O48" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P48" s="82"/>
+      <c r="P48" s="6"/>
       <c r="Q48" s="12" t="s">
         <v>1542</v>
       </c>
       <c r="R48" s="12" t="s">
         <v>1548</v>
       </c>
-      <c r="S48" s="83" t="s">
+      <c r="S48" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A49" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B49" s="81" t="str">
+      <c r="A49" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B49" t="str">
         <f>IF(D49&lt;&gt;"",VLOOKUP(D49,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C49" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D49" s="82" t="s">
+      <c r="C49" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="82" t="s">
+      <c r="E49" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="F49" s="82" t="s">
+      <c r="F49" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G49" s="84" t="s">
+      <c r="G49" s="79" t="s">
         <v>1416</v>
       </c>
-      <c r="H49" s="82"/>
-      <c r="I49" s="82"/>
-      <c r="J49" s="82" t="s">
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K49" s="82" t="s">
+      <c r="K49" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L49" s="82" t="s">
+      <c r="L49" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M49" s="82" t="s">
+      <c r="M49" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N49" s="82" t="s">
+      <c r="N49" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O49" s="82" t="s">
+      <c r="O49" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P49" s="82"/>
+      <c r="P49" s="6"/>
       <c r="Q49" s="13" t="s">
         <v>1416</v>
       </c>
       <c r="R49" s="14" t="s">
         <v>1550</v>
       </c>
-      <c r="S49" s="83" t="s">
+      <c r="S49" s="5" t="s">
         <v>1549</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A50" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B50" s="81" t="str">
+      <c r="A50" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B50" t="str">
         <f>IF(D50&lt;&gt;"",VLOOKUP(D50,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C50" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D50" s="82" t="s">
+      <c r="C50" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E50" s="82" t="s">
+      <c r="E50" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F50" s="82" t="s">
+      <c r="F50" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G50" s="82" t="s">
+      <c r="G50" s="6" t="s">
         <v>1540</v>
       </c>
-      <c r="H50" s="82"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="82" t="s">
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K50" s="82" t="s">
+      <c r="K50" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L50" s="82" t="s">
+      <c r="L50" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="M50" s="82" t="s">
+      <c r="M50" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N50" s="82" t="s">
+      <c r="N50" s="6" t="s">
         <v>1536</v>
       </c>
-      <c r="O50" s="82" t="s">
+      <c r="O50" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P50" s="82"/>
+      <c r="P50" s="6"/>
       <c r="Q50" s="12" t="s">
         <v>1540</v>
       </c>
       <c r="R50" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="S50" s="83" t="s">
+      <c r="S50" s="5" t="s">
         <v>1549</v>
       </c>
-      <c r="T50" s="81" t="s">
+      <c r="T50" t="s">
         <v>1541</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B51" s="81" t="str">
+      <c r="B51" t="str">
         <f>IF(D51&lt;&gt;"",VLOOKUP(D51,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A52" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B52" s="81" t="str">
+      <c r="A52" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B52" t="str">
         <f>IF(D52&lt;&gt;"",VLOOKUP(D52,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>AMR detection information</v>
       </c>
-      <c r="C52" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D52" s="82" t="s">
+      <c r="C52" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>1122</v>
       </c>
-      <c r="E52" s="82"/>
-      <c r="F52" s="82" t="s">
+      <c r="E52" s="6"/>
+      <c r="F52" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G52" s="82"/>
-      <c r="H52" s="82" t="s">
+      <c r="G52" s="6"/>
+      <c r="H52" s="6" t="s">
         <v>1718</v>
       </c>
-      <c r="I52" s="82"/>
-      <c r="J52" s="82" t="s">
+      <c r="I52" s="6"/>
+      <c r="J52" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K52" s="82" t="s">
+      <c r="K52" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L52" s="82" t="s">
+      <c r="L52" s="6" t="s">
         <v>1122</v>
       </c>
-      <c r="M52" s="82" t="s">
+      <c r="M52" s="6" t="s">
         <v>2076</v>
       </c>
-      <c r="N52" s="82"/>
-      <c r="O52" s="82" t="s">
+      <c r="N52" s="6"/>
+      <c r="O52" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P52" s="82"/>
-      <c r="Q52" s="82" t="s">
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6" t="s">
         <v>1567</v>
       </c>
-      <c r="R52" s="82" t="s">
+      <c r="R52" s="6" t="s">
         <v>1686</v>
       </c>
-      <c r="S52" s="83" t="s">
+      <c r="S52" s="5" t="s">
         <v>1568</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A53" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B53" s="81" t="str">
+      <c r="A53" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B53" t="str">
         <f>IF(D53&lt;&gt;"",VLOOKUP(D53,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="C53" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D53" s="82" t="s">
+      <c r="C53" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="82"/>
-      <c r="F53" s="82" t="s">
+      <c r="E53" s="6"/>
+      <c r="F53" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G53" s="82"/>
-      <c r="H53" s="82" t="s">
+      <c r="G53" s="6"/>
+      <c r="H53" s="6" t="s">
         <v>1715</v>
       </c>
-      <c r="I53" s="82"/>
-      <c r="J53" s="82" t="s">
+      <c r="I53" s="6"/>
+      <c r="J53" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K53" s="82" t="s">
+      <c r="K53" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L53" s="82" t="s">
+      <c r="L53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M53" s="82" t="s">
+      <c r="M53" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N53" s="82"/>
-      <c r="O53" s="82" t="s">
+      <c r="N53" s="6"/>
+      <c r="O53" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P53" s="82"/>
-      <c r="Q53" s="82" t="s">
+      <c r="P53" s="6"/>
+      <c r="Q53" s="6" t="s">
         <v>1571</v>
       </c>
-      <c r="R53" s="82" t="s">
+      <c r="R53" s="6" t="s">
         <v>1687</v>
       </c>
-      <c r="S53" s="83" t="s">
+      <c r="S53" s="5" t="s">
         <v>1572</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A54" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B54" s="81" t="str">
+      <c r="A54" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B54" t="str">
         <f>IF(D54&lt;&gt;"",VLOOKUP(D54,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="C54" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D54" s="82" t="s">
+      <c r="C54" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E54" s="82"/>
-      <c r="F54" s="82" t="s">
+      <c r="E54" s="6"/>
+      <c r="F54" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82" t="s">
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K54" s="82" t="s">
+      <c r="K54" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L54" s="82" t="s">
+      <c r="L54" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M54" s="82" t="s">
+      <c r="M54" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N54" s="82"/>
-      <c r="O54" s="82" t="s">
+      <c r="N54" s="6"/>
+      <c r="O54" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P54" s="82"/>
-      <c r="Q54" s="82" t="s">
+      <c r="P54" s="6"/>
+      <c r="Q54" s="6" t="s">
         <v>1574</v>
       </c>
-      <c r="R54" s="82" t="s">
+      <c r="R54" s="6" t="s">
         <v>1688</v>
       </c>
-      <c r="S54" s="83" t="s">
+      <c r="S54" s="5" t="s">
         <v>1572</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A55" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B55" s="81" t="str">
+      <c r="A55" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B55" t="str">
         <f>IF(D55&lt;&gt;"",VLOOKUP(D55,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="C55" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D55" s="82" t="s">
+      <c r="C55" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E55" s="82"/>
-      <c r="F55" s="82" t="s">
+      <c r="E55" s="6"/>
+      <c r="F55" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
-      <c r="J55" s="82" t="s">
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K55" s="82" t="s">
+      <c r="K55" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L55" s="82" t="s">
+      <c r="L55" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="M55" s="82" t="s">
+      <c r="M55" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N55" s="82"/>
-      <c r="O55" s="82" t="s">
+      <c r="N55" s="6"/>
+      <c r="O55" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P55" s="82"/>
-      <c r="Q55" s="82" t="s">
+      <c r="P55" s="6"/>
+      <c r="Q55" s="6" t="s">
         <v>1575</v>
       </c>
-      <c r="R55" s="82" t="s">
+      <c r="R55" s="6" t="s">
         <v>1689</v>
       </c>
-      <c r="S55" s="83" t="s">
+      <c r="S55" s="5" t="s">
         <v>1572</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A56" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B56" s="81" t="str">
+      <c r="A56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B56" t="str">
         <f>IF(D56&lt;&gt;"",VLOOKUP(D56,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="C56" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D56" s="82" t="s">
+      <c r="C56" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D56" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E56" s="82"/>
-      <c r="F56" s="82" t="s">
+      <c r="E56" s="6"/>
+      <c r="F56" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G56" s="82"/>
-      <c r="H56" s="82"/>
-      <c r="I56" s="82"/>
-      <c r="J56" s="82" t="s">
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K56" s="82" t="s">
+      <c r="K56" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L56" s="82" t="s">
+      <c r="L56" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="M56" s="82" t="s">
+      <c r="M56" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N56" s="82"/>
-      <c r="O56" s="82" t="s">
+      <c r="N56" s="6"/>
+      <c r="O56" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P56" s="82"/>
-      <c r="Q56" s="82" t="s">
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6" t="s">
         <v>1579</v>
       </c>
-      <c r="R56" s="82" t="s">
+      <c r="R56" s="6" t="s">
         <v>1690</v>
       </c>
-      <c r="S56" s="83" t="s">
+      <c r="S56" s="5" t="s">
         <v>1572</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A57" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B57" s="81" t="str">
+      <c r="A57" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B57" t="str">
         <f>IF(D57&lt;&gt;"",VLOOKUP(D57,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Bioinformatics and QC metrics</v>
       </c>
-      <c r="C57" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D57" s="82" t="s">
+      <c r="C57" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D57" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E57" s="82"/>
-      <c r="F57" s="82" t="s">
+      <c r="E57" s="6"/>
+      <c r="F57" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G57" s="82"/>
-      <c r="H57" s="82" t="s">
+      <c r="G57" s="6"/>
+      <c r="H57" s="6" t="s">
         <v>1716</v>
       </c>
-      <c r="I57" s="82"/>
-      <c r="J57" s="82" t="s">
+      <c r="I57" s="6"/>
+      <c r="J57" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K57" s="82" t="s">
+      <c r="K57" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L57" s="82" t="s">
+      <c r="L57" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="M57" s="82" t="s">
+      <c r="M57" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N57" s="82"/>
-      <c r="O57" s="82" t="s">
+      <c r="N57" s="6"/>
+      <c r="O57" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P57" s="82"/>
-      <c r="Q57" s="82" t="s">
+      <c r="P57" s="6"/>
+      <c r="Q57" s="6" t="s">
         <v>1581</v>
       </c>
-      <c r="R57" s="82" t="s">
+      <c r="R57" s="6" t="s">
         <v>1691</v>
       </c>
-      <c r="S57" s="83" t="s">
+      <c r="S57" s="5" t="s">
         <v>1572</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A58" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B58" s="81" t="str">
+      <c r="A58" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B58" t="str">
         <f>IF(D58&lt;&gt;"",VLOOKUP(D58,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Lineage/clade information</v>
       </c>
-      <c r="C58" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D58" s="82" t="s">
+      <c r="C58" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>1129</v>
       </c>
-      <c r="E58" s="82"/>
-      <c r="F58" s="82" t="s">
+      <c r="E58" s="6"/>
+      <c r="F58" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G58" s="82"/>
-      <c r="H58" s="82"/>
-      <c r="I58" s="82"/>
-      <c r="J58" s="82" t="s">
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K58" s="82" t="s">
+      <c r="K58" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L58" s="82" t="s">
+      <c r="L58" s="6" t="s">
         <v>1129</v>
       </c>
-      <c r="M58" s="82" t="s">
+      <c r="M58" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N58" s="82"/>
-      <c r="O58" s="82" t="s">
+      <c r="N58" s="6"/>
+      <c r="O58" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P58" s="82"/>
-      <c r="Q58" s="82" t="s">
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6" t="s">
         <v>1583</v>
       </c>
-      <c r="R58" s="82" t="s">
+      <c r="R58" s="6" t="s">
         <v>1692</v>
       </c>
-      <c r="S58" s="83" t="s">
+      <c r="S58" s="5" t="s">
         <v>1584</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B59" s="81" t="str">
+      <c r="B59" t="str">
         <f>IF(D59&lt;&gt;"",VLOOKUP(D59,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A60" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B60" s="81" t="str">
+      <c r="A60" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B60" t="str">
         <f>IF(D60&lt;&gt;"",VLOOKUP(D60,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C60" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D60" s="82" t="s">
+      <c r="C60" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>1843</v>
       </c>
-      <c r="E60" s="82"/>
-      <c r="F60" s="82" t="s">
+      <c r="E60" s="6"/>
+      <c r="F60" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G60" s="82"/>
-      <c r="H60" s="82" t="s">
+      <c r="G60" s="6"/>
+      <c r="H60" s="6" t="s">
         <v>2018</v>
       </c>
-      <c r="I60" s="82"/>
-      <c r="J60" s="82" t="s">
+      <c r="I60" s="6"/>
+      <c r="J60" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K60" s="82" t="s">
+      <c r="K60" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L60" s="82" t="s">
+      <c r="L60" s="6" t="s">
         <v>1843</v>
       </c>
-      <c r="M60" s="82" t="s">
+      <c r="M60" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N60" s="82"/>
-      <c r="O60" s="82" t="s">
+      <c r="N60" s="6"/>
+      <c r="O60" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P60" s="82"/>
-      <c r="Q60" s="82" t="s">
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6" t="s">
         <v>1593</v>
       </c>
-      <c r="R60" s="82" t="s">
+      <c r="R60" s="6" t="s">
         <v>2019</v>
       </c>
-      <c r="S60" s="83" t="s">
+      <c r="S60" s="5" t="s">
         <v>1594</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B61" s="81" t="str">
+      <c r="B61" t="str">
         <f>IF(D61&lt;&gt;"",VLOOKUP(D61,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A62" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B62" s="81" t="str">
+      <c r="A62" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B62" t="str">
         <f>IF(D62&lt;&gt;"",VLOOKUP(D62,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="C62" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D62" s="82" t="s">
+      <c r="C62" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D62" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E62" s="82"/>
-      <c r="F62" s="82" t="s">
+      <c r="E62" s="6"/>
+      <c r="F62" s="6" t="s">
         <v>1237</v>
       </c>
       <c r="G62" s="9"/>
-      <c r="H62" s="82" t="s">
+      <c r="H62" s="6" t="s">
         <v>1738</v>
       </c>
-      <c r="I62" s="82"/>
-      <c r="J62" s="82" t="s">
+      <c r="I62" s="6"/>
+      <c r="J62" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K62" s="82" t="s">
+      <c r="K62" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="L62" s="82" t="s">
+      <c r="L62" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="M62" s="82" t="s">
+      <c r="M62" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N62" s="82"/>
-      <c r="O62" s="82" t="s">
+      <c r="N62" s="6"/>
+      <c r="O62" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P62" s="82"/>
-      <c r="Q62" s="82" t="s">
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6" t="s">
         <v>1606</v>
       </c>
-      <c r="R62" s="82" t="s">
+      <c r="R62" s="6" t="s">
         <v>1605</v>
       </c>
-      <c r="S62" s="83" t="s">
+      <c r="S62" s="5" t="s">
         <v>1607</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="B63" s="81" t="str">
+      <c r="B63" t="str">
         <f>IF(D63&lt;&gt;"",VLOOKUP(D63,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A64" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B64" s="81" t="str">
+      <c r="A64" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B64" t="str">
         <f>IF(D64&lt;&gt;"",VLOOKUP(D64,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C64" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D64" s="82" t="s">
+      <c r="C64" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D64" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="82"/>
-      <c r="F64" s="82" t="s">
+      <c r="E64" s="6"/>
+      <c r="F64" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G64" s="82"/>
-      <c r="H64" s="82" t="s">
+      <c r="G64" s="6"/>
+      <c r="H64" s="6" t="s">
         <v>1741</v>
       </c>
-      <c r="I64" s="82"/>
-      <c r="J64" s="82" t="s">
+      <c r="I64" s="6"/>
+      <c r="J64" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K64" s="82" t="s">
+      <c r="K64" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L64" s="82" t="s">
+      <c r="L64" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="M64" s="82" t="s">
+      <c r="M64" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N64" s="82"/>
-      <c r="O64" s="82" t="s">
+      <c r="N64" s="6"/>
+      <c r="O64" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P64" s="82"/>
-      <c r="Q64" s="82" t="s">
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6" t="s">
         <v>1619</v>
       </c>
-      <c r="R64" s="82" t="s">
+      <c r="R64" s="6" t="s">
         <v>1618</v>
       </c>
-      <c r="S64" s="83" t="s">
+      <c r="S64" s="5" t="s">
         <v>1620</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B65" s="81" t="str">
+      <c r="B65" t="str">
         <f>IF(D65&lt;&gt;"",VLOOKUP(D65,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A66" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B66" s="81" t="str">
+      <c r="A66" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B66" t="str">
         <f>IF(D66&lt;&gt;"",VLOOKUP(D66,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C66" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D66" s="82" t="s">
+      <c r="C66" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E66" s="82" t="s">
+      <c r="E66" s="6" t="s">
         <v>2004</v>
       </c>
-      <c r="F66" s="82" t="s">
+      <c r="F66" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G66" s="82" t="s">
+      <c r="G66" s="6" t="s">
         <v>1624</v>
       </c>
-      <c r="H66" s="82"/>
-      <c r="I66" s="82" t="s">
+      <c r="H66" s="6"/>
+      <c r="I66" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J66" s="82" t="s">
+      <c r="J66" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K66" s="82" t="s">
+      <c r="K66" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L66" s="82" t="s">
+      <c r="L66" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="M66" s="82" t="s">
+      <c r="M66" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N66" s="82"/>
-      <c r="O66" s="82" t="s">
+      <c r="N66" s="6"/>
+      <c r="O66" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P66" s="82"/>
-      <c r="Q66" s="82" t="s">
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6" t="s">
         <v>1622</v>
       </c>
-      <c r="R66" s="82" t="s">
+      <c r="R66" s="6" t="s">
         <v>1714</v>
       </c>
-      <c r="S66" s="83" t="s">
+      <c r="S66" s="5" t="s">
         <v>1629</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A67" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B67" s="81" t="str">
+      <c r="A67" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B67" t="str">
         <f>IF(D67&lt;&gt;"",VLOOKUP(D67,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C67" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D67" s="82" t="s">
+      <c r="C67" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D67" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E67" s="82" t="s">
+      <c r="E67" s="6" t="s">
         <v>1623</v>
       </c>
-      <c r="F67" s="82" t="s">
+      <c r="F67" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G67" s="82" t="s">
+      <c r="G67" s="6" t="s">
         <v>1626</v>
       </c>
-      <c r="H67" s="82"/>
-      <c r="I67" s="82" t="s">
+      <c r="H67" s="6"/>
+      <c r="I67" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J67" s="82" t="s">
+      <c r="J67" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K67" s="82" t="s">
+      <c r="K67" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L67" s="82" t="s">
+      <c r="L67" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="M67" s="82" t="s">
+      <c r="M67" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N67" s="82"/>
-      <c r="O67" s="82" t="s">
+      <c r="N67" s="6"/>
+      <c r="O67" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P67" s="82"/>
-      <c r="Q67" s="82" t="s">
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6" t="s">
         <v>1622</v>
       </c>
-      <c r="R67" s="82" t="s">
+      <c r="R67" s="6" t="s">
         <v>1714</v>
       </c>
-      <c r="S67" s="83" t="s">
+      <c r="S67" s="5" t="s">
         <v>1629</v>
       </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A68" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B68" s="81" t="str">
+      <c r="A68" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B68" t="str">
         <f>IF(D68&lt;&gt;"",VLOOKUP(D68,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C68" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D68" s="82" t="s">
+      <c r="C68" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D68" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E68" s="82" t="s">
+      <c r="E68" s="6" t="s">
         <v>2003</v>
       </c>
-      <c r="F68" s="82" t="s">
+      <c r="F68" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G68" s="82" t="s">
+      <c r="G68" s="6" t="s">
         <v>1625</v>
       </c>
-      <c r="H68" s="82"/>
-      <c r="I68" s="82" t="s">
+      <c r="H68" s="6"/>
+      <c r="I68" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J68" s="82" t="s">
+      <c r="J68" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K68" s="82" t="s">
+      <c r="K68" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L68" s="82" t="s">
+      <c r="L68" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="M68" s="82" t="s">
+      <c r="M68" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N68" s="82"/>
-      <c r="O68" s="82" t="s">
+      <c r="N68" s="6"/>
+      <c r="O68" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P68" s="82"/>
-      <c r="Q68" s="82" t="s">
+      <c r="P68" s="6"/>
+      <c r="Q68" s="6" t="s">
         <v>1622</v>
       </c>
-      <c r="R68" s="82" t="s">
+      <c r="R68" s="6" t="s">
         <v>1714</v>
       </c>
-      <c r="S68" s="83" t="s">
+      <c r="S68" s="5" t="s">
         <v>1629</v>
       </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A69" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B69" s="81" t="str">
+      <c r="A69" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B69" t="str">
         <f>IF(D69&lt;&gt;"",VLOOKUP(D69,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C69" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D69" s="82" t="s">
+      <c r="C69" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E69" s="82" t="s">
+      <c r="E69" s="6" t="s">
         <v>2001</v>
       </c>
-      <c r="F69" s="82" t="s">
+      <c r="F69" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G69" s="82" t="s">
+      <c r="G69" s="6" t="s">
         <v>1627</v>
       </c>
-      <c r="H69" s="82"/>
-      <c r="I69" s="82" t="s">
+      <c r="H69" s="6"/>
+      <c r="I69" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J69" s="82" t="s">
+      <c r="J69" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K69" s="82" t="s">
+      <c r="K69" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L69" s="82" t="s">
+      <c r="L69" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="M69" s="82" t="s">
+      <c r="M69" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N69" s="82"/>
-      <c r="O69" s="82" t="s">
+      <c r="N69" s="6"/>
+      <c r="O69" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P69" s="82"/>
-      <c r="Q69" s="82" t="s">
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6" t="s">
         <v>1622</v>
       </c>
-      <c r="R69" s="82" t="s">
+      <c r="R69" s="6" t="s">
         <v>1714</v>
       </c>
-      <c r="S69" s="83" t="s">
+      <c r="S69" s="5" t="s">
         <v>1629</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A70" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B70" s="81" t="str">
+      <c r="A70" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B70" t="str">
         <f>IF(D70&lt;&gt;"",VLOOKUP(D70,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sequence information</v>
       </c>
-      <c r="C70" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D70" s="82" t="s">
+      <c r="C70" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D70" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="E70" s="82" t="s">
+      <c r="E70" s="6" t="s">
         <v>2002</v>
       </c>
-      <c r="F70" s="82" t="s">
+      <c r="F70" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G70" s="82" t="s">
+      <c r="G70" s="6" t="s">
         <v>1628</v>
       </c>
-      <c r="H70" s="82"/>
-      <c r="I70" s="82" t="s">
+      <c r="H70" s="6"/>
+      <c r="I70" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J70" s="82" t="s">
+      <c r="J70" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K70" s="82" t="s">
+      <c r="K70" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L70" s="82" t="s">
+      <c r="L70" s="6" t="s">
         <v>1117</v>
       </c>
-      <c r="M70" s="82" t="s">
+      <c r="M70" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N70" s="82"/>
-      <c r="O70" s="82" t="s">
+      <c r="N70" s="6"/>
+      <c r="O70" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P70" s="82"/>
-      <c r="Q70" s="82" t="s">
+      <c r="P70" s="6"/>
+      <c r="Q70" s="6" t="s">
         <v>1622</v>
       </c>
-      <c r="R70" s="82" t="s">
+      <c r="R70" s="6" t="s">
         <v>1714</v>
       </c>
-      <c r="S70" s="83" t="s">
+      <c r="S70" s="5" t="s">
         <v>1629</v>
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B71" s="81" t="str">
+      <c r="B71" t="str">
         <f>IF(D71&lt;&gt;"",VLOOKUP(D71,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A72" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B72" s="81" t="str">
+      <c r="A72" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B72" t="str">
         <f>IF(D72&lt;&gt;"",VLOOKUP(D72,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Strain and isolation information</v>
       </c>
-      <c r="C72" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D72" s="82" t="s">
+      <c r="C72" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D72" s="6" t="s">
         <v>1113</v>
       </c>
-      <c r="E72" s="82"/>
-      <c r="F72" s="82" t="s">
+      <c r="E72" s="6"/>
+      <c r="F72" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G72" s="82"/>
-      <c r="H72" s="82" t="s">
+      <c r="G72" s="6"/>
+      <c r="H72" s="6" t="s">
         <v>1658</v>
       </c>
-      <c r="I72" s="82"/>
-      <c r="J72" s="82" t="s">
+      <c r="I72" s="6"/>
+      <c r="J72" s="6" t="s">
         <v>1107</v>
       </c>
-      <c r="K72" s="82" t="s">
+      <c r="K72" s="6" t="s">
         <v>1107</v>
       </c>
-      <c r="L72" s="82" t="s">
+      <c r="L72" s="6" t="s">
         <v>1113</v>
       </c>
-      <c r="M72" s="82" t="s">
+      <c r="M72" s="6" t="s">
         <v>1990</v>
       </c>
-      <c r="N72" s="82"/>
-      <c r="O72" s="82" t="s">
+      <c r="N72" s="6"/>
+      <c r="O72" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P72" s="82" t="s">
+      <c r="P72" s="6" t="s">
         <v>1656</v>
       </c>
-      <c r="Q72" s="82"/>
-      <c r="R72" s="82" t="s">
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6" t="s">
         <v>1652</v>
       </c>
-      <c r="S72" s="83" t="s">
+      <c r="S72" s="5" t="s">
         <v>1659</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B73" s="81" t="str">
+      <c r="B73" t="str">
         <f>IF(D73&lt;&gt;"",VLOOKUP(D73,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A74" s="82" t="b">
-        <v>1</v>
-      </c>
-      <c r="B74" s="81" t="str">
+      <c r="A74" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B74" t="str">
         <f>IF(D74&lt;&gt;"",VLOOKUP(D74,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Taxonomic identification information</v>
       </c>
-      <c r="C74" s="82" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D74" s="82" t="s">
+      <c r="C74" s="6" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E74" s="82"/>
-      <c r="F74" s="82" t="s">
+      <c r="E74" s="6"/>
+      <c r="F74" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="G74" s="82"/>
-      <c r="H74" s="82"/>
-      <c r="I74" s="82"/>
-      <c r="J74" s="82" t="s">
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="K74" s="82" t="s">
+      <c r="K74" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="L74" s="82" t="s">
+      <c r="L74" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M74" s="82" t="s">
+      <c r="M74" s="6" t="s">
         <v>2075</v>
       </c>
-      <c r="N74" s="82"/>
-      <c r="O74" s="82" t="s">
+      <c r="N74" s="6"/>
+      <c r="O74" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="P74" s="82" t="s">
+      <c r="P74" s="6" t="s">
         <v>1657</v>
       </c>
-      <c r="Q74" s="82"/>
-      <c r="R74" s="82" t="s">
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6" t="s">
         <v>1655</v>
       </c>
-      <c r="S74" s="83" t="s">
+      <c r="S74" s="5" t="s">
         <v>1659</v>
       </c>
     </row>
@@ -37892,7 +37886,6 @@
       <c r="C28" t="s">
         <v>1809</v>
       </c>
-      <c r="D28" s="85"/>
       <c r="F28" t="s">
         <v>1400</v>
       </c>
@@ -37919,7 +37912,6 @@
       <c r="C29" t="s">
         <v>1809</v>
       </c>
-      <c r="D29" s="85"/>
       <c r="F29" t="s">
         <v>1400</v>
       </c>
@@ -37946,7 +37938,6 @@
       <c r="C30" t="s">
         <v>1809</v>
       </c>
-      <c r="D30" s="85"/>
       <c r="F30" t="s">
         <v>1400</v>
       </c>
@@ -37973,7 +37964,6 @@
       <c r="C31" t="s">
         <v>1809</v>
       </c>
-      <c r="D31" s="85"/>
       <c r="F31" t="s">
         <v>1400</v>
       </c>
@@ -63039,7 +63029,7 @@
         <v>1803</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>1791</v>
+        <v>2089</v>
       </c>
       <c r="M1" s="17" t="s">
         <v>1804</v>

--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32979847-AEA8-4A44-B26C-105F0E4A8CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AD8CCF-E901-144F-917B-C6FBFA573CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="660" windowWidth="40800" windowHeight="20740" firstSheet="19" activeTab="22" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
@@ -39832,7 +39832,7 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="str">
         <f>IF(D30&lt;&gt;"",VLOOKUP(D30,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
@@ -39862,7 +39862,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="str">
         <f>IF(D31&lt;&gt;"",VLOOKUP(D31,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>

--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E194AF8-2581-3141-9B84-699B1BF5AD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D6475E-DF38-194C-85F2-B12A319B9DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="660" windowWidth="40800" windowHeight="20740" firstSheet="10" activeTab="11" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="40800" windowHeight="20740" firstSheet="19" activeTab="28" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="global_enums" sheetId="42" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9757" uniqueCount="2120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9776" uniqueCount="2122">
   <si>
     <t>Complete</t>
   </si>
@@ -6480,9 +6480,6 @@
     target = emap.collection_method</t>
   </si>
   <si>
-    <t>{ mirror_source: True }</t>
-  </si>
-  <si>
     <t>enumDerivationSettings</t>
   </si>
   <si>
@@ -6512,6 +6509,19 @@
   </si>
   <si>
     <t>{{quality control determination}}</t>
+  </si>
+  <si>
+    <t>{ mirror_source: False }</t>
+  </si>
+  <si>
+    <t>pooled</t>
+  </si>
+  <si>
+    <t>def is_pooled(values):
+    values = [v.lower().split('[')[0].strip() for v in values if isinstance(v, str)]
+    values = [v for v in values if v == "pooling specimens"]
+    return len(values) &gt; 0
+target = is_pooled(src.specimen_processing)</t>
   </si>
 </sst>
 </file>
@@ -6845,7 +6855,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -7002,6 +7012,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -21045,7 +21059,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -21059,7 +21073,7 @@
         <v>441</v>
       </c>
       <c r="D2" t="s">
-        <v>2110</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -26462,7 +26476,7 @@
         <v>1906</v>
       </c>
       <c r="S1" s="16" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="T1" s="17" t="s">
         <v>1734</v>
@@ -32683,7 +32697,7 @@
         <v>2093</v>
       </c>
       <c r="S139" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="T139" t="s">
         <v>1917</v>
@@ -35338,7 +35352,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E19831EB-F90F-BD49-AC5C-0138EB88F455}">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:U74"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
@@ -37372,54 +37386,59 @@
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A51" t="b">
+        <v>1</v>
+      </c>
       <c r="B51" t="str">
         <f>IF(D51&lt;&gt;"",VLOOKUP(D51,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D51" t="s">
+        <v>128</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J51" t="s">
+        <v>127</v>
+      </c>
+      <c r="K51" t="s">
+        <v>127</v>
+      </c>
+      <c r="L51" t="s">
+        <v>128</v>
+      </c>
+      <c r="M51" t="s">
+        <v>121</v>
+      </c>
+      <c r="N51" t="s">
+        <v>1506</v>
+      </c>
+      <c r="O51" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q51" s="8" t="s">
+        <v>2102</v>
+      </c>
+      <c r="R51" s="8"/>
+      <c r="S51" s="8"/>
+      <c r="T51" t="s">
+        <v>1513</v>
+      </c>
+      <c r="U51" t="s">
+        <v>1511</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A52" t="b">
-        <v>1</v>
-      </c>
       <c r="B52" t="str">
         <f>IF(D52&lt;&gt;"",VLOOKUP(D52,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>AMR detection information</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F52" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H52" t="s">
-        <v>1664</v>
-      </c>
-      <c r="J52" t="s">
-        <v>1105</v>
-      </c>
-      <c r="K52" t="s">
-        <v>1105</v>
-      </c>
-      <c r="L52" t="s">
-        <v>1112</v>
-      </c>
-      <c r="M52" t="s">
-        <v>2099</v>
-      </c>
-      <c r="O52" t="s">
-        <v>1027</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>1528</v>
-      </c>
-      <c r="R52" t="s">
-        <v>1634</v>
-      </c>
-      <c r="T52" t="s">
-        <v>1529</v>
+        <v/>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.2">
@@ -37428,19 +37447,19 @@
       </c>
       <c r="B53" t="str">
         <f>IF(D53&lt;&gt;"",VLOOKUP(D53,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Bioinformatics and QC metrics</v>
+        <v>AMR detection information</v>
       </c>
       <c r="C53" t="s">
         <v>1751</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>1112</v>
       </c>
       <c r="F53" t="s">
         <v>1226</v>
       </c>
       <c r="H53" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="J53" t="s">
         <v>1105</v>
@@ -37449,22 +37468,22 @@
         <v>1105</v>
       </c>
       <c r="L53" t="s">
-        <v>13</v>
+        <v>1112</v>
       </c>
       <c r="M53" t="s">
-        <v>121</v>
+        <v>2099</v>
       </c>
       <c r="O53" t="s">
         <v>1027</v>
       </c>
       <c r="Q53" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="R53" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="T53" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.2">
@@ -37479,11 +37498,14 @@
         <v>1751</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F54" t="s">
         <v>1226</v>
       </c>
+      <c r="H54" t="s">
+        <v>1661</v>
+      </c>
       <c r="J54" t="s">
         <v>1105</v>
       </c>
@@ -37491,7 +37513,7 @@
         <v>1105</v>
       </c>
       <c r="L54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M54" t="s">
         <v>121</v>
@@ -37500,10 +37522,10 @@
         <v>1027</v>
       </c>
       <c r="Q54" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="R54" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="T54" t="s">
         <v>1533</v>
@@ -37521,7 +37543,7 @@
         <v>1751</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F55" t="s">
         <v>1226</v>
@@ -37533,7 +37555,7 @@
         <v>1105</v>
       </c>
       <c r="L55" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M55" t="s">
         <v>121</v>
@@ -37542,10 +37564,10 @@
         <v>1027</v>
       </c>
       <c r="Q55" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="R55" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="T55" t="s">
         <v>1533</v>
@@ -37563,7 +37585,7 @@
         <v>1751</v>
       </c>
       <c r="D56" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="F56" t="s">
         <v>1226</v>
@@ -37575,7 +37597,7 @@
         <v>1105</v>
       </c>
       <c r="L56" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="M56" t="s">
         <v>121</v>
@@ -37584,10 +37606,10 @@
         <v>1027</v>
       </c>
       <c r="Q56" t="s">
-        <v>1539</v>
+        <v>1535</v>
       </c>
       <c r="R56" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="T56" t="s">
         <v>1533</v>
@@ -37605,14 +37627,11 @@
         <v>1751</v>
       </c>
       <c r="D57" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F57" t="s">
         <v>1226</v>
       </c>
-      <c r="H57" t="s">
-        <v>1662</v>
-      </c>
       <c r="J57" t="s">
         <v>1105</v>
       </c>
@@ -37620,7 +37639,7 @@
         <v>1105</v>
       </c>
       <c r="L57" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M57" t="s">
         <v>121</v>
@@ -37629,10 +37648,10 @@
         <v>1027</v>
       </c>
       <c r="Q57" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="R57" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="T57" t="s">
         <v>1533</v>
@@ -37644,19 +37663,19 @@
       </c>
       <c r="B58" t="str">
         <f>IF(D58&lt;&gt;"",VLOOKUP(D58,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Lineage/clade information</v>
+        <v>Bioinformatics and QC metrics</v>
       </c>
       <c r="C58" t="s">
         <v>1751</v>
       </c>
       <c r="D58" t="s">
-        <v>1119</v>
+        <v>95</v>
       </c>
       <c r="F58" t="s">
         <v>1226</v>
       </c>
       <c r="H58" t="s">
-        <v>2021</v>
+        <v>1662</v>
       </c>
       <c r="J58" t="s">
         <v>1105</v>
@@ -37665,7 +37684,7 @@
         <v>1105</v>
       </c>
       <c r="L58" t="s">
-        <v>1119</v>
+        <v>95</v>
       </c>
       <c r="M58" t="s">
         <v>121</v>
@@ -37674,224 +37693,218 @@
         <v>1027</v>
       </c>
       <c r="Q58" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="R58" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="T58" t="s">
-        <v>1542</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A59" t="b">
+        <v>1</v>
+      </c>
       <c r="B59" t="str">
         <f>IF(D59&lt;&gt;"",VLOOKUP(D59,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
+        <v>Lineage/clade information</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H59" t="s">
+        <v>2021</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K59" t="s">
+        <v>1105</v>
+      </c>
+      <c r="L59" t="s">
+        <v>1119</v>
+      </c>
+      <c r="M59" t="s">
+        <v>121</v>
+      </c>
+      <c r="O59" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>1541</v>
+      </c>
+      <c r="R59" t="s">
+        <v>1640</v>
+      </c>
+      <c r="T59" t="s">
+        <v>1542</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A60" t="b">
-        <v>1</v>
-      </c>
       <c r="B60" t="str">
         <f>IF(D60&lt;&gt;"",VLOOKUP(D60,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1784</v>
-      </c>
-      <c r="F60" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H60" t="s">
-        <v>1951</v>
-      </c>
-      <c r="J60" t="s">
-        <v>127</v>
-      </c>
-      <c r="K60" t="s">
-        <v>127</v>
-      </c>
-      <c r="L60" t="s">
-        <v>1784</v>
-      </c>
-      <c r="M60" t="s">
-        <v>121</v>
-      </c>
-      <c r="O60" t="s">
-        <v>1027</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>1549</v>
-      </c>
-      <c r="R60" t="s">
-        <v>1952</v>
-      </c>
-      <c r="T60" t="s">
-        <v>1550</v>
+        <v/>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A61" t="b">
+        <v>1</v>
+      </c>
       <c r="B61" t="str">
         <f>IF(D61&lt;&gt;"",VLOOKUP(D61,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1951</v>
+      </c>
+      <c r="J61" t="s">
+        <v>127</v>
+      </c>
+      <c r="K61" t="s">
+        <v>127</v>
+      </c>
+      <c r="L61" t="s">
+        <v>1784</v>
+      </c>
+      <c r="M61" t="s">
+        <v>121</v>
+      </c>
+      <c r="O61" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>1549</v>
+      </c>
+      <c r="R61" t="s">
+        <v>1952</v>
+      </c>
+      <c r="T61" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A62" t="b">
-        <v>1</v>
-      </c>
       <c r="B62" t="str">
         <f>IF(D62&lt;&gt;"",VLOOKUP(D62,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D62" t="s">
-        <v>125</v>
-      </c>
-      <c r="F62" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G62" s="9"/>
-      <c r="H62" t="s">
-        <v>1681</v>
-      </c>
-      <c r="J62" t="s">
-        <v>127</v>
-      </c>
-      <c r="K62" t="s">
-        <v>127</v>
-      </c>
-      <c r="L62" t="s">
-        <v>125</v>
-      </c>
-      <c r="M62" t="s">
-        <v>121</v>
-      </c>
-      <c r="O62" t="s">
-        <v>1027</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>1560</v>
-      </c>
-      <c r="R62" t="s">
-        <v>1559</v>
-      </c>
-      <c r="T62" t="s">
-        <v>1561</v>
+        <v/>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A63" t="b">
+        <v>1</v>
+      </c>
       <c r="B63" t="str">
         <f>IF(D63&lt;&gt;"",VLOOKUP(D63,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D63" t="s">
+        <v>125</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G63" s="9"/>
+      <c r="H63" t="s">
+        <v>1681</v>
+      </c>
+      <c r="J63" t="s">
+        <v>127</v>
+      </c>
+      <c r="K63" t="s">
+        <v>127</v>
+      </c>
+      <c r="L63" t="s">
+        <v>125</v>
+      </c>
+      <c r="M63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O63" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>1560</v>
+      </c>
+      <c r="R63" t="s">
+        <v>1559</v>
+      </c>
+      <c r="T63" t="s">
+        <v>1561</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A64" t="b">
-        <v>1</v>
-      </c>
       <c r="B64" t="str">
         <f>IF(D64&lt;&gt;"",VLOOKUP(D64,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D64" t="s">
-        <v>89</v>
-      </c>
-      <c r="F64" t="s">
-        <v>1226</v>
-      </c>
-      <c r="H64" t="s">
-        <v>1684</v>
-      </c>
-      <c r="J64" t="s">
-        <v>1105</v>
-      </c>
-      <c r="K64" t="s">
-        <v>1105</v>
-      </c>
-      <c r="L64" t="s">
-        <v>89</v>
-      </c>
-      <c r="M64" t="s">
-        <v>121</v>
-      </c>
-      <c r="O64" t="s">
-        <v>1027</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>1573</v>
-      </c>
-      <c r="R64" t="s">
-        <v>1572</v>
-      </c>
-      <c r="T64" t="s">
-        <v>1574</v>
+        <v/>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A65" t="b">
+        <v>1</v>
+      </c>
       <c r="B65" t="str">
         <f>IF(D65&lt;&gt;"",VLOOKUP(D65,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
+        <v>Sequence information</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D65" t="s">
+        <v>89</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1684</v>
+      </c>
+      <c r="J65" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K65" t="s">
+        <v>1105</v>
+      </c>
+      <c r="L65" t="s">
+        <v>89</v>
+      </c>
+      <c r="M65" t="s">
+        <v>121</v>
+      </c>
+      <c r="O65" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>1573</v>
+      </c>
+      <c r="R65" t="s">
+        <v>1572</v>
+      </c>
+      <c r="T65" t="s">
+        <v>1574</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A66" t="b">
-        <v>1</v>
-      </c>
       <c r="B66" t="str">
         <f>IF(D66&lt;&gt;"",VLOOKUP(D66,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sequence information</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D66" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E66" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F66" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G66" t="s">
-        <v>1578</v>
-      </c>
-      <c r="I66" t="s">
-        <v>19</v>
-      </c>
-      <c r="J66" t="s">
-        <v>1105</v>
-      </c>
-      <c r="K66" t="s">
-        <v>1105</v>
-      </c>
-      <c r="L66" t="s">
-        <v>1107</v>
-      </c>
-      <c r="M66" t="s">
-        <v>121</v>
-      </c>
-      <c r="O66" t="s">
-        <v>1027</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>1576</v>
-      </c>
-      <c r="R66" t="s">
-        <v>1660</v>
-      </c>
-      <c r="T66" t="s">
-        <v>1583</v>
+        <v/>
       </c>
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.2">
@@ -37909,13 +37922,13 @@
         <v>1107</v>
       </c>
       <c r="E67" t="s">
-        <v>1577</v>
+        <v>1937</v>
       </c>
       <c r="F67" t="s">
         <v>1226</v>
       </c>
       <c r="G67" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -37960,13 +37973,13 @@
         <v>1107</v>
       </c>
       <c r="E68" t="s">
-        <v>1936</v>
+        <v>1577</v>
       </c>
       <c r="F68" t="s">
         <v>1226</v>
       </c>
       <c r="G68" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
@@ -38011,13 +38024,13 @@
         <v>1107</v>
       </c>
       <c r="E69" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="F69" t="s">
         <v>1226</v>
       </c>
       <c r="G69" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="I69" t="s">
         <v>19</v>
@@ -38062,13 +38075,13 @@
         <v>1107</v>
       </c>
       <c r="E70" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="F70" t="s">
         <v>1226</v>
       </c>
       <c r="G70" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="I70" t="s">
         <v>19</v>
@@ -38099,101 +38112,152 @@
       </c>
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A71" t="b">
+        <v>1</v>
+      </c>
       <c r="B71" t="str">
         <f>IF(D71&lt;&gt;"",VLOOKUP(D71,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
+        <v>Sequence information</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1935</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1582</v>
+      </c>
+      <c r="I71" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K71" t="s">
+        <v>1105</v>
+      </c>
+      <c r="L71" t="s">
+        <v>1107</v>
+      </c>
+      <c r="M71" t="s">
+        <v>121</v>
+      </c>
+      <c r="O71" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>1576</v>
+      </c>
+      <c r="R71" t="s">
+        <v>1660</v>
+      </c>
+      <c r="T71" t="s">
+        <v>1583</v>
       </c>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A72" t="b">
-        <v>1</v>
-      </c>
       <c r="B72" t="str">
         <f>IF(D72&lt;&gt;"",VLOOKUP(D72,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Strain and isolation information</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D72" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F72" t="s">
-        <v>1226</v>
-      </c>
-      <c r="J72" t="s">
-        <v>1097</v>
-      </c>
-      <c r="K72" t="s">
-        <v>1097</v>
-      </c>
-      <c r="L72" t="s">
-        <v>1103</v>
-      </c>
-      <c r="M72" t="s">
-        <v>2101</v>
-      </c>
-      <c r="O72" t="s">
-        <v>1027</v>
-      </c>
-      <c r="P72" t="s">
-        <v>1609</v>
-      </c>
-      <c r="R72" t="s">
-        <v>1605</v>
-      </c>
-      <c r="T72" t="s">
-        <v>1611</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A73" t="b">
+        <v>1</v>
+      </c>
       <c r="B73" t="str">
         <f>IF(D73&lt;&gt;"",VLOOKUP(D73,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
+        <v>Strain and isolation information</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J73" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K73" t="s">
+        <v>1097</v>
+      </c>
+      <c r="L73" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M73" t="s">
+        <v>2101</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1027</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1609</v>
+      </c>
+      <c r="R73" t="s">
+        <v>1605</v>
+      </c>
+      <c r="T73" t="s">
+        <v>1611</v>
       </c>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A74" t="b">
-        <v>1</v>
-      </c>
       <c r="B74" t="str">
         <f>IF(D74&lt;&gt;"",VLOOKUP(D74,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A75" t="b">
+        <v>1</v>
+      </c>
+      <c r="B75" t="str">
+        <f>IF(D75&lt;&gt;"",VLOOKUP(D75,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Taxonomic identification information</v>
       </c>
-      <c r="C74" t="s">
-        <v>1751</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C75" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D75" t="s">
         <v>91</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F75" t="s">
         <v>1226</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H75" t="s">
         <v>2023</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J75" t="s">
         <v>1105</v>
       </c>
-      <c r="K74" t="s">
+      <c r="K75" t="s">
         <v>1105</v>
       </c>
-      <c r="L74" t="s">
+      <c r="L75" t="s">
         <v>91</v>
       </c>
-      <c r="M74" t="s">
+      <c r="M75" t="s">
         <v>121</v>
       </c>
-      <c r="O74" t="s">
+      <c r="O75" t="s">
         <v>1027</v>
       </c>
-      <c r="P74" t="s">
+      <c r="P75" t="s">
         <v>1610</v>
       </c>
-      <c r="R74" t="s">
+      <c r="R75" t="s">
         <v>1608</v>
       </c>
-      <c r="T74" t="s">
+      <c r="T75" t="s">
         <v>1611</v>
       </c>
     </row>
@@ -40390,7 +40454,7 @@
         <v>1250</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>2095</v>
@@ -42701,7 +42765,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E39206-1F1B-2D4B-82A5-94676E67F7A4}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -43478,6 +43542,36 @@
       </c>
       <c r="P20" s="24" t="s">
         <v>1754</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="78" customFormat="1" ht="119" x14ac:dyDescent="0.2">
+      <c r="B22" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22" s="78" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="78" t="str">
+        <f>IF(G22&lt;&gt;"",VLOOKUP(G22,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>1751</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>2120</v>
+      </c>
+      <c r="L22" s="79" t="s">
+        <v>2121</v>
       </c>
     </row>
   </sheetData>
@@ -54585,7 +54679,7 @@
         <v>1178</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>127</v>
@@ -64381,10 +64475,10 @@
         <v>1957</v>
       </c>
       <c r="J1" s="10" t="s">
+        <v>2114</v>
+      </c>
+      <c r="K1" s="10" t="s">
         <v>2115</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>2116</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>1964</v>
@@ -64643,7 +64737,7 @@
       </c>
       <c r="L4" s="15"/>
       <c r="M4" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N4" s="15"/>
       <c r="O4" s="18" t="s">
@@ -64685,7 +64779,7 @@
       </c>
       <c r="L5" s="15"/>
       <c r="M5" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N5" s="15"/>
       <c r="O5" s="18" t="s">
@@ -64727,7 +64821,7 @@
       </c>
       <c r="L6" s="15"/>
       <c r="M6" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N6" s="15"/>
       <c r="O6" s="18" t="s">
@@ -64769,7 +64863,7 @@
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N7" s="15"/>
       <c r="O7" s="18" t="s">
@@ -64811,7 +64905,7 @@
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N8" s="15"/>
       <c r="O8" s="18" t="s">
@@ -64853,7 +64947,7 @@
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N9" s="15"/>
       <c r="O9" s="18" t="s">
@@ -64895,7 +64989,7 @@
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N10" s="15"/>
       <c r="O10" s="18" t="s">
@@ -64937,7 +65031,7 @@
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="18" t="s">
@@ -64979,7 +65073,7 @@
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N12" s="15"/>
       <c r="O12" s="18" t="s">
@@ -65021,7 +65115,7 @@
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="18" t="s">
@@ -65063,7 +65157,7 @@
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N14" s="15"/>
       <c r="O14" s="18" t="s">
@@ -65105,7 +65199,7 @@
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="18" t="s">
@@ -65147,7 +65241,7 @@
       </c>
       <c r="L16" s="15"/>
       <c r="M16" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="18" t="s">
@@ -65189,7 +65283,7 @@
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N17" s="15"/>
       <c r="O17" s="18" t="s">
@@ -65231,7 +65325,7 @@
       </c>
       <c r="L18" s="15"/>
       <c r="M18" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N18" s="15"/>
       <c r="O18" s="18" t="s">
@@ -65273,7 +65367,7 @@
       </c>
       <c r="L19" s="15"/>
       <c r="M19" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N19" s="15"/>
       <c r="O19" s="18" t="s">
@@ -65315,7 +65409,7 @@
       </c>
       <c r="L20" s="15"/>
       <c r="M20" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N20" s="15"/>
       <c r="O20" s="18" t="s">
@@ -65357,7 +65451,7 @@
       </c>
       <c r="L21" s="15"/>
       <c r="M21" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N21" s="15"/>
       <c r="O21" s="18" t="s">
@@ -65399,7 +65493,7 @@
       </c>
       <c r="L22" s="15"/>
       <c r="M22" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N22" s="15"/>
       <c r="O22" s="18" t="s">
@@ -65441,7 +65535,7 @@
       </c>
       <c r="L23" s="15"/>
       <c r="M23" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N23" s="15"/>
       <c r="O23" s="18" t="s">
@@ -65483,7 +65577,7 @@
       </c>
       <c r="L24" s="15"/>
       <c r="M24" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N24" s="15"/>
       <c r="O24" s="18" t="s">
@@ -65525,7 +65619,7 @@
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N25" s="15"/>
       <c r="O25" s="18" t="s">
@@ -65567,7 +65661,7 @@
       </c>
       <c r="L26" s="15"/>
       <c r="M26" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N26" s="15"/>
       <c r="O26" s="18" t="s">
@@ -65609,7 +65703,7 @@
       </c>
       <c r="L27" s="15"/>
       <c r="M27" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N27" s="15"/>
       <c r="O27" s="18" t="s">
@@ -65651,7 +65745,7 @@
       </c>
       <c r="L28" s="15"/>
       <c r="M28" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N28" s="15"/>
       <c r="O28" s="18" t="s">
@@ -65693,7 +65787,7 @@
       </c>
       <c r="L29" s="15"/>
       <c r="M29" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N29" s="15"/>
       <c r="O29" s="18" t="s">
@@ -65735,7 +65829,7 @@
       </c>
       <c r="L30" s="15"/>
       <c r="M30" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N30" s="15"/>
       <c r="O30" s="18" t="s">
@@ -65777,7 +65871,7 @@
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N31" s="15"/>
       <c r="O31" s="18" t="s">
@@ -65819,7 +65913,7 @@
       </c>
       <c r="L32" s="15"/>
       <c r="M32" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N32" s="15"/>
       <c r="O32" s="18" t="s">
@@ -65861,7 +65955,7 @@
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N33" s="15"/>
       <c r="O33" s="18" t="s">
@@ -65903,7 +65997,7 @@
       </c>
       <c r="L34" s="15"/>
       <c r="M34" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N34" s="15"/>
       <c r="O34" s="18" t="s">
@@ -65945,7 +66039,7 @@
       </c>
       <c r="L35" s="15"/>
       <c r="M35" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N35" s="15"/>
       <c r="O35" s="18" t="s">
@@ -65987,7 +66081,7 @@
       </c>
       <c r="L36" s="15"/>
       <c r="M36" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N36" s="15"/>
       <c r="O36" s="18" t="s">
@@ -66029,7 +66123,7 @@
       </c>
       <c r="L37" s="15"/>
       <c r="M37" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N37" s="15"/>
       <c r="O37" s="18" t="s">
@@ -66071,7 +66165,7 @@
       </c>
       <c r="L38" s="15"/>
       <c r="M38" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N38" s="15"/>
       <c r="O38" s="18" t="s">
@@ -66113,7 +66207,7 @@
       </c>
       <c r="L39" s="15"/>
       <c r="M39" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N39" s="15"/>
       <c r="O39" s="18" t="s">
@@ -66155,7 +66249,7 @@
       </c>
       <c r="L40" s="15"/>
       <c r="M40" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N40" s="15"/>
       <c r="O40" s="18" t="s">
@@ -66197,7 +66291,7 @@
       </c>
       <c r="L41" s="15"/>
       <c r="M41" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N41" s="15"/>
       <c r="O41" s="18" t="s">
@@ -66239,7 +66333,7 @@
       </c>
       <c r="L42" s="15"/>
       <c r="M42" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N42" s="15"/>
       <c r="O42" s="18" t="s">
@@ -66281,7 +66375,7 @@
       </c>
       <c r="L43" s="15"/>
       <c r="M43" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N43" s="15"/>
       <c r="O43" s="18" t="s">
@@ -66323,7 +66417,7 @@
       </c>
       <c r="L44" s="15"/>
       <c r="M44" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N44" s="15"/>
       <c r="O44" s="18" t="s">
@@ -66365,7 +66459,7 @@
       </c>
       <c r="L45" s="15"/>
       <c r="M45" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N45" s="15"/>
       <c r="O45" s="18" t="s">
@@ -66407,7 +66501,7 @@
       </c>
       <c r="L46" s="15"/>
       <c r="M46" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N46" s="15"/>
       <c r="O46" s="18" t="s">
@@ -66449,7 +66543,7 @@
       </c>
       <c r="L47" s="15"/>
       <c r="M47" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N47" s="15"/>
       <c r="O47" s="18" t="s">
@@ -66491,7 +66585,7 @@
       </c>
       <c r="L48" s="15"/>
       <c r="M48" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N48" s="15"/>
       <c r="O48" s="18" t="s">
@@ -66533,7 +66627,7 @@
       </c>
       <c r="L49" s="15"/>
       <c r="M49" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N49" s="15"/>
       <c r="O49" s="18" t="s">
@@ -66575,7 +66669,7 @@
       </c>
       <c r="L50" s="15"/>
       <c r="M50" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N50" s="15"/>
       <c r="O50" s="18" t="s">
@@ -66617,7 +66711,7 @@
       </c>
       <c r="L51" s="15"/>
       <c r="M51" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N51" s="15"/>
       <c r="O51" s="18" t="s">
@@ -66659,7 +66753,7 @@
       </c>
       <c r="L52" s="15"/>
       <c r="M52" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N52" s="15"/>
       <c r="O52" s="18" t="s">
@@ -66701,7 +66795,7 @@
       </c>
       <c r="L53" s="15"/>
       <c r="M53" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N53" s="15"/>
       <c r="O53" s="18" t="s">
@@ -66743,7 +66837,7 @@
       </c>
       <c r="L54" s="15"/>
       <c r="M54" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N54" s="15"/>
       <c r="O54" s="18" t="s">
@@ -66785,7 +66879,7 @@
       </c>
       <c r="L55" s="15"/>
       <c r="M55" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N55" s="15"/>
       <c r="O55" s="18" t="s">
@@ -66827,7 +66921,7 @@
       </c>
       <c r="L56" s="15"/>
       <c r="M56" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N56" s="15"/>
       <c r="O56" s="18" t="s">
@@ -66869,7 +66963,7 @@
       </c>
       <c r="L57" s="15"/>
       <c r="M57" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N57" s="15"/>
       <c r="O57" s="18" t="s">
@@ -66911,7 +67005,7 @@
       </c>
       <c r="L58" s="15"/>
       <c r="M58" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N58" s="15"/>
       <c r="O58" s="18" t="s">
@@ -66953,7 +67047,7 @@
       </c>
       <c r="L59" s="15"/>
       <c r="M59" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N59" s="15"/>
       <c r="O59" s="18" t="s">
@@ -66995,7 +67089,7 @@
       </c>
       <c r="L60" s="15"/>
       <c r="M60" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N60" s="15"/>
       <c r="O60" s="18" t="s">
@@ -67037,7 +67131,7 @@
       </c>
       <c r="L61" s="15"/>
       <c r="M61" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N61" s="15"/>
       <c r="O61" s="18" t="s">
@@ -67079,7 +67173,7 @@
       </c>
       <c r="L62" s="15"/>
       <c r="M62" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N62" s="15"/>
       <c r="O62" s="18" t="s">
@@ -67121,7 +67215,7 @@
       </c>
       <c r="L63" s="15"/>
       <c r="M63" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N63" s="15"/>
       <c r="O63" s="18" t="s">
@@ -67163,7 +67257,7 @@
       </c>
       <c r="L64" s="15"/>
       <c r="M64" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N64" s="15"/>
       <c r="O64" s="18" t="s">
@@ -67205,7 +67299,7 @@
       </c>
       <c r="L65" s="15"/>
       <c r="M65" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N65" s="15"/>
       <c r="O65" s="18" t="s">
@@ -67247,7 +67341,7 @@
       </c>
       <c r="L66" s="15"/>
       <c r="M66" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N66" s="15"/>
       <c r="O66" s="18" t="s">
@@ -67289,7 +67383,7 @@
       </c>
       <c r="L67" s="15"/>
       <c r="M67" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N67" s="15"/>
       <c r="O67" s="18" t="s">
@@ -67331,7 +67425,7 @@
       </c>
       <c r="L68" s="15"/>
       <c r="M68" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N68" s="15"/>
       <c r="O68" s="18" t="s">
@@ -67373,7 +67467,7 @@
       </c>
       <c r="L69" s="15"/>
       <c r="M69" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N69" s="15"/>
       <c r="O69" s="18" t="s">
@@ -67415,7 +67509,7 @@
       </c>
       <c r="L70" s="15"/>
       <c r="M70" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N70" s="15"/>
       <c r="O70" s="18" t="s">
@@ -67457,7 +67551,7 @@
       </c>
       <c r="L71" s="15"/>
       <c r="M71" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N71" s="15"/>
       <c r="O71" s="18" t="s">
@@ -67499,7 +67593,7 @@
       </c>
       <c r="L72" s="15"/>
       <c r="M72" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N72" s="15"/>
       <c r="O72" s="18" t="s">
@@ -67541,7 +67635,7 @@
       </c>
       <c r="L73" s="15"/>
       <c r="M73" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N73" s="15"/>
       <c r="O73" s="18" t="s">
@@ -67583,7 +67677,7 @@
       </c>
       <c r="L74" s="15"/>
       <c r="M74" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N74" s="15"/>
       <c r="O74" s="18" t="s">
@@ -67625,7 +67719,7 @@
       </c>
       <c r="L75" s="15"/>
       <c r="M75" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N75" s="15"/>
       <c r="O75" s="18" t="s">
@@ -67667,7 +67761,7 @@
       </c>
       <c r="L76" s="15"/>
       <c r="M76" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N76" s="15"/>
       <c r="O76" s="18" t="s">
@@ -67709,7 +67803,7 @@
       </c>
       <c r="L77" s="15"/>
       <c r="M77" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N77" s="15"/>
       <c r="O77" s="18" t="s">
@@ -67751,7 +67845,7 @@
       </c>
       <c r="L78" s="15"/>
       <c r="M78" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N78" s="15"/>
       <c r="O78" s="18" t="s">
@@ -67793,7 +67887,7 @@
       </c>
       <c r="L79" s="15"/>
       <c r="M79" s="15" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="N79" s="15"/>
       <c r="O79" s="18" t="s">
@@ -67855,7 +67949,7 @@
       </c>
       <c r="L81" s="15"/>
       <c r="M81" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N81" s="15"/>
       <c r="O81" s="18" t="s">
@@ -67897,7 +67991,7 @@
       </c>
       <c r="L82" s="15"/>
       <c r="M82" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N82" s="15"/>
       <c r="O82" s="18" t="s">
@@ -67939,7 +68033,7 @@
       </c>
       <c r="L83" s="15"/>
       <c r="M83" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N83" s="15"/>
       <c r="O83" s="18" t="s">
@@ -67981,7 +68075,7 @@
       </c>
       <c r="L84" s="15"/>
       <c r="M84" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N84" s="15"/>
       <c r="O84" s="18" t="s">
@@ -68023,7 +68117,7 @@
       </c>
       <c r="L85" s="15"/>
       <c r="M85" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N85" s="15"/>
       <c r="O85" s="18" t="s">
@@ -68065,7 +68159,7 @@
       </c>
       <c r="L86" s="15"/>
       <c r="M86" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N86" s="15"/>
       <c r="O86" s="18" t="s">
@@ -68107,7 +68201,7 @@
       </c>
       <c r="L87" s="15"/>
       <c r="M87" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N87" s="15"/>
       <c r="O87" s="18" t="s">
@@ -68149,7 +68243,7 @@
       </c>
       <c r="L88" s="15"/>
       <c r="M88" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N88" s="15"/>
       <c r="O88" s="18" t="s">
@@ -68191,7 +68285,7 @@
       </c>
       <c r="L89" s="15"/>
       <c r="M89" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N89" s="15"/>
       <c r="O89" s="18" t="s">
@@ -68233,7 +68327,7 @@
       </c>
       <c r="L90" s="15"/>
       <c r="M90" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N90" s="15"/>
       <c r="O90" s="18" t="s">
@@ -68275,7 +68369,7 @@
       </c>
       <c r="L91" s="15"/>
       <c r="M91" s="15" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="N91" s="15"/>
       <c r="O91" s="18" t="s">

--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CDD092-14A8-A141-A375-569E80801639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D729AA-BD62-4341-8F84-E321421C099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20920" firstSheet="9" activeTab="12" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>

--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D729AA-BD62-4341-8F84-E321421C099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20496620-5BF8-824E-80A7-FE087193A186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20920" firstSheet="9" activeTab="12" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20920" firstSheet="19" activeTab="31" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="global_enums" sheetId="42" r:id="rId1"/>
@@ -43,12 +43,13 @@
     <sheet name="samples_enums" sheetId="28" r:id="rId28"/>
     <sheet name="samples_maps" sheetId="24" r:id="rId29"/>
     <sheet name="samples_wide" sheetId="27" r:id="rId30"/>
-    <sheet name="sites_maps" sheetId="25" r:id="rId31"/>
-    <sheet name="OTHER_maps" sheetId="26" r:id="rId32"/>
-    <sheet name="PHA4GEVars" sheetId="35" r:id="rId33"/>
+    <sheet name="sites_enums" sheetId="44" r:id="rId31"/>
+    <sheet name="sites_maps" sheetId="25" r:id="rId32"/>
+    <sheet name="OTHER_maps" sheetId="26" r:id="rId33"/>
+    <sheet name="PHA4GEVars" sheetId="35" r:id="rId34"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId34"/>
+    <externalReference r:id="rId35"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">protocols_wide!$A$1:$G$1</definedName>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9409" uniqueCount="2111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9786" uniqueCount="2114">
   <si>
     <t>Complete</t>
   </si>
@@ -6507,6 +6508,18 @@
   </si>
   <si>
     <t>internatSurv</t>
+  </si>
+  <si>
+    <t>if isinstance(src.environmental_material, str) and "Bar Screen" in src.environmental_material:
+    target = "barScreen"</t>
+  </si>
+  <si>
+    <t>Bar screen</t>
+  </si>
+  <si>
+    <t>target = emap.environmental_site
+if len([v for v in src.environmental_material if "bar screen" in str(v).lower()]) &gt; 0:
+    target.append("siteType:barScreen")</t>
   </si>
 </sst>
 </file>
@@ -42506,7 +42519,7 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52CAD1A-92FF-3346-8108-2C4AA07D2B2C}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AD44"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -43648,48 +43661,42 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B32" t="b">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>108</v>
+      </c>
       <c r="D32" t="str">
         <f>IF(F32&lt;&gt;"",VLOOKUP(F32,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F32" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32" t="s">
+        <v>2112</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I32" t="s">
+        <v>1334</v>
+      </c>
+      <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>325</v>
-      </c>
-      <c r="B33" t="b">
-        <f>IF(OR(G33="NA",H33="wide_value"),"",TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>108</v>
-      </c>
       <c r="D33" t="str">
         <f>IF(F33&lt;&gt;"",VLOOKUP(F33,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E33" t="s">
-        <v>1650</v>
-      </c>
-      <c r="F33" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G33" t="s">
-        <v>1061</v>
-      </c>
-      <c r="H33" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I33" t="s">
-        <v>1398</v>
-      </c>
-      <c r="J33" t="s">
-        <v>2032</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="b">
         <f>IF(OR(G34="NA",H34="wide_value"),"",TRUE)</f>
@@ -43709,7 +43716,7 @@
         <v>1013</v>
       </c>
       <c r="G34" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H34" t="s">
         <v>1096</v>
@@ -43718,12 +43725,12 @@
         <v>1398</v>
       </c>
       <c r="J34" t="s">
-        <v>1399</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B35" t="b">
         <f>IF(OR(G35="NA",H35="wide_value"),"",TRUE)</f>
@@ -43743,7 +43750,7 @@
         <v>1013</v>
       </c>
       <c r="G35" t="s">
-        <v>205</v>
+        <v>1062</v>
       </c>
       <c r="H35" t="s">
         <v>1096</v>
@@ -43752,12 +43759,12 @@
         <v>1398</v>
       </c>
       <c r="J35" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="b">
         <f>IF(OR(G36="NA",H36="wide_value"),"",TRUE)</f>
@@ -43777,7 +43784,7 @@
         <v>1013</v>
       </c>
       <c r="G36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H36" t="s">
         <v>1096</v>
@@ -43786,66 +43793,62 @@
         <v>1398</v>
       </c>
       <c r="J36" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C37" s="15"/>
+      <c r="A37">
+        <v>328</v>
+      </c>
+      <c r="B37" t="b">
+        <f>IF(OR(G37="NA",H37="wide_value"),"",TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>108</v>
+      </c>
       <c r="D37" t="str">
         <f>IF(F37&lt;&gt;"",VLOOKUP(F37,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G37" t="s">
+        <v>206</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1398</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1401</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>622</v>
-      </c>
-      <c r="B38" t="b">
-        <f>IF(OR(G38="NA",H38="wide_value"),"",TRUE)</f>
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
+      <c r="C38" s="15"/>
       <c r="D38" t="str">
         <f>IF(F38&lt;&gt;"",VLOOKUP(F38,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1650</v>
-      </c>
-      <c r="F38" t="s">
-        <v>146</v>
-      </c>
-      <c r="G38" t="s">
-        <v>166</v>
-      </c>
-      <c r="H38" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I38" t="s">
-        <v>1850</v>
-      </c>
-      <c r="J38" t="s">
-        <v>1184</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="N38" s="17"/>
+        <v/>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B39" t="b">
-        <f t="shared" ref="B39:B44" si="3">IF(OR(G39="NA",H39="wide_value"),"",TRUE)</f>
+        <f>IF(OR(G39="NA",H39="wide_value"),"",TRUE)</f>
         <v>1</v>
       </c>
       <c r="C39" t="s">
@@ -43862,7 +43865,7 @@
         <v>146</v>
       </c>
       <c r="G39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H39" t="s">
         <v>1096</v>
@@ -43871,7 +43874,7 @@
         <v>1850</v>
       </c>
       <c r="J39" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>1182</v>
@@ -43880,10 +43883,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B40" t="b">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="B40:B45" si="3">IF(OR(G40="NA",H40="wide_value"),"",TRUE)</f>
         <v>1</v>
       </c>
       <c r="C40" t="s">
@@ -43900,7 +43903,7 @@
         <v>146</v>
       </c>
       <c r="G40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H40" t="s">
         <v>1096</v>
@@ -43909,7 +43912,7 @@
         <v>1850</v>
       </c>
       <c r="J40" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>1182</v>
@@ -43918,7 +43921,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B41" t="b">
         <f t="shared" si="3"/>
@@ -43938,7 +43941,7 @@
         <v>146</v>
       </c>
       <c r="G41" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H41" t="s">
         <v>1096</v>
@@ -43947,7 +43950,7 @@
         <v>1850</v>
       </c>
       <c r="J41" t="s">
-        <v>1181</v>
+        <v>1186</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>1182</v>
@@ -43956,7 +43959,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B42" t="b">
         <f t="shared" si="3"/>
@@ -43976,7 +43979,7 @@
         <v>146</v>
       </c>
       <c r="G42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H42" t="s">
         <v>1096</v>
@@ -43985,16 +43988,16 @@
         <v>1850</v>
       </c>
       <c r="J42" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B43" t="b">
         <f t="shared" si="3"/>
@@ -44014,7 +44017,7 @@
         <v>146</v>
       </c>
       <c r="G43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H43" t="s">
         <v>1096</v>
@@ -44023,7 +44026,7 @@
         <v>1850</v>
       </c>
       <c r="J43" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>1179</v>
@@ -44032,7 +44035,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B44" t="b">
         <f t="shared" si="3"/>
@@ -44052,7 +44055,7 @@
         <v>146</v>
       </c>
       <c r="G44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H44" t="s">
         <v>1096</v>
@@ -44061,12 +44064,50 @@
         <v>1850</v>
       </c>
       <c r="J44" t="s">
-        <v>1183</v>
+        <v>1188</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>1179</v>
       </c>
       <c r="N44" s="17"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>628</v>
+      </c>
+      <c r="B45" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" t="str">
+        <f>IF(F45&lt;&gt;"",VLOOKUP(F45,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1650</v>
+      </c>
+      <c r="F45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45" t="s">
+        <v>172</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1096</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1850</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="N45" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -56338,9 +56379,1620 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88DA42E7-5DB5-464B-854A-174287DABDEA}">
+  <dimension ref="A1:L51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>1751</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" t="b">
+        <f t="shared" ref="A2" si="0">IF(OR(F2="NA",G2="wide_value"),"",TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="str">
+        <f>IF(E2&lt;&gt;"",VLOOKUP(E2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="b">
+        <f t="shared" ref="A3:A51" si="1">IF(OR(F3="NA",G3="wide_value"),"",TRUE)</f>
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" t="str">
+        <f>IF(E3&lt;&gt;"",VLOOKUP(E3,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="str">
+        <f>IF(E4&lt;&gt;"",VLOOKUP(E4,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="str">
+        <f>IF(E5&lt;&gt;"",VLOOKUP(E5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="str">
+        <f>IF(E6&lt;&gt;"",VLOOKUP(E6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" t="str">
+        <f>IF(E7&lt;&gt;"",VLOOKUP(E7,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="str">
+        <f>IF(E8&lt;&gt;"",VLOOKUP(E8,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="str">
+        <f>IF(E9&lt;&gt;"",VLOOKUP(E9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="str">
+        <f>IF(E10&lt;&gt;"",VLOOKUP(E10,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" t="str">
+        <f>IF(E11&lt;&gt;"",VLOOKUP(E11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" t="str">
+        <f>IF(E12&lt;&gt;"",VLOOKUP(E12,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" t="str">
+        <f>IF(E13&lt;&gt;"",VLOOKUP(E13,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" t="str">
+        <f>IF(E14&lt;&gt;"",VLOOKUP(E14,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="str">
+        <f>IF(E15&lt;&gt;"",VLOOKUP(E15,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="str">
+        <f>IF(E16&lt;&gt;"",VLOOKUP(E16,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" t="str">
+        <f>IF(E17&lt;&gt;"",VLOOKUP(E17,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="str">
+        <f>IF(E18&lt;&gt;"",VLOOKUP(E18,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="str">
+        <f>IF(E19&lt;&gt;"",VLOOKUP(E19,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="str">
+        <f>IF(E20&lt;&gt;"",VLOOKUP(E20,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="str">
+        <f>IF(E21&lt;&gt;"",VLOOKUP(E21,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" t="str">
+        <f>IF(E22&lt;&gt;"",VLOOKUP(E22,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" t="str">
+        <f>IF(E23&lt;&gt;"",VLOOKUP(E23,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" t="str">
+        <f>IF(E24&lt;&gt;"",VLOOKUP(E24,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" t="str">
+        <f>IF(E25&lt;&gt;"",VLOOKUP(E25,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="str">
+        <f>IF(E26&lt;&gt;"",VLOOKUP(E26,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="str">
+        <f>IF(E27&lt;&gt;"",VLOOKUP(E27,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" t="str">
+        <f>IF(E28&lt;&gt;"",VLOOKUP(E28,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" t="str">
+        <f>IF(E29&lt;&gt;"",VLOOKUP(E29,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" t="str">
+        <f>IF(E30&lt;&gt;"",VLOOKUP(E30,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" t="str">
+        <f>IF(E31&lt;&gt;"",VLOOKUP(E31,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B32" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" t="str">
+        <f>IF(E32&lt;&gt;"",VLOOKUP(E32,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="str">
+        <f>IF(E33&lt;&gt;"",VLOOKUP(E33,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" t="str">
+        <f>IF(E34&lt;&gt;"",VLOOKUP(E34,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" t="str">
+        <f>IF(E35&lt;&gt;"",VLOOKUP(E35,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" t="str">
+        <f>IF(E36&lt;&gt;"",VLOOKUP(E36,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" t="str">
+        <f>IF(E37&lt;&gt;"",VLOOKUP(E37,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" t="str">
+        <f>IF(E38&lt;&gt;"",VLOOKUP(E38,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" t="str">
+        <f>IF(E39&lt;&gt;"",VLOOKUP(E39,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1760</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" t="str">
+        <f>IF(E40&lt;&gt;"",VLOOKUP(E40,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" t="str">
+        <f>IF(E41&lt;&gt;"",VLOOKUP(E41,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1762</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" t="str">
+        <f>IF(E42&lt;&gt;"",VLOOKUP(E42,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" t="str">
+        <f>IF(E43&lt;&gt;"",VLOOKUP(E43,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1764</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" t="str">
+        <f>IF(E44&lt;&gt;"",VLOOKUP(E44,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" t="str">
+        <f>IF(E45&lt;&gt;"",VLOOKUP(E45,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B46" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" t="str">
+        <f>IF(E46&lt;&gt;"",VLOOKUP(E46,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1767</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I46" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" t="str">
+        <f>IF(E47&lt;&gt;"",VLOOKUP(E47,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1768</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" t="str">
+        <f>IF(E48&lt;&gt;"",VLOOKUP(E48,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I48" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B49" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" t="str">
+        <f>IF(E49&lt;&gt;"",VLOOKUP(E49,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1770</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I49" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" t="str">
+        <f>IF(E50&lt;&gt;"",VLOOKUP(E50,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1771</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" t="str">
+        <f>IF(E51&lt;&gt;"",VLOOKUP(E51,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098C5693-7744-414E-A1CB-7D8D34C0B793}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -56351,16 +58003,15 @@
     <col min="7" max="7" width="20.6640625" customWidth="1"/>
     <col min="8" max="8" width="33.1640625" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="7.5" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" customWidth="1"/>
-    <col min="16" max="16" width="49.5" customWidth="1"/>
-    <col min="17" max="17" width="114.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="7.5" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" customWidth="1"/>
+    <col min="15" max="15" width="49.5" customWidth="1"/>
+    <col min="16" max="16" width="114.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>1293</v>
       </c>
@@ -56389,31 +58040,28 @@
         <v>4</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>1586</v>
+        <v>5</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>6</v>
+        <v>1624</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>1624</v>
+        <v>1574</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>1574</v>
+        <v>8</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" s="16" t="s">
         <v>1566</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="15">
         <v>61</v>
       </c>
@@ -56440,20 +58088,19 @@
       <c r="I2" s="27" t="s">
         <v>1101</v>
       </c>
-      <c r="J2" s="27"/>
+      <c r="J2" s="15" t="s">
+        <v>1102</v>
+      </c>
       <c r="K2" s="15" t="s">
-        <v>1102</v>
-      </c>
-      <c r="L2" s="15" t="s">
         <v>1103</v>
       </c>
+      <c r="L2" s="15"/>
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -56466,16 +58113,15 @@
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
       <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
+      <c r="J3" s="15"/>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:16" ht="170" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
         <v>287</v>
       </c>
@@ -56498,36 +58144,31 @@
       <c r="G4" s="15" t="s">
         <v>1680</v>
       </c>
-      <c r="H4" s="15" t="s">
-        <v>207</v>
-      </c>
+      <c r="H4" s="15"/>
       <c r="I4" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15" t="s">
+      <c r="J4" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L4" s="15" t="s">
-        <v>1587</v>
+      <c r="K4" s="15"/>
+      <c r="L4" s="69" t="s">
+        <v>2113</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
-      <c r="Q4" s="15" t="s">
-        <v>1658</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B5" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C5" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>108</v>
@@ -56543,35 +58184,33 @@
         <v>1680</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K5" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15" t="s">
+      <c r="P5" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B6" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C6" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>108</v>
@@ -56587,35 +58226,34 @@
         <v>1680</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="J6" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K6" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>1589</v>
-      </c>
+        <v>1588</v>
+      </c>
+      <c r="L6" s="15"/>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15" t="s">
+      <c r="P6" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B7" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C7" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>108</v>
@@ -56631,35 +58269,34 @@
         <v>1680</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K7" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>1590</v>
-      </c>
+        <v>1589</v>
+      </c>
+      <c r="L7" s="15"/>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
       <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15" t="s">
+      <c r="P7" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B8" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C8" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>108</v>
@@ -56675,35 +58312,34 @@
         <v>1680</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J8" s="15"/>
+      <c r="J8" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K8" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L8" s="15" t="s">
-        <v>1591</v>
-      </c>
+        <v>1590</v>
+      </c>
+      <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15" t="s">
+      <c r="P8" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B9" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C9" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>108</v>
@@ -56719,35 +58355,34 @@
         <v>1680</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J9" s="15"/>
+      <c r="J9" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K9" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>1592</v>
-      </c>
+        <v>1591</v>
+      </c>
+      <c r="L9" s="15"/>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
       <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15" t="s">
+      <c r="P9" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B10" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C10" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>108</v>
@@ -56763,35 +58398,34 @@
         <v>1680</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K10" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L10" s="15" t="s">
-        <v>1593</v>
-      </c>
+        <v>1592</v>
+      </c>
+      <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15" t="s">
+      <c r="P10" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B11" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C11" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>108</v>
@@ -56807,35 +58441,34 @@
         <v>1680</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="J11" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K11" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>1594</v>
-      </c>
+        <v>1593</v>
+      </c>
+      <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15" t="s">
+      <c r="P11" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B12" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C12" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>108</v>
@@ -56851,35 +58484,34 @@
         <v>1680</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="J12" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K12" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>1595</v>
-      </c>
+        <v>1594</v>
+      </c>
+      <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15" t="s">
+      <c r="P12" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B13" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C13" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>108</v>
@@ -56895,35 +58527,34 @@
         <v>1680</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J13" s="15"/>
+      <c r="J13" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K13" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>1596</v>
-      </c>
+        <v>1595</v>
+      </c>
+      <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15" t="s">
+      <c r="P13" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B14" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C14" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>108</v>
@@ -56939,35 +58570,34 @@
         <v>1680</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J14" s="15"/>
+      <c r="J14" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K14" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>1597</v>
-      </c>
+        <v>1596</v>
+      </c>
+      <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15" t="s">
+      <c r="P14" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B15" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C15" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>108</v>
@@ -56983,35 +58613,34 @@
         <v>1680</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J15" s="15"/>
+      <c r="J15" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K15" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>1598</v>
-      </c>
+        <v>1597</v>
+      </c>
+      <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15" t="s">
+      <c r="P15" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="15">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B16" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C16" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>108</v>
@@ -57027,35 +58656,34 @@
         <v>1680</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J16" s="15"/>
+      <c r="J16" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K16" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>1599</v>
-      </c>
+        <v>1598</v>
+      </c>
+      <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15" t="s">
+      <c r="P16" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B17" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C17" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>108</v>
@@ -57071,35 +58699,34 @@
         <v>1680</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K17" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>1600</v>
-      </c>
+        <v>1599</v>
+      </c>
+      <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15" t="s">
+      <c r="P17" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B18" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C18" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>108</v>
@@ -57115,35 +58742,34 @@
         <v>1680</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J18" s="15"/>
+      <c r="J18" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K18" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>1601</v>
-      </c>
+        <v>1600</v>
+      </c>
+      <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
       <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15" t="s">
+      <c r="P18" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B19" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C19" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>108</v>
@@ -57159,35 +58785,34 @@
         <v>1680</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J19" s="15"/>
+      <c r="J19" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K19" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>1602</v>
-      </c>
+        <v>1601</v>
+      </c>
+      <c r="L19" s="15"/>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15" t="s">
+      <c r="P19" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B20" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C20" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>108</v>
@@ -57203,35 +58828,34 @@
         <v>1680</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J20" s="15"/>
+      <c r="J20" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K20" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>1603</v>
-      </c>
+        <v>1602</v>
+      </c>
+      <c r="L20" s="15"/>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15" t="s">
+      <c r="P20" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B21" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C21" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>108</v>
@@ -57247,35 +58871,34 @@
         <v>1680</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J21" s="15"/>
+      <c r="J21" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K21" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>1604</v>
-      </c>
+        <v>1603</v>
+      </c>
+      <c r="L21" s="15"/>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15" t="s">
+      <c r="P21" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B22" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C22" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>108</v>
@@ -57291,35 +58914,34 @@
         <v>1680</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J22" s="15"/>
+      <c r="J22" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K22" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>1605</v>
-      </c>
+        <v>1604</v>
+      </c>
+      <c r="L22" s="15"/>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15" t="s">
+      <c r="P22" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="15">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B23" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C23" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>108</v>
@@ -57335,35 +58957,34 @@
         <v>1680</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J23" s="15"/>
+      <c r="J23" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K23" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>1606</v>
-      </c>
+        <v>1605</v>
+      </c>
+      <c r="L23" s="15"/>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15" t="s">
+      <c r="P23" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B24" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C24" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>108</v>
@@ -57379,35 +59000,34 @@
         <v>1680</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J24" s="15"/>
+      <c r="J24" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K24" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>1607</v>
-      </c>
+        <v>1606</v>
+      </c>
+      <c r="L24" s="15"/>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15" t="s">
+      <c r="P24" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="15">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B25" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C25" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>108</v>
@@ -57423,35 +59043,34 @@
         <v>1680</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J25" s="15"/>
+      <c r="J25" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K25" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L25" s="15" t="s">
-        <v>1608</v>
-      </c>
+        <v>1607</v>
+      </c>
+      <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15" t="s">
+      <c r="P25" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B26" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C26" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>108</v>
@@ -57467,35 +59086,34 @@
         <v>1680</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J26" s="15"/>
+      <c r="J26" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K26" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L26" s="15" t="s">
-        <v>1609</v>
-      </c>
+        <v>1608</v>
+      </c>
+      <c r="L26" s="15"/>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15" t="s">
+      <c r="P26" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B27" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C27" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>108</v>
@@ -57511,35 +59129,34 @@
         <v>1680</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J27" s="15"/>
+      <c r="J27" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K27" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L27" s="15" t="s">
-        <v>1610</v>
-      </c>
+        <v>1609</v>
+      </c>
+      <c r="L27" s="15"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15" t="s">
+      <c r="P27" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B28" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C28" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>108</v>
@@ -57555,35 +59172,34 @@
         <v>1680</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J28" s="15"/>
+      <c r="J28" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K28" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L28" s="15" t="s">
-        <v>1611</v>
-      </c>
+        <v>1610</v>
+      </c>
+      <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15" t="s">
+      <c r="P28" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B29" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C29" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>108</v>
@@ -57599,35 +59215,34 @@
         <v>1680</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J29" s="15"/>
+      <c r="J29" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K29" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>1612</v>
-      </c>
+        <v>1611</v>
+      </c>
+      <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15" t="s">
+      <c r="P29" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B30" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C30" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>108</v>
@@ -57643,35 +59258,34 @@
         <v>1680</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J30" s="15"/>
+      <c r="J30" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K30" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L30" s="15" t="s">
-        <v>1613</v>
-      </c>
+        <v>1612</v>
+      </c>
+      <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15" t="s">
+      <c r="P30" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="15">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B31" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C31" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>108</v>
@@ -57687,35 +59301,34 @@
         <v>1680</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J31" s="15"/>
+      <c r="J31" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K31" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>1614</v>
-      </c>
+        <v>1613</v>
+      </c>
+      <c r="L31" s="15"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15" t="s">
+      <c r="P31" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="15">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B32" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C32" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>108</v>
@@ -57731,35 +59344,34 @@
         <v>1680</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J32" s="15"/>
+      <c r="J32" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K32" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>1615</v>
-      </c>
+        <v>1614</v>
+      </c>
+      <c r="L32" s="15"/>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15" t="s">
+      <c r="P32" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B33" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C33" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>108</v>
@@ -57775,35 +59387,34 @@
         <v>1680</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J33" s="15"/>
+      <c r="J33" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K33" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>1616</v>
-      </c>
+        <v>1615</v>
+      </c>
+      <c r="L33" s="15"/>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15" t="s">
+      <c r="P33" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B34" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C34" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>108</v>
@@ -57819,35 +59430,34 @@
         <v>1680</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>1881</v>
+        <v>236</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J34" s="15"/>
+      <c r="J34" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K34" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L34" s="15" t="s">
-        <v>1617</v>
-      </c>
+        <v>1616</v>
+      </c>
+      <c r="L34" s="15"/>
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
       <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15" t="s">
+      <c r="P34" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B35" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C35" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>108</v>
@@ -57863,35 +59473,34 @@
         <v>1680</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>1057</v>
+        <v>1881</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J35" s="15"/>
+      <c r="J35" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K35" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L35" s="15" t="s">
-        <v>1618</v>
-      </c>
+        <v>1617</v>
+      </c>
+      <c r="L35" s="15"/>
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15" t="s">
+      <c r="P35" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B36" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C36" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>108</v>
@@ -57907,35 +59516,34 @@
         <v>1680</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>237</v>
+        <v>1057</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J36" s="15"/>
+      <c r="J36" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K36" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>1619</v>
-      </c>
+        <v>1618</v>
+      </c>
+      <c r="L36" s="15"/>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15" t="s">
+      <c r="P36" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B37" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C37" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>108</v>
@@ -57951,35 +59559,34 @@
         <v>1680</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J37" s="15"/>
+      <c r="J37" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K37" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L37" s="15" t="s">
-        <v>1620</v>
-      </c>
+        <v>1619</v>
+      </c>
+      <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15" t="s">
+      <c r="P37" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B38" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C38" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>108</v>
@@ -57995,35 +59602,34 @@
         <v>1680</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J38" s="15"/>
+      <c r="J38" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K38" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L38" s="15" t="s">
-        <v>1621</v>
-      </c>
+        <v>1620</v>
+      </c>
+      <c r="L38" s="15"/>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
       <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15" t="s">
+      <c r="P38" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="15">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B39" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C39" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>108</v>
@@ -58039,32 +59645,34 @@
         <v>1680</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J39" s="15"/>
+      <c r="J39" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K39" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L39" s="15" t="s">
-        <v>1622</v>
-      </c>
+        <v>1621</v>
+      </c>
+      <c r="L39" s="15"/>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15" t="s">
+      <c r="P39" s="15" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="15">
+        <v>322</v>
+      </c>
       <c r="B40" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C40" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>108</v>
@@ -58079,28 +59687,32 @@
       <c r="G40" s="15" t="s">
         <v>1680</v>
       </c>
-      <c r="H40" t="s">
-        <v>1759</v>
+      <c r="H40" s="15" t="s">
+        <v>240</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>1101</v>
       </c>
+      <c r="J40" s="15" t="s">
+        <v>1151</v>
+      </c>
       <c r="K40" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="L40" t="s">
-        <v>1773</v>
-      </c>
-      <c r="Q40" s="15" t="s">
-        <v>1755</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1622</v>
+      </c>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B41" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C41" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>108</v>
@@ -58116,27 +59728,27 @@
         <v>1680</v>
       </c>
       <c r="H41" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K41" s="15" t="s">
+      <c r="J41" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L41" t="s">
-        <v>1774</v>
-      </c>
-      <c r="Q41" s="15" t="s">
+      <c r="K41" t="s">
+        <v>1773</v>
+      </c>
+      <c r="P41" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B42" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C42" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>108</v>
@@ -58152,27 +59764,27 @@
         <v>1680</v>
       </c>
       <c r="H42" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K42" s="15" t="s">
+      <c r="J42" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L42" t="s">
-        <v>1775</v>
-      </c>
-      <c r="Q42" s="15" t="s">
+      <c r="K42" t="s">
+        <v>1774</v>
+      </c>
+      <c r="P42" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B43" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C43" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>108</v>
@@ -58188,27 +59800,27 @@
         <v>1680</v>
       </c>
       <c r="H43" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K43" s="15" t="s">
+      <c r="J43" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L43" t="s">
-        <v>1776</v>
-      </c>
-      <c r="Q43" s="15" t="s">
+      <c r="K43" t="s">
+        <v>1775</v>
+      </c>
+      <c r="P43" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B44" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C44" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>108</v>
@@ -58224,27 +59836,27 @@
         <v>1680</v>
       </c>
       <c r="H44" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K44" s="15" t="s">
+      <c r="J44" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L44" t="s">
-        <v>1777</v>
-      </c>
-      <c r="Q44" s="15" t="s">
+      <c r="K44" t="s">
+        <v>1776</v>
+      </c>
+      <c r="P44" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B45" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C45" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>108</v>
@@ -58260,27 +59872,27 @@
         <v>1680</v>
       </c>
       <c r="H45" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K45" s="15" t="s">
+      <c r="J45" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L45" t="s">
-        <v>1778</v>
-      </c>
-      <c r="Q45" s="15" t="s">
+      <c r="K45" t="s">
+        <v>1777</v>
+      </c>
+      <c r="P45" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B46" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C46" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>108</v>
@@ -58296,27 +59908,27 @@
         <v>1680</v>
       </c>
       <c r="H46" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K46" s="15" t="s">
+      <c r="J46" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L46" t="s">
-        <v>1779</v>
-      </c>
-      <c r="Q46" s="15" t="s">
+      <c r="K46" t="s">
+        <v>1778</v>
+      </c>
+      <c r="P46" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B47" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C47" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>108</v>
@@ -58332,27 +59944,27 @@
         <v>1680</v>
       </c>
       <c r="H47" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K47" s="15" t="s">
+      <c r="J47" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L47" t="s">
-        <v>1780</v>
-      </c>
-      <c r="Q47" s="15" t="s">
+      <c r="K47" t="s">
+        <v>1779</v>
+      </c>
+      <c r="P47" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B48" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C48" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>108</v>
@@ -58368,27 +59980,27 @@
         <v>1680</v>
       </c>
       <c r="H48" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K48" s="15" t="s">
+      <c r="J48" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L48" t="s">
-        <v>1781</v>
-      </c>
-      <c r="Q48" s="15" t="s">
+      <c r="K48" t="s">
+        <v>1780</v>
+      </c>
+      <c r="P48" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B49" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C49" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>108</v>
@@ -58404,27 +60016,27 @@
         <v>1680</v>
       </c>
       <c r="H49" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K49" s="15" t="s">
+      <c r="J49" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L49" t="s">
-        <v>1782</v>
-      </c>
-      <c r="Q49" s="15" t="s">
+      <c r="K49" t="s">
+        <v>1781</v>
+      </c>
+      <c r="P49" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B50" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C50" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>108</v>
@@ -58440,27 +60052,27 @@
         <v>1680</v>
       </c>
       <c r="H50" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K50" s="15" t="s">
+      <c r="J50" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L50" t="s">
-        <v>1783</v>
-      </c>
-      <c r="Q50" s="15" t="s">
+      <c r="K50" t="s">
+        <v>1782</v>
+      </c>
+      <c r="P50" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B51" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C51" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>108</v>
@@ -58476,27 +60088,27 @@
         <v>1680</v>
       </c>
       <c r="H51" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K51" s="15" t="s">
+      <c r="J51" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L51" t="s">
-        <v>1784</v>
-      </c>
-      <c r="Q51" s="15" t="s">
+      <c r="K51" t="s">
+        <v>1783</v>
+      </c>
+      <c r="P51" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B52" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C52" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>108</v>
@@ -58512,27 +60124,27 @@
         <v>1680</v>
       </c>
       <c r="H52" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K52" s="15" t="s">
+      <c r="J52" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L52" t="s">
-        <v>1785</v>
-      </c>
-      <c r="Q52" s="15" t="s">
+      <c r="K52" t="s">
+        <v>1784</v>
+      </c>
+      <c r="P52" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B53" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C53" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>108</v>
@@ -58548,194 +60160,168 @@
         <v>1680</v>
       </c>
       <c r="H53" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K53" s="15" t="s">
+      <c r="J53" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="L53" t="s">
-        <v>1786</v>
-      </c>
-      <c r="Q53" s="15" t="s">
+      <c r="K53" t="s">
+        <v>1785</v>
+      </c>
+      <c r="P53" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B54" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C54" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="E54" t="str">
         <f>IF(G54&lt;&gt;"",VLOOKUP(G54,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="15"/>
-      <c r="M54" s="15"/>
-      <c r="N54" s="15"/>
-      <c r="O54" s="15"/>
-      <c r="P54" s="15"/>
-      <c r="Q54" s="15"/>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A55" s="15">
-        <v>333</v>
-      </c>
-      <c r="B55" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C55" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>108</v>
-      </c>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1772</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K54" t="s">
+        <v>1786</v>
+      </c>
+      <c r="P54" s="15" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
       <c r="E55" t="str">
         <f>IF(G55&lt;&gt;"",VLOOKUP(G55,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G55" s="15" t="s">
-        <v>1004</v>
-      </c>
-      <c r="H55" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="I55" s="15" t="s">
-        <v>1101</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
       <c r="J55" s="15"/>
-      <c r="K55" s="15" t="s">
-        <v>1190</v>
-      </c>
-      <c r="L55" s="15" t="s">
-        <v>1192</v>
-      </c>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
       <c r="M55" s="15"/>
       <c r="N55" s="15"/>
       <c r="O55" s="15"/>
       <c r="P55" s="15"/>
-      <c r="Q55" s="15"/>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A56" s="15">
-        <v>334</v>
-      </c>
+    </row>
+    <row r="56" spans="1:16" ht="136" x14ac:dyDescent="0.2">
+      <c r="A56" s="15"/>
       <c r="B56" s="15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E56" t="str">
-        <f>IF(G56&lt;&gt;"",VLOOKUP(G56,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D56" s="15"/>
       <c r="F56" s="15" t="s">
         <v>1650</v>
       </c>
-      <c r="G56" s="15" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H56" s="15" t="s">
-        <v>368</v>
-      </c>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
       <c r="I56" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15" t="s">
-        <v>1191</v>
-      </c>
-      <c r="L56" s="15" t="s">
-        <v>1193</v>
+      <c r="J56" s="15" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K56" s="15"/>
+      <c r="L56" s="69" t="s">
+        <v>2111</v>
       </c>
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
       <c r="O56" s="15"/>
       <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A57" s="15">
-        <v>336</v>
-      </c>
-      <c r="B57" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C57" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E57" t="str">
-        <f>IF(G57&lt;&gt;"",VLOOKUP(G57,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>1675</v>
-      </c>
-      <c r="H57" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="I57" s="15" t="s">
-        <v>1101</v>
-      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
       <c r="J57" s="15"/>
-      <c r="K57" s="15" t="s">
-        <v>1071</v>
-      </c>
-      <c r="L57" s="15" t="s">
-        <v>1120</v>
-      </c>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
       <c r="M57" s="15"/>
       <c r="N57" s="15"/>
       <c r="O57" s="15"/>
       <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A58" s="15"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>333</v>
+      </c>
+      <c r="B58" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C58" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="E58" t="str">
         <f>IF(G58&lt;&gt;"",VLOOKUP(G58,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>1190</v>
+      </c>
+      <c r="K58" s="15" t="s">
+        <v>1192</v>
+      </c>
       <c r="L58" s="15"/>
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
       <c r="O58" s="15"/>
       <c r="P58" s="15"/>
-      <c r="Q58" s="15"/>
-    </row>
-    <row r="59" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="16">
-        <v>680</v>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>334</v>
       </c>
       <c r="B59" s="15" t="b">
         <v>1</v>
@@ -58743,45 +60329,40 @@
       <c r="C59" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D59" s="16" t="s">
+      <c r="D59" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E59" s="17" t="str">
+      <c r="E59" t="str">
         <f>IF(G59&lt;&gt;"",VLOOKUP(G59,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="F59" s="16" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="H59" s="16" t="s">
-        <v>1423</v>
-      </c>
-      <c r="I59" s="16" t="s">
+      <c r="F59" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="I59" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L59" s="16" t="s">
-        <v>1153</v>
-      </c>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
-      <c r="P59" s="22" t="s">
-        <v>1433</v>
-      </c>
-      <c r="Q59" s="16" t="s">
-        <v>1583</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="16">
-        <v>681</v>
+      <c r="J59" s="15" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K59" s="15" t="s">
+        <v>1193</v>
+      </c>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="15"/>
+      <c r="P59" s="15"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>336</v>
       </c>
       <c r="B60" s="15" t="b">
         <v>1</v>
@@ -58789,91 +60370,61 @@
       <c r="C60" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E60" s="17" t="str">
+      <c r="E60" t="str">
         <f>IF(G60&lt;&gt;"",VLOOKUP(G60,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="F60" s="16" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="H60" s="16" t="s">
-        <v>1424</v>
-      </c>
-      <c r="I60" s="16" t="s">
+      <c r="F60" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="I60" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L60" s="16" t="s">
-        <v>1154</v>
-      </c>
-      <c r="M60" s="16"/>
-      <c r="N60" s="16"/>
-      <c r="O60" s="16"/>
-      <c r="P60" s="22" t="s">
-        <v>1433</v>
-      </c>
-      <c r="Q60" s="16" t="s">
-        <v>1583</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="16">
-        <v>682</v>
-      </c>
-      <c r="B61" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C61" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E61" s="17" t="str">
+      <c r="J60" s="15" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K60" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" t="str">
         <f>IF(G61&lt;&gt;"",VLOOKUP(G61,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F61" s="16" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="H61" s="16" t="s">
-        <v>1882</v>
-      </c>
-      <c r="I61" s="16" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J61" s="16"/>
-      <c r="K61" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L61" s="16" t="s">
-        <v>1429</v>
-      </c>
-      <c r="M61" s="16"/>
-      <c r="N61" s="16"/>
-      <c r="O61" s="16"/>
-      <c r="P61" s="22" t="s">
-        <v>1433</v>
-      </c>
-      <c r="Q61" s="16" t="s">
-        <v>1583</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
+        <v/>
+      </c>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="15"/>
+      <c r="P61" s="15"/>
+    </row>
+    <row r="62" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="16">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B62" s="15" t="b">
         <v>1</v>
@@ -58895,31 +60446,30 @@
         <v>143</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>1056</v>
+        <v>1423</v>
       </c>
       <c r="I62" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="J62" s="16"/>
+      <c r="J62" s="16" t="s">
+        <v>1152</v>
+      </c>
       <c r="K62" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L62" s="16" t="s">
-        <v>1150</v>
-      </c>
+        <v>1153</v>
+      </c>
+      <c r="L62" s="16"/>
       <c r="M62" s="16"/>
       <c r="N62" s="16"/>
-      <c r="O62" s="16"/>
-      <c r="P62" s="22" t="s">
+      <c r="O62" s="22" t="s">
         <v>1433</v>
       </c>
-      <c r="Q62" s="16" t="s">
+      <c r="P62" s="16" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B63" s="15" t="b">
         <v>1</v>
@@ -58941,31 +60491,30 @@
         <v>143</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="I63" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="J63" s="16"/>
+      <c r="J63" s="16" t="s">
+        <v>1152</v>
+      </c>
       <c r="K63" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L63" s="16" t="s">
-        <v>1430</v>
-      </c>
+        <v>1154</v>
+      </c>
+      <c r="L63" s="16"/>
       <c r="M63" s="16"/>
       <c r="N63" s="16"/>
-      <c r="O63" s="16"/>
-      <c r="P63" s="22" t="s">
+      <c r="O63" s="22" t="s">
         <v>1433</v>
       </c>
-      <c r="Q63" s="16" t="s">
+      <c r="P63" s="16" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B64" s="15" t="b">
         <v>1</v>
@@ -58987,31 +60536,30 @@
         <v>143</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>1426</v>
+        <v>1882</v>
       </c>
       <c r="I64" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="J64" s="16"/>
+      <c r="J64" s="16" t="s">
+        <v>1152</v>
+      </c>
       <c r="K64" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L64" s="16" t="s">
-        <v>1155</v>
-      </c>
+        <v>1429</v>
+      </c>
+      <c r="L64" s="16"/>
       <c r="M64" s="16"/>
       <c r="N64" s="16"/>
-      <c r="O64" s="16"/>
-      <c r="P64" s="22" t="s">
+      <c r="O64" s="22" t="s">
         <v>1433</v>
       </c>
-      <c r="Q64" s="16" t="s">
+      <c r="P64" s="16" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B65" s="15" t="b">
         <v>1</v>
@@ -59033,31 +60581,30 @@
         <v>143</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>1427</v>
+        <v>1056</v>
       </c>
       <c r="I65" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="J65" s="16"/>
+      <c r="J65" s="16" t="s">
+        <v>1152</v>
+      </c>
       <c r="K65" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L65" s="16" t="s">
-        <v>1431</v>
-      </c>
+        <v>1150</v>
+      </c>
+      <c r="L65" s="16"/>
       <c r="M65" s="16"/>
       <c r="N65" s="16"/>
-      <c r="O65" s="16"/>
-      <c r="P65" s="22" t="s">
+      <c r="O65" s="22" t="s">
         <v>1433</v>
       </c>
-      <c r="Q65" s="16" t="s">
+      <c r="P65" s="16" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B66" s="15" t="b">
         <v>1</v>
@@ -59079,65 +60626,199 @@
         <v>143</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="I66" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="J66" s="16"/>
+      <c r="J66" s="16" t="s">
+        <v>1152</v>
+      </c>
       <c r="K66" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="L66" s="16" t="s">
-        <v>1432</v>
-      </c>
+        <v>1430</v>
+      </c>
+      <c r="L66" s="16"/>
       <c r="M66" s="16"/>
       <c r="N66" s="16"/>
-      <c r="O66" s="16"/>
-      <c r="P66" s="22" t="s">
+      <c r="O66" s="22" t="s">
         <v>1433</v>
       </c>
-      <c r="Q66" s="16" t="s">
+      <c r="P66" s="16" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="16">
+        <v>685</v>
+      </c>
+      <c r="B67" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C67" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E67" s="17" t="str">
+        <f>IF(G67&lt;&gt;"",VLOOKUP(G67,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>1426</v>
+      </c>
+      <c r="I67" s="16" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>1155</v>
+      </c>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="22" t="s">
+        <v>1433</v>
+      </c>
+      <c r="P67" s="16" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="16">
+        <v>686</v>
+      </c>
       <c r="B68" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C68" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="F68" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="I68" s="15" t="s">
+      <c r="D68" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E68" s="17" t="str">
+        <f>IF(G68&lt;&gt;"",VLOOKUP(G68,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I68" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="K68" s="15" t="s">
+      <c r="J68" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>1431</v>
+      </c>
+      <c r="L68" s="16"/>
+      <c r="M68" s="16"/>
+      <c r="N68" s="16"/>
+      <c r="O68" s="22" t="s">
+        <v>1433</v>
+      </c>
+      <c r="P68" s="16" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="16">
+        <v>687</v>
+      </c>
+      <c r="B69" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C69" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E69" s="17" t="str">
+        <f>IF(G69&lt;&gt;"",VLOOKUP(G69,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>1428</v>
+      </c>
+      <c r="I69" s="16" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>1432</v>
+      </c>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+      <c r="O69" s="22" t="s">
+        <v>1433</v>
+      </c>
+      <c r="P69" s="16" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B71" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C71" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J71" s="15" t="s">
         <v>1863</v>
       </c>
-      <c r="M68" t="s">
+      <c r="L71" t="s">
         <v>1911</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B69" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C69" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="I69" s="15" t="s">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B72" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C72" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="I72" s="15" t="s">
         <v>1101</v>
       </c>
-      <c r="K69" s="15" t="s">
+      <c r="J72" s="15" t="s">
         <v>1866</v>
       </c>
-      <c r="M69" t="s">
+      <c r="L72" t="s">
         <v>1911</v>
       </c>
     </row>
@@ -59147,7 +60828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52738BB-55BF-8748-8C35-72338C2A6B88}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:O9"/>
@@ -59482,7 +61163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61AACA08-9138-E54D-BAC1-6C74392A11F1}">
   <sheetPr codeName="Sheet27"/>
   <dimension ref="A1:C1173"/>

--- a/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
+++ b/odm_map_maker/data/mapping_config_files/pha4ge_to_odm_v2_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinwellman/Documents/Health/Wastewater/PHES-ODM-MapGenerator/PHES-ODM-MapGenerator/odm_map_maker/data/mapping_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20496620-5BF8-824E-80A7-FE087193A186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58480776-F019-1347-84EC-A5CA5C68AD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20920" firstSheet="19" activeTab="31" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="40960" windowHeight="20760" firstSheet="20" activeTab="20" xr2:uid="{D031FD9F-8EDE-1249-89E5-2C42697DC0B4}"/>
   </bookViews>
   <sheets>
     <sheet name="global_enums" sheetId="42" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9786" uniqueCount="2114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9797" uniqueCount="2118">
   <si>
     <t>Complete</t>
   </si>
@@ -6136,7 +6136,391 @@
     <t>value_expr</t>
   </si>
   <si>
-    <t>value_map = {
+    <t>sourceEnum</t>
+  </si>
+  <si>
+    <t>NullValueMenu</t>
+  </si>
+  <si>
+    <t>miss</t>
+  </si>
+  <si>
+    <t>dnc</t>
+  </si>
+  <si>
+    <t>enumDerivationSettings</t>
+  </si>
+  <si>
+    <t>target = [v.split("[")[0].strip() for v in src.sequencing_instrument]</t>
+  </si>
+  <si>
+    <t>target = [v.split("[")[0].strip() for v in src.sequencing_platform]</t>
+  </si>
+  <si>
+    <t>{
+    "purpose_value": "{{purpose of sampling}}",
+    "saMaterial_value": "{{environmental material}}",
+    "repType_value": "{{experimental specimen role type}}"
+}</t>
+  </si>
+  <si>
+    <t>_extra_custodyCont_contactID_tag_value</t>
+  </si>
+  <si>
+    <t>_extra_funderCont_contactID_tag_value</t>
+  </si>
+  <si>
+    <t>_extra_measures_measure_tag</t>
+  </si>
+  <si>
+    <t>reportable_value</t>
+  </si>
+  <si>
+    <t>{{quality control determination}}</t>
+  </si>
+  <si>
+    <t>{ mirror_source: False }</t>
+  </si>
+  <si>
+    <t>pooled</t>
+  </si>
+  <si>
+    <t>def is_pooled(values):
+    values = [v.lower().split('[')[0].strip() for v in values if isinstance(v, str)]
+    values = [v for v in values if v == "pooling specimens"]
+    return len(values) &gt; 0
+target = is_pooled(src.specimen_processing)</t>
+  </si>
+  <si>
+    <t>sampleID_expr</t>
+  </si>
+  <si>
+    <t>_extra_code_selector_value</t>
+  </si>
+  <si>
+    <t>replicate</t>
+  </si>
+  <si>
+    <t>def is_replicate(values, rep_type):
+    values = [v.lower().split('[')[0].strip() for v in values if isinstance(v, str)]
+    values = [v for v in values if v == f"{rep_type} replicate process"]
+    return len(values) &gt; 0
+if is_replicate(src.specimen_processing, "technical"):
+    target = "techRep"
+else:
+    target = ""</t>
+  </si>
+  <si>
+    <t>def is_replicate(values, rep_type):
+    values = [v.lower().split('[')[0].strip() for v in values if isinstance(v, str)]
+    values = [v for v in values if v == f"{rep_type} replicate process"]
+    return len(values) &gt; 0
+if is_replicate(src.specimen_processing, "biological"):
+    target = "bioRep"
+else:
+    target = ""</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>biological replicate</t>
+  </si>
+  <si>
+    <t>technical replicate</t>
+  </si>
+  <si>
+    <t>_extra_sample_type_tag_value</t>
+  </si>
+  <si>
+    <t>_extra_sample_type_paired_tag_value</t>
+  </si>
+  <si>
+    <t>technical replicate ID</t>
+  </si>
+  <si>
+    <t>biological replicate ID</t>
+  </si>
+  <si>
+    <t>{
+  "saMaterial_value": "",
+  "pooled_value": "",
+  "collNum_value": "",
+  "collType_value": ""
+}</t>
+  </si>
+  <si>
+    <t>pos</t>
+  </si>
+  <si>
+    <t>n50</t>
+  </si>
+  <si>
+    <t>{{n50}}</t>
+  </si>
+  <si>
+    <t>OrganismMenu</t>
+  </si>
+  <si>
+    <t>sarsCov2</t>
+  </si>
+  <si>
+    <t>Severe acute respiratory syndrome coronavirus 2</t>
+  </si>
+  <si>
+    <t>diagnostic measurement unit 1</t>
+  </si>
+  <si>
+    <t>diagnostic measurement unit 2</t>
+  </si>
+  <si>
+    <t>diagnostic measurement unit 3</t>
+  </si>
+  <si>
+    <t>uL</t>
+  </si>
+  <si>
+    <t>cycle threshold (Ct)</t>
+  </si>
+  <si>
+    <t>cone</t>
+  </si>
+  <si>
+    <t>sm</t>
+  </si>
+  <si>
+    <t>"ngsInst"</t>
+  </si>
+  <si>
+    <t>sit</t>
+  </si>
+  <si>
+    <t>E gene (orf4)</t>
+  </si>
+  <si>
+    <t>M gene (orf5)</t>
+  </si>
+  <si>
+    <t>N gene (orf9)</t>
+  </si>
+  <si>
+    <t>Spike gene (orf2)</t>
+  </si>
+  <si>
+    <t>orf1ab (rep)</t>
+  </si>
+  <si>
+    <t>orf1a (pp1a)</t>
+  </si>
+  <si>
+    <t>nsp11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">nsp10 </t>
+  </si>
+  <si>
+    <t>RdRp gene (nsp12)</t>
+  </si>
+  <si>
+    <t>hel gene (nsp13)</t>
+  </si>
+  <si>
+    <t>exoN gene (nsp14)</t>
+  </si>
+  <si>
+    <t>nsp15</t>
+  </si>
+  <si>
+    <t>nsp16</t>
+  </si>
+  <si>
+    <t>orf3a</t>
+  </si>
+  <si>
+    <t>orf3b</t>
+  </si>
+  <si>
+    <t>orf6 (ns6)</t>
+  </si>
+  <si>
+    <t>orf7a</t>
+  </si>
+  <si>
+    <t>orf7b (ns7b)</t>
+  </si>
+  <si>
+    <t>orf8 (ns8)</t>
+  </si>
+  <si>
+    <t>orf9b</t>
+  </si>
+  <si>
+    <t>orf9c</t>
+  </si>
+  <si>
+    <t>orf10</t>
+  </si>
+  <si>
+    <t>orf14</t>
+  </si>
+  <si>
+    <t>SARS-COV-2 5' UTR</t>
+  </si>
+  <si>
+    <t>covE</t>
+  </si>
+  <si>
+    <t>covM</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>spikeGene</t>
+  </si>
+  <si>
+    <t>orf1ab</t>
+  </si>
+  <si>
+    <t>orf1a</t>
+  </si>
+  <si>
+    <t>nsp1</t>
+  </si>
+  <si>
+    <t>nsp2</t>
+  </si>
+  <si>
+    <t>nsp3</t>
+  </si>
+  <si>
+    <t>nsp4</t>
+  </si>
+  <si>
+    <t>nsp5</t>
+  </si>
+  <si>
+    <t>nsp6</t>
+  </si>
+  <si>
+    <t>nsp7</t>
+  </si>
+  <si>
+    <t>nsp8</t>
+  </si>
+  <si>
+    <t>nsp9</t>
+  </si>
+  <si>
+    <t>nsp10</t>
+  </si>
+  <si>
+    <t>covRdrp</t>
+  </si>
+  <si>
+    <t>hel</t>
+  </si>
+  <si>
+    <t>exoNnsp14</t>
+  </si>
+  <si>
+    <t>orf6</t>
+  </si>
+  <si>
+    <t>orf7b</t>
+  </si>
+  <si>
+    <t>orf8</t>
+  </si>
+  <si>
+    <t>covUTR5</t>
+  </si>
+  <si>
+    <t>GeneSymbolMenu</t>
+  </si>
+  <si>
+    <t>randomSurv</t>
+  </si>
+  <si>
+    <t>targetSurv</t>
+  </si>
+  <si>
+    <t>emergSurv</t>
+  </si>
+  <si>
+    <t>longSurv</t>
+  </si>
+  <si>
+    <t>travelSurv</t>
+  </si>
+  <si>
+    <t>domSurv</t>
+  </si>
+  <si>
+    <t>internatSurv</t>
+  </si>
+  <si>
+    <t>if isinstance(src.environmental_material, str) and "Bar Screen" in src.environmental_material:
+    target = "barScreen"</t>
+  </si>
+  <si>
+    <t>Bar screen</t>
+  </si>
+  <si>
+    <t>_extra_environmental_site</t>
+  </si>
+  <si>
+    <t>_extra_mapped_collection_device</t>
+  </si>
+  <si>
+    <t>_extra_mapped_collection_method</t>
+  </si>
+  <si>
+    <t>if len([d for d in slot('_extra_mapped_collection_device') if isinstance(d, str) and len(d) &gt; 0]):
+    target = slot('_extra_mapped_collection_device')
+else:
+    target = slot('_extra_mapped_collection_method')</t>
+  </si>
+  <si>
+    <t>_extra_mapped_environmental_site</t>
+  </si>
+  <si>
+    <t>target = (lambda v: v)(slot('_extra_mapped_environmental_site'))
+if len([v for v in src.environmental_material if "bar screen" in str(v).lower()]) &gt; 0:
+    target.append("siteType:barScreen")</t>
+  </si>
+  <si>
+    <t>value_map = (lambda v: v)({
     "Concentration": "NR",
     "Centrifugation": "cent",
     "Filtration": "filt",
@@ -6146,380 +6530,8 @@
     "Gravity separation": "graSet",
     "Growth in enrichment broth": "growBroth",
     "Pasteurization": "TRUE",
-}
+})
 target = [value_map.get(str(v).split("[")[0].strip(), "") for v in src.specimen_processing]</t>
-  </si>
-  <si>
-    <t>sourceEnum</t>
-  </si>
-  <si>
-    <t>NullValueMenu</t>
-  </si>
-  <si>
-    <t>miss</t>
-  </si>
-  <si>
-    <t>dnc</t>
-  </si>
-  <si>
-    <t>if len([d for d in emap.collection_device if isinstance(d, str) and len(d) &gt; 0]):
-    target = emap.collection_device
-else:
-    target = emap.collection_method</t>
-  </si>
-  <si>
-    <t>enumDerivationSettings</t>
-  </si>
-  <si>
-    <t>target = [v.split("[")[0].strip() for v in src.sequencing_instrument]</t>
-  </si>
-  <si>
-    <t>target = [v.split("[")[0].strip() for v in src.sequencing_platform]</t>
-  </si>
-  <si>
-    <t>{
-    "purpose_value": "{{purpose of sampling}}",
-    "saMaterial_value": "{{environmental material}}",
-    "repType_value": "{{experimental specimen role type}}"
-}</t>
-  </si>
-  <si>
-    <t>_extra_custodyCont_contactID_tag_value</t>
-  </si>
-  <si>
-    <t>_extra_funderCont_contactID_tag_value</t>
-  </si>
-  <si>
-    <t>_extra_measures_measure_tag</t>
-  </si>
-  <si>
-    <t>reportable_value</t>
-  </si>
-  <si>
-    <t>{{quality control determination}}</t>
-  </si>
-  <si>
-    <t>{ mirror_source: False }</t>
-  </si>
-  <si>
-    <t>pooled</t>
-  </si>
-  <si>
-    <t>def is_pooled(values):
-    values = [v.lower().split('[')[0].strip() for v in values if isinstance(v, str)]
-    values = [v for v in values if v == "pooling specimens"]
-    return len(values) &gt; 0
-target = is_pooled(src.specimen_processing)</t>
-  </si>
-  <si>
-    <t>sampleID_expr</t>
-  </si>
-  <si>
-    <t>_extra_code_selector_value</t>
-  </si>
-  <si>
-    <t>replicate</t>
-  </si>
-  <si>
-    <t>def is_replicate(values, rep_type):
-    values = [v.lower().split('[')[0].strip() for v in values if isinstance(v, str)]
-    values = [v for v in values if v == f"{rep_type} replicate process"]
-    return len(values) &gt; 0
-if is_replicate(src.specimen_processing, "technical"):
-    target = "techRep"
-else:
-    target = ""</t>
-  </si>
-  <si>
-    <t>def is_replicate(values, rep_type):
-    values = [v.lower().split('[')[0].strip() for v in values if isinstance(v, str)]
-    values = [v for v in values if v == f"{rep_type} replicate process"]
-    return len(values) &gt; 0
-if is_replicate(src.specimen_processing, "biological"):
-    target = "bioRep"
-else:
-    target = ""</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>event</t>
-  </si>
-  <si>
-    <t>biological replicate</t>
-  </si>
-  <si>
-    <t>technical replicate</t>
-  </si>
-  <si>
-    <t>_extra_sample_type_tag_value</t>
-  </si>
-  <si>
-    <t>_extra_sample_type_paired_tag_value</t>
-  </si>
-  <si>
-    <t>technical replicate ID</t>
-  </si>
-  <si>
-    <t>biological replicate ID</t>
-  </si>
-  <si>
-    <t>{
-  "saMaterial_value": "",
-  "pooled_value": "",
-  "collNum_value": "",
-  "collType_value": ""
-}</t>
-  </si>
-  <si>
-    <t>pos</t>
-  </si>
-  <si>
-    <t>n50</t>
-  </si>
-  <si>
-    <t>{{n50}}</t>
-  </si>
-  <si>
-    <t>OrganismMenu</t>
-  </si>
-  <si>
-    <t>sarsCov2</t>
-  </si>
-  <si>
-    <t>Severe acute respiratory syndrome coronavirus 2</t>
-  </si>
-  <si>
-    <t>diagnostic measurement unit 1</t>
-  </si>
-  <si>
-    <t>diagnostic measurement unit 2</t>
-  </si>
-  <si>
-    <t>diagnostic measurement unit 3</t>
-  </si>
-  <si>
-    <t>uL</t>
-  </si>
-  <si>
-    <t>cycle threshold (Ct)</t>
-  </si>
-  <si>
-    <t>cone</t>
-  </si>
-  <si>
-    <t>sm</t>
-  </si>
-  <si>
-    <t>"ngsInst"</t>
-  </si>
-  <si>
-    <t>sit</t>
-  </si>
-  <si>
-    <t>E gene (orf4)</t>
-  </si>
-  <si>
-    <t>M gene (orf5)</t>
-  </si>
-  <si>
-    <t>N gene (orf9)</t>
-  </si>
-  <si>
-    <t>Spike gene (orf2)</t>
-  </si>
-  <si>
-    <t>orf1ab (rep)</t>
-  </si>
-  <si>
-    <t>orf1a (pp1a)</t>
-  </si>
-  <si>
-    <t>nsp11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp4 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp5 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp6 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp8 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp9 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nsp10 </t>
-  </si>
-  <si>
-    <t>RdRp gene (nsp12)</t>
-  </si>
-  <si>
-    <t>hel gene (nsp13)</t>
-  </si>
-  <si>
-    <t>exoN gene (nsp14)</t>
-  </si>
-  <si>
-    <t>nsp15</t>
-  </si>
-  <si>
-    <t>nsp16</t>
-  </si>
-  <si>
-    <t>orf3a</t>
-  </si>
-  <si>
-    <t>orf3b</t>
-  </si>
-  <si>
-    <t>orf6 (ns6)</t>
-  </si>
-  <si>
-    <t>orf7a</t>
-  </si>
-  <si>
-    <t>orf7b (ns7b)</t>
-  </si>
-  <si>
-    <t>orf8 (ns8)</t>
-  </si>
-  <si>
-    <t>orf9b</t>
-  </si>
-  <si>
-    <t>orf9c</t>
-  </si>
-  <si>
-    <t>orf10</t>
-  </si>
-  <si>
-    <t>orf14</t>
-  </si>
-  <si>
-    <t>SARS-COV-2 5' UTR</t>
-  </si>
-  <si>
-    <t>covE</t>
-  </si>
-  <si>
-    <t>covM</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>spikeGene</t>
-  </si>
-  <si>
-    <t>orf1ab</t>
-  </si>
-  <si>
-    <t>orf1a</t>
-  </si>
-  <si>
-    <t>nsp1</t>
-  </si>
-  <si>
-    <t>nsp2</t>
-  </si>
-  <si>
-    <t>nsp3</t>
-  </si>
-  <si>
-    <t>nsp4</t>
-  </si>
-  <si>
-    <t>nsp5</t>
-  </si>
-  <si>
-    <t>nsp6</t>
-  </si>
-  <si>
-    <t>nsp7</t>
-  </si>
-  <si>
-    <t>nsp8</t>
-  </si>
-  <si>
-    <t>nsp9</t>
-  </si>
-  <si>
-    <t>nsp10</t>
-  </si>
-  <si>
-    <t>covRdrp</t>
-  </si>
-  <si>
-    <t>hel</t>
-  </si>
-  <si>
-    <t>exoNnsp14</t>
-  </si>
-  <si>
-    <t>orf6</t>
-  </si>
-  <si>
-    <t>orf7b</t>
-  </si>
-  <si>
-    <t>orf8</t>
-  </si>
-  <si>
-    <t>covUTR5</t>
-  </si>
-  <si>
-    <t>GeneSymbolMenu</t>
-  </si>
-  <si>
-    <t>randomSurv</t>
-  </si>
-  <si>
-    <t>targetSurv</t>
-  </si>
-  <si>
-    <t>emergSurv</t>
-  </si>
-  <si>
-    <t>longSurv</t>
-  </si>
-  <si>
-    <t>travelSurv</t>
-  </si>
-  <si>
-    <t>domSurv</t>
-  </si>
-  <si>
-    <t>internatSurv</t>
-  </si>
-  <si>
-    <t>if isinstance(src.environmental_material, str) and "Bar Screen" in src.environmental_material:
-    target = "barScreen"</t>
-  </si>
-  <si>
-    <t>Bar screen</t>
-  </si>
-  <si>
-    <t>target = emap.environmental_site
-if len([v for v in src.environmental_material if "bar screen" in str(v).lower()]) &gt; 0:
-    target.append("siteType:barScreen")</t>
   </si>
 </sst>
 </file>
@@ -7006,10 +7018,10 @@
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -7041,6 +7053,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="summary"/>
@@ -21044,7 +21057,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>3</v>
@@ -21053,12 +21066,12 @@
         <v>6</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B2" t="s">
         <v>363</v>
@@ -21067,34 +21080,34 @@
         <v>368</v>
       </c>
       <c r="D2" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B3" t="s">
         <v>366</v>
       </c>
       <c r="C3" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B4" t="s">
         <v>364</v>
       </c>
       <c r="C4" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B5" t="s">
         <v>365</v>
@@ -21105,7 +21118,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B6" t="s">
         <v>367</v>
@@ -21116,13 +21129,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B8" t="s">
         <v>2035</v>
       </c>
-      <c r="B8" t="s">
-        <v>2037</v>
-      </c>
       <c r="C8" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
   </sheetData>
@@ -21720,7 +21733,7 @@
         <v>1803</v>
       </c>
       <c r="S1" s="16" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="T1" s="17" t="s">
         <v>1634</v>
@@ -21777,7 +21790,7 @@
         <v>127</v>
       </c>
       <c r="P2" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q2" t="s">
         <v>954</v>
@@ -21828,7 +21841,7 @@
         <v>127</v>
       </c>
       <c r="P3" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q3" t="s">
         <v>955</v>
@@ -21930,7 +21943,7 @@
         <v>127</v>
       </c>
       <c r="P5" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q5" t="s">
         <v>957</v>
@@ -21987,7 +22000,7 @@
         <v>127</v>
       </c>
       <c r="P7" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q7" t="s">
         <v>962</v>
@@ -22035,7 +22048,7 @@
         <v>127</v>
       </c>
       <c r="P8" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q8" t="s">
         <v>962</v>
@@ -22083,7 +22096,7 @@
         <v>127</v>
       </c>
       <c r="P9" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q9" t="s">
         <v>962</v>
@@ -22137,7 +22150,7 @@
         <v>127</v>
       </c>
       <c r="P11" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q11" t="s">
         <v>964</v>
@@ -22185,7 +22198,7 @@
         <v>127</v>
       </c>
       <c r="P13" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q13" t="s">
         <v>965</v>
@@ -22242,7 +22255,7 @@
         <v>127</v>
       </c>
       <c r="P15" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q15" t="s">
         <v>966</v>
@@ -22296,7 +22309,7 @@
         <v>127</v>
       </c>
       <c r="P16" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q16" t="s">
         <v>966</v>
@@ -22350,7 +22363,7 @@
         <v>127</v>
       </c>
       <c r="P17" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q17" t="s">
         <v>966</v>
@@ -22404,7 +22417,7 @@
         <v>127</v>
       </c>
       <c r="P18" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q18" t="s">
         <v>966</v>
@@ -22458,7 +22471,7 @@
         <v>127</v>
       </c>
       <c r="P19" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q19" t="s">
         <v>966</v>
@@ -22512,7 +22525,7 @@
         <v>127</v>
       </c>
       <c r="P20" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q20" t="s">
         <v>966</v>
@@ -22566,7 +22579,7 @@
         <v>127</v>
       </c>
       <c r="P21" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q21" t="s">
         <v>966</v>
@@ -22623,7 +22636,7 @@
         <v>127</v>
       </c>
       <c r="P23" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q23" t="s">
         <v>974</v>
@@ -22683,7 +22696,7 @@
         <v>127</v>
       </c>
       <c r="P25" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q25" t="s">
         <v>984</v>
@@ -22734,7 +22747,7 @@
         <v>127</v>
       </c>
       <c r="P26" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q26" t="s">
         <v>984</v>
@@ -22785,7 +22798,7 @@
         <v>127</v>
       </c>
       <c r="P27" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q27" t="s">
         <v>984</v>
@@ -22836,7 +22849,7 @@
         <v>127</v>
       </c>
       <c r="P28" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q28" t="s">
         <v>984</v>
@@ -22887,7 +22900,7 @@
         <v>127</v>
       </c>
       <c r="P29" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q29" t="s">
         <v>984</v>
@@ -22938,7 +22951,7 @@
         <v>127</v>
       </c>
       <c r="P30" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q30" t="s">
         <v>984</v>
@@ -22989,7 +23002,7 @@
         <v>127</v>
       </c>
       <c r="P31" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q31" t="s">
         <v>984</v>
@@ -23040,7 +23053,7 @@
         <v>127</v>
       </c>
       <c r="P32" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q32" t="s">
         <v>984</v>
@@ -23097,7 +23110,7 @@
         <v>127</v>
       </c>
       <c r="P34" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q34" t="s">
         <v>991</v>
@@ -23148,7 +23161,7 @@
         <v>127</v>
       </c>
       <c r="P35" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q35" t="s">
         <v>991</v>
@@ -23199,7 +23212,7 @@
         <v>127</v>
       </c>
       <c r="P36" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q36" t="s">
         <v>991</v>
@@ -23250,7 +23263,7 @@
         <v>127</v>
       </c>
       <c r="P37" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q37" t="s">
         <v>991</v>
@@ -23301,7 +23314,7 @@
         <v>127</v>
       </c>
       <c r="P38" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q38" t="s">
         <v>991</v>
@@ -23352,7 +23365,7 @@
         <v>127</v>
       </c>
       <c r="P39" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q39" t="s">
         <v>991</v>
@@ -23403,7 +23416,7 @@
         <v>127</v>
       </c>
       <c r="P40" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q40" t="s">
         <v>991</v>
@@ -23454,7 +23467,7 @@
         <v>127</v>
       </c>
       <c r="P41" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q41" t="s">
         <v>991</v>
@@ -23694,7 +23707,7 @@
         <v>1650</v>
       </c>
       <c r="E47" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="F47" t="s">
         <v>1910</v>
@@ -23718,10 +23731,10 @@
         <v>953</v>
       </c>
       <c r="Q47" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="V47" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="W47" t="s">
         <v>1227</v>
@@ -24403,7 +24416,7 @@
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q61" t="s">
         <v>1261</v>
@@ -24589,7 +24602,7 @@
         <v>127</v>
       </c>
       <c r="P65" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q65" t="s">
         <v>1265</v>
@@ -24637,7 +24650,7 @@
         <v>127</v>
       </c>
       <c r="P66" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q66" t="s">
         <v>1266</v>
@@ -24829,7 +24842,7 @@
         <v>127</v>
       </c>
       <c r="P70" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q70" t="s">
         <v>1275</v>
@@ -24880,7 +24893,7 @@
         <v>127</v>
       </c>
       <c r="P71" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q71" t="s">
         <v>1275</v>
@@ -25829,7 +25842,7 @@
         <v>1201</v>
       </c>
       <c r="P93" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q93" t="s">
         <v>1397</v>
@@ -25880,7 +25893,7 @@
         <v>1201</v>
       </c>
       <c r="P94" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q94" t="s">
         <v>1397</v>
@@ -25931,7 +25944,7 @@
         <v>1201</v>
       </c>
       <c r="P95" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q95" t="s">
         <v>1397</v>
@@ -25982,7 +25995,7 @@
         <v>1201</v>
       </c>
       <c r="P96" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q96" t="s">
         <v>1397</v>
@@ -26033,7 +26046,7 @@
         <v>1201</v>
       </c>
       <c r="P97" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q97" t="s">
         <v>1397</v>
@@ -26084,7 +26097,7 @@
         <v>1201</v>
       </c>
       <c r="P98" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q98" t="s">
         <v>1397</v>
@@ -26135,7 +26148,7 @@
         <v>1201</v>
       </c>
       <c r="P99" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q99" t="s">
         <v>1397</v>
@@ -26186,7 +26199,7 @@
         <v>1201</v>
       </c>
       <c r="P100" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q100" t="s">
         <v>1397</v>
@@ -26237,7 +26250,7 @@
         <v>1201</v>
       </c>
       <c r="P101" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q101" t="s">
         <v>1397</v>
@@ -26288,7 +26301,7 @@
         <v>1201</v>
       </c>
       <c r="P102" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q102" t="s">
         <v>1397</v>
@@ -26339,7 +26352,7 @@
         <v>1201</v>
       </c>
       <c r="P103" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q103" t="s">
         <v>1397</v>
@@ -26396,7 +26409,7 @@
         <v>1201</v>
       </c>
       <c r="P105" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q105" t="s">
         <v>1402</v>
@@ -26453,7 +26466,7 @@
         <v>1201</v>
       </c>
       <c r="P106" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q106" t="s">
         <v>1402</v>
@@ -26510,7 +26523,7 @@
         <v>1201</v>
       </c>
       <c r="P107" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q107" t="s">
         <v>1402</v>
@@ -26567,7 +26580,7 @@
         <v>1201</v>
       </c>
       <c r="P108" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q108" t="s">
         <v>1402</v>
@@ -26624,7 +26637,7 @@
         <v>1201</v>
       </c>
       <c r="P109" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q109" t="s">
         <v>1402</v>
@@ -26681,7 +26694,7 @@
         <v>1201</v>
       </c>
       <c r="P110" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q110" t="s">
         <v>1402</v>
@@ -26738,7 +26751,7 @@
         <v>1201</v>
       </c>
       <c r="P111" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q111" t="s">
         <v>1402</v>
@@ -26795,7 +26808,7 @@
         <v>1201</v>
       </c>
       <c r="P112" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q112" t="s">
         <v>1402</v>
@@ -26852,7 +26865,7 @@
         <v>1201</v>
       </c>
       <c r="P113" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q113" t="s">
         <v>1402</v>
@@ -26909,7 +26922,7 @@
         <v>1201</v>
       </c>
       <c r="P114" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q114" t="s">
         <v>1402</v>
@@ -26966,7 +26979,7 @@
         <v>1201</v>
       </c>
       <c r="P115" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q115" t="s">
         <v>1402</v>
@@ -27026,7 +27039,7 @@
         <v>1201</v>
       </c>
       <c r="P116" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q116" t="s">
         <v>1402</v>
@@ -27086,7 +27099,7 @@
         <v>1201</v>
       </c>
       <c r="P117" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q117" t="s">
         <v>1402</v>
@@ -27146,7 +27159,7 @@
         <v>1201</v>
       </c>
       <c r="P118" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q118" t="s">
         <v>1402</v>
@@ -27206,7 +27219,7 @@
         <v>1201</v>
       </c>
       <c r="P119" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q119" t="s">
         <v>1402</v>
@@ -27266,7 +27279,7 @@
         <v>1201</v>
       </c>
       <c r="P120" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q120" t="s">
         <v>1402</v>
@@ -27326,7 +27339,7 @@
         <v>1201</v>
       </c>
       <c r="P121" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="Q121" t="s">
         <v>1402</v>
@@ -27896,7 +27909,7 @@
         <v>1989</v>
       </c>
       <c r="S138" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="T138" t="s">
         <v>1814</v>
@@ -27955,7 +27968,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="G1" s="17" t="s">
         <v>2</v>
@@ -28441,7 +28454,7 @@
         <v>896</v>
       </c>
       <c r="K17" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>905</v>
@@ -28926,7 +28939,7 @@
         <v>48</v>
       </c>
       <c r="H32" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="I32" t="s">
         <v>884</v>
@@ -31522,7 +31535,7 @@
         <v>1650</v>
       </c>
       <c r="G118" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H118" t="s">
         <v>322</v>
@@ -31561,10 +31574,10 @@
         <v>1650</v>
       </c>
       <c r="G119" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H119" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="I119" t="s">
         <v>884</v>
@@ -31597,7 +31610,7 @@
         <v>1650</v>
       </c>
       <c r="G120" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H120" t="s">
         <v>326</v>
@@ -31633,7 +31646,7 @@
         <v>1650</v>
       </c>
       <c r="G121" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H121" t="s">
         <v>327</v>
@@ -31669,7 +31682,7 @@
         <v>1650</v>
       </c>
       <c r="G122" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H122" t="s">
         <v>328</v>
@@ -31705,7 +31718,7 @@
         <v>1650</v>
       </c>
       <c r="G123" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H123" t="s">
         <v>329</v>
@@ -31741,7 +31754,7 @@
         <v>1650</v>
       </c>
       <c r="G124" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="H124" t="s">
         <v>330</v>
@@ -31777,7 +31790,7 @@
         <v>1650</v>
       </c>
       <c r="G125" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H125" t="s">
         <v>322</v>
@@ -31816,10 +31829,10 @@
         <v>1650</v>
       </c>
       <c r="G126" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H126" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="I126" t="s">
         <v>884</v>
@@ -31852,7 +31865,7 @@
         <v>1650</v>
       </c>
       <c r="G127" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H127" t="s">
         <v>326</v>
@@ -31888,7 +31901,7 @@
         <v>1650</v>
       </c>
       <c r="G128" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H128" t="s">
         <v>327</v>
@@ -31924,7 +31937,7 @@
         <v>1650</v>
       </c>
       <c r="G129" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H129" t="s">
         <v>328</v>
@@ -31960,7 +31973,7 @@
         <v>1650</v>
       </c>
       <c r="G130" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H130" t="s">
         <v>329</v>
@@ -31996,7 +32009,7 @@
         <v>1650</v>
       </c>
       <c r="G131" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="H131" t="s">
         <v>330</v>
@@ -32032,7 +32045,7 @@
         <v>1650</v>
       </c>
       <c r="G132" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H132" t="s">
         <v>322</v>
@@ -32071,10 +32084,10 @@
         <v>1650</v>
       </c>
       <c r="G133" t="s">
+        <v>2038</v>
+      </c>
+      <c r="H133" t="s">
         <v>2040</v>
-      </c>
-      <c r="H133" t="s">
-        <v>2042</v>
       </c>
       <c r="I133" t="s">
         <v>884</v>
@@ -32107,7 +32120,7 @@
         <v>1650</v>
       </c>
       <c r="G134" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H134" t="s">
         <v>326</v>
@@ -32143,7 +32156,7 @@
         <v>1650</v>
       </c>
       <c r="G135" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H135" t="s">
         <v>327</v>
@@ -32179,7 +32192,7 @@
         <v>1650</v>
       </c>
       <c r="G136" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H136" t="s">
         <v>328</v>
@@ -32215,7 +32228,7 @@
         <v>1650</v>
       </c>
       <c r="G137" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H137" t="s">
         <v>329</v>
@@ -32251,7 +32264,7 @@
         <v>1650</v>
       </c>
       <c r="G138" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="H138" t="s">
         <v>330</v>
@@ -32571,7 +32584,7 @@
         <v>896</v>
       </c>
       <c r="K148" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="N148" s="1" t="s">
         <v>905</v>
@@ -32682,7 +32695,7 @@
         <v>1850</v>
       </c>
       <c r="K152" s="15" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="L152" s="15"/>
       <c r="M152" s="15"/>
@@ -32724,7 +32737,7 @@
         <v>1850</v>
       </c>
       <c r="K153" s="15" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="L153" s="15"/>
       <c r="M153" s="15"/>
@@ -32764,7 +32777,7 @@
         <v>1850</v>
       </c>
       <c r="K154" s="15" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
       <c r="L154" s="15"/>
       <c r="M154" s="15"/>
@@ -32804,7 +32817,7 @@
         <v>1850</v>
       </c>
       <c r="K155" s="15" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="L155" s="15"/>
       <c r="M155" s="15"/>
@@ -32844,7 +32857,7 @@
         <v>1850</v>
       </c>
       <c r="K156" s="15" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
       <c r="L156" s="15"/>
       <c r="M156" s="15"/>
@@ -32884,7 +32897,7 @@
         <v>1850</v>
       </c>
       <c r="K157" s="15" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="L157" s="15"/>
       <c r="M157" s="15"/>
@@ -32924,7 +32937,7 @@
         <v>1850</v>
       </c>
       <c r="K158" s="15" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
       <c r="L158" s="15"/>
       <c r="M158" s="15"/>
@@ -33074,7 +33087,7 @@
       <c r="G163" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="H163" s="77" t="s">
+      <c r="H163" s="76" t="s">
         <v>1875</v>
       </c>
       <c r="I163" s="15" t="s">
@@ -33221,16 +33234,16 @@
         <v>1650</v>
       </c>
       <c r="F170" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H170" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="I170" t="s">
         <v>884</v>
       </c>
       <c r="K170" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.2">
@@ -33245,16 +33258,16 @@
         <v>1650</v>
       </c>
       <c r="F171" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H171" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="I171" t="s">
         <v>884</v>
       </c>
       <c r="K171" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.2">
@@ -33269,16 +33282,16 @@
         <v>1650</v>
       </c>
       <c r="F172" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H172" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="I172" t="s">
         <v>884</v>
       </c>
       <c r="K172" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.2">
@@ -33293,16 +33306,16 @@
         <v>1650</v>
       </c>
       <c r="F173" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H173" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="I173" t="s">
         <v>884</v>
       </c>
       <c r="K173" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.2">
@@ -33317,16 +33330,16 @@
         <v>1650</v>
       </c>
       <c r="F174" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H174" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="I174" t="s">
         <v>884</v>
       </c>
       <c r="K174" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.2">
@@ -33341,16 +33354,16 @@
         <v>1650</v>
       </c>
       <c r="F175" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H175" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="I175" t="s">
         <v>884</v>
       </c>
       <c r="K175" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.2">
@@ -33365,16 +33378,16 @@
         <v>1650</v>
       </c>
       <c r="F176" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H176" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="I176" t="s">
         <v>884</v>
       </c>
       <c r="K176" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.2">
@@ -33389,16 +33402,16 @@
         <v>1650</v>
       </c>
       <c r="F177" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H177" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="I177" t="s">
         <v>884</v>
       </c>
       <c r="K177" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.2">
@@ -33413,16 +33426,16 @@
         <v>1650</v>
       </c>
       <c r="F178" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H178" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="I178" t="s">
         <v>884</v>
       </c>
       <c r="K178" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.2">
@@ -33437,16 +33450,16 @@
         <v>1650</v>
       </c>
       <c r="F179" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H179" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="I179" t="s">
         <v>884</v>
       </c>
       <c r="K179" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.2">
@@ -33461,16 +33474,16 @@
         <v>1650</v>
       </c>
       <c r="F180" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H180" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="I180" t="s">
         <v>884</v>
       </c>
       <c r="K180" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.2">
@@ -33485,16 +33498,16 @@
         <v>1650</v>
       </c>
       <c r="F181" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H181" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="I181" t="s">
         <v>884</v>
       </c>
       <c r="K181" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.2">
@@ -33509,16 +33522,16 @@
         <v>1650</v>
       </c>
       <c r="F182" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H182" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="I182" t="s">
         <v>884</v>
       </c>
       <c r="K182" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.2">
@@ -33533,16 +33546,16 @@
         <v>1650</v>
       </c>
       <c r="F183" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H183" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="I183" t="s">
         <v>884</v>
       </c>
       <c r="K183" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.2">
@@ -33557,16 +33570,16 @@
         <v>1650</v>
       </c>
       <c r="F184" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H184" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="I184" t="s">
         <v>884</v>
       </c>
       <c r="K184" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.2">
@@ -33581,16 +33594,16 @@
         <v>1650</v>
       </c>
       <c r="F185" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H185" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="I185" t="s">
         <v>884</v>
       </c>
       <c r="K185" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.2">
@@ -33605,16 +33618,16 @@
         <v>1650</v>
       </c>
       <c r="F186" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H186" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="I186" t="s">
         <v>884</v>
       </c>
       <c r="K186" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="187" spans="2:11" x14ac:dyDescent="0.2">
@@ -33629,16 +33642,16 @@
         <v>1650</v>
       </c>
       <c r="F187" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H187" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="I187" t="s">
         <v>884</v>
       </c>
       <c r="K187" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.2">
@@ -33653,16 +33666,16 @@
         <v>1650</v>
       </c>
       <c r="F188" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H188" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="I188" t="s">
         <v>884</v>
       </c>
       <c r="K188" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="189" spans="2:11" x14ac:dyDescent="0.2">
@@ -33677,16 +33690,16 @@
         <v>1650</v>
       </c>
       <c r="F189" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H189" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="I189" t="s">
         <v>884</v>
       </c>
       <c r="K189" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="190" spans="2:11" x14ac:dyDescent="0.2">
@@ -33701,16 +33714,16 @@
         <v>1650</v>
       </c>
       <c r="F190" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H190" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="I190" t="s">
         <v>884</v>
       </c>
       <c r="K190" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.2">
@@ -33725,16 +33738,16 @@
         <v>1650</v>
       </c>
       <c r="F191" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H191" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="I191" t="s">
         <v>884</v>
       </c>
       <c r="K191" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.2">
@@ -33749,16 +33762,16 @@
         <v>1650</v>
       </c>
       <c r="F192" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H192" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="I192" t="s">
         <v>884</v>
       </c>
       <c r="K192" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.2">
@@ -33773,16 +33786,16 @@
         <v>1650</v>
       </c>
       <c r="F193" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H193" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="I193" t="s">
         <v>884</v>
       </c>
       <c r="K193" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.2">
@@ -33797,16 +33810,16 @@
         <v>1650</v>
       </c>
       <c r="F194" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H194" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="I194" t="s">
         <v>884</v>
       </c>
       <c r="K194" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.2">
@@ -33821,16 +33834,16 @@
         <v>1650</v>
       </c>
       <c r="F195" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H195" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="I195" t="s">
         <v>884</v>
       </c>
       <c r="K195" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.2">
@@ -33845,16 +33858,16 @@
         <v>1650</v>
       </c>
       <c r="F196" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H196" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="I196" t="s">
         <v>884</v>
       </c>
       <c r="K196" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.2">
@@ -33869,16 +33882,16 @@
         <v>1650</v>
       </c>
       <c r="F197" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H197" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="I197" t="s">
         <v>884</v>
       </c>
       <c r="K197" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="198" spans="2:11" x14ac:dyDescent="0.2">
@@ -33893,16 +33906,16 @@
         <v>1650</v>
       </c>
       <c r="F198" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H198" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="I198" t="s">
         <v>884</v>
       </c>
       <c r="K198" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="199" spans="2:11" x14ac:dyDescent="0.2">
@@ -33917,16 +33930,16 @@
         <v>1650</v>
       </c>
       <c r="F199" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H199" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="I199" t="s">
         <v>884</v>
       </c>
       <c r="K199" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.2">
@@ -33941,16 +33954,16 @@
         <v>1650</v>
       </c>
       <c r="F200" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H200" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="I200" t="s">
         <v>884</v>
       </c>
       <c r="K200" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.2">
@@ -33965,16 +33978,16 @@
         <v>1650</v>
       </c>
       <c r="F201" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H201" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="I201" t="s">
         <v>884</v>
       </c>
       <c r="K201" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="202" spans="2:11" x14ac:dyDescent="0.2">
@@ -33989,16 +34002,16 @@
         <v>1650</v>
       </c>
       <c r="F202" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="H202" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="I202" t="s">
         <v>884</v>
       </c>
       <c r="K202" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
   </sheetData>
@@ -38253,8 +38266,8 @@
         <v>1998</v>
       </c>
       <c r="R42" s="8"/>
-      <c r="S42" s="76" t="s">
-        <v>2000</v>
+      <c r="S42" s="77" t="s">
+        <v>2117</v>
       </c>
       <c r="T42" t="s">
         <v>1421</v>
@@ -41735,7 +41748,7 @@
         <v>1167</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="M17" s="15" t="s">
         <v>1991</v>
@@ -42216,7 +42229,7 @@
         <v>1858</v>
       </c>
       <c r="N1" s="17" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -42468,16 +42481,16 @@
         <v>1630</v>
       </c>
       <c r="K9" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="L9" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="M9" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="N9" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -42498,16 +42511,16 @@
         <v>1630</v>
       </c>
       <c r="K10" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="L10" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="M10" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="N10" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
   </sheetData>
@@ -42741,7 +42754,7 @@
         <v>1145</v>
       </c>
       <c r="J5" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>1377</v>
@@ -43678,7 +43691,7 @@
         <v>148</v>
       </c>
       <c r="G32" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
       <c r="H32" t="s">
         <v>1096</v>
@@ -43725,7 +43738,7 @@
         <v>1398</v>
       </c>
       <c r="J34" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -44118,7 +44131,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E39206-1F1B-2D4B-82A5-94676E67F7A4}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -44188,56 +44201,31 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="85" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
-      <c r="B2" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" t="str">
-        <f>IF(G2&lt;&gt;"",VLOOKUP(G2,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>117</v>
-      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="15"/>
-      <c r="I2" s="15" t="s">
-        <v>1096</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>1145</v>
-      </c>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
       <c r="K2" s="15"/>
-      <c r="L2" s="69" t="s">
-        <v>2005</v>
-      </c>
+      <c r="L2" s="15"/>
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
-      <c r="O2" s="18" t="s">
-        <v>1377</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>1721</v>
-      </c>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="15">
-        <v>261</v>
-      </c>
+      <c r="A3" s="15"/>
       <c r="B3" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C3" s="15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>108</v>
@@ -44250,28 +44238,24 @@
         <v>1650</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1681</v>
+        <v>117</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1145</v>
+        <v>2112</v>
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
-      <c r="O3" s="18" t="s">
-        <v>1381</v>
-      </c>
+      <c r="O3" s="15"/>
       <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="15">
-        <v>267</v>
-      </c>
+      <c r="A4" s="15"/>
       <c r="B4" s="15" t="b">
         <v>1</v>
       </c>
@@ -44289,87 +44273,97 @@
         <v>1650</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>148</v>
+        <v>1681</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>1334</v>
+        <v>2113</v>
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
-      <c r="O4" s="18" t="s">
-        <v>1179</v>
-      </c>
-      <c r="P4" s="15" t="s">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="15">
-        <v>325</v>
-      </c>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+    </row>
+    <row r="5" spans="1:18" ht="85" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
       <c r="B5" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C5" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" t="str">
-        <f>IF(G5&lt;&gt;"",VLOOKUP(G5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
+      <c r="D5" s="15"/>
       <c r="F5" s="15" t="s">
         <v>1650</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>1013</v>
-      </c>
+      <c r="G5" s="15"/>
       <c r="H5" s="15"/>
       <c r="I5" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>1398</v>
+        <v>1145</v>
       </c>
       <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
+      <c r="L5" s="69" t="s">
+        <v>2114</v>
+      </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="15"/>
+      <c r="O5" s="18" t="s">
+        <v>1377</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>1721</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
+      <c r="A6" s="15">
+        <v>261</v>
+      </c>
+      <c r="B6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="E6" t="str">
         <f>IF(G6&lt;&gt;"",VLOOKUP(G6,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>1681</v>
+      </c>
       <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
+      <c r="I6" s="15" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>1145</v>
+      </c>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="25"/>
+      <c r="O6" s="18" t="s">
+        <v>1381</v>
+      </c>
+      <c r="P6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
-        <v>629</v>
+        <v>267</v>
       </c>
       <c r="B7" s="15" t="b">
         <v>1</v>
@@ -44388,29 +44382,29 @@
         <v>1650</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="H7" s="15"/>
       <c r="I7" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>1148</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>1149</v>
-      </c>
+        <v>1334</v>
+      </c>
+      <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
       <c r="O7" s="18" t="s">
-        <v>1651</v>
-      </c>
-      <c r="P7" s="15"/>
+        <v>1179</v>
+      </c>
+      <c r="P7" s="15" t="s">
+        <v>1575</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
-        <v>631</v>
+        <v>325</v>
       </c>
       <c r="B8" s="15" t="b">
         <v>1</v>
@@ -44429,74 +44423,46 @@
         <v>1650</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>144</v>
+        <v>1013</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>1156</v>
+        <v>1398</v>
       </c>
       <c r="K8" s="15"/>
-      <c r="L8" s="15" t="s">
-        <v>1712</v>
-      </c>
+      <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
-      <c r="O8" s="18" t="s">
-        <v>1534</v>
-      </c>
-      <c r="P8" s="23" t="s">
-        <v>1711</v>
-      </c>
+      <c r="O8" s="23"/>
+      <c r="P8" s="15"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="15">
-        <v>632</v>
-      </c>
-      <c r="B9" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>108</v>
-      </c>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
       <c r="E9" t="str">
         <f>IF(G9&lt;&gt;"",VLOOKUP(G9,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>1009</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="15" t="s">
-        <v>1096</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>1157</v>
-      </c>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="15" t="s">
-        <v>1659</v>
-      </c>
+      <c r="L9" s="15"/>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
-      <c r="O9" s="18" t="s">
-        <v>1158</v>
-      </c>
-      <c r="P9" s="23" t="s">
-        <v>1581</v>
-      </c>
+      <c r="O9" s="18"/>
+      <c r="P9" s="25"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B10" s="15" t="b">
         <v>1</v>
@@ -44515,48 +44481,72 @@
         <v>1650</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>1010</v>
+        <v>127</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>1580</v>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15" t="s">
-        <v>1712</v>
-      </c>
+        <v>1148</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>1149</v>
+      </c>
+      <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="23"/>
+      <c r="O10" s="18" t="s">
+        <v>1651</v>
+      </c>
+      <c r="P10" s="15"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
+      <c r="A11" s="15">
+        <v>631</v>
+      </c>
+      <c r="B11" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="E11" t="str">
         <f>IF(G11&lt;&gt;"",VLOOKUP(G11,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>144</v>
+      </c>
       <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
+      <c r="I11" s="15" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>1156</v>
+      </c>
       <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
+      <c r="L11" s="15" t="s">
+        <v>1712</v>
+      </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="23"/>
+      <c r="O11" s="18" t="s">
+        <v>1534</v>
+      </c>
+      <c r="P11" s="23" t="s">
+        <v>1711</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="B12" s="15" t="b">
         <v>1</v>
@@ -44575,33 +44565,31 @@
         <v>1650</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>176</v>
-      </c>
+        <v>1009</v>
+      </c>
+      <c r="H12" s="15"/>
       <c r="I12" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>1533</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>1461</v>
-      </c>
-      <c r="L12" s="15"/>
+        <v>1157</v>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15" t="s">
+        <v>1659</v>
+      </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="18" t="s">
-        <v>1465</v>
-      </c>
-      <c r="P12" s="25" t="s">
-        <v>1569</v>
+        <v>1158</v>
+      </c>
+      <c r="P12" s="23" t="s">
+        <v>1581</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="B13" s="15" t="b">
         <v>1</v>
@@ -44620,78 +44608,48 @@
         <v>1650</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>177</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="H13" s="15"/>
       <c r="I13" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>1533</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>1462</v>
-      </c>
-      <c r="L13" s="15"/>
+        <v>1580</v>
+      </c>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15" t="s">
+        <v>1712</v>
+      </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
-      <c r="O13" s="18" t="s">
-        <v>1465</v>
-      </c>
-      <c r="P13" s="25" t="s">
-        <v>1569</v>
-      </c>
+      <c r="O13" s="18"/>
+      <c r="P13" s="23"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="15">
-        <v>645</v>
-      </c>
-      <c r="B14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>108</v>
-      </c>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
       <c r="E14" t="str">
         <f>IF(G14&lt;&gt;"",VLOOKUP(G14,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>1096</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>1533</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>1463</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
-      <c r="O14" s="18" t="s">
-        <v>1465</v>
-      </c>
-      <c r="P14" s="25" t="s">
-        <v>1569</v>
-      </c>
+      <c r="O14" s="18"/>
+      <c r="P14" s="23"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B15" s="15" t="b">
         <v>1</v>
@@ -44713,7 +44671,7 @@
         <v>123</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>1096</v>
@@ -44722,7 +44680,7 @@
         <v>1533</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
@@ -44734,30 +44692,54 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17" t="str">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A16" s="15">
+        <v>644</v>
+      </c>
+      <c r="B16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" t="str">
         <f>IF(G16&lt;&gt;"",VLOOKUP(G16,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="24"/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>1533</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>1462</v>
+      </c>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="P16" s="25" t="s">
+        <v>1569</v>
+      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B17" s="15" t="b">
         <v>1</v>
@@ -44776,155 +44758,266 @@
         <v>1650</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="H17" s="15"/>
+        <v>123</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>178</v>
+      </c>
       <c r="I17" s="15" t="s">
         <v>1096</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>1203</v>
+        <v>1533</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>1204</v>
+        <v>1463</v>
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="15"/>
-    </row>
-    <row r="18" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17" t="str">
+      <c r="O17" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="P17" s="25" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" s="15">
+        <v>646</v>
+      </c>
+      <c r="B18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" t="str">
         <f>IF(G18&lt;&gt;"",VLOOKUP(G18,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="16"/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>1533</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>1464</v>
+      </c>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="18" t="s">
+        <v>1465</v>
+      </c>
+      <c r="P18" s="25" t="s">
+        <v>1569</v>
+      </c>
     </row>
     <row r="19" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="16">
-        <v>677</v>
-      </c>
+      <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
-      <c r="D19" s="16" t="s">
-        <v>108</v>
-      </c>
+      <c r="D19" s="16"/>
       <c r="E19" s="17" t="str">
         <f>IF(G19&lt;&gt;"",VLOOKUP(G19,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>1054</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>1096</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>1097</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>1526</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
-      <c r="O19" s="22" t="s">
-        <v>1528</v>
-      </c>
-      <c r="P19" s="24" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16">
-        <v>678</v>
-      </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16" t="s">
+      <c r="O19" s="22"/>
+      <c r="P19" s="24"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="15">
+        <v>649</v>
+      </c>
+      <c r="B20" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E20" s="17" t="str">
+      <c r="E20" t="str">
         <f>IF(G20&lt;&gt;"",VLOOKUP(G20,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="F20" s="16" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I20" s="16" t="s">
+      <c r="F20" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15" t="s">
         <v>1096</v>
       </c>
-      <c r="J20" s="16" t="s">
-        <v>1097</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>1527</v>
-      </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="22" t="s">
-        <v>1529</v>
-      </c>
-      <c r="P20" s="24" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="119" x14ac:dyDescent="0.2">
-      <c r="B22" t="b">
-        <v>1</v>
-      </c>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="s">
+      <c r="J20" s="15" t="s">
+        <v>1203</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="15"/>
+    </row>
+    <row r="21" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17" t="str">
+        <f>IF(G21&lt;&gt;"",VLOOKUP(G21,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="16"/>
+    </row>
+    <row r="22" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="16">
+        <v>677</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E22" s="17" t="str">
         <f>IF(G22&lt;&gt;"",VLOOKUP(G22,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v>Sample collection and processing</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G22" s="15" t="s">
+      <c r="F22" s="16" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G22" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="H22" s="16" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I22" s="16" t="s">
         <v>1096</v>
       </c>
-      <c r="J22" s="15" t="s">
-        <v>2016</v>
-      </c>
-      <c r="L22" s="28" t="s">
-        <v>2017</v>
+      <c r="J22" s="16" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>1526</v>
+      </c>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="22" t="s">
+        <v>1528</v>
+      </c>
+      <c r="P22" s="24" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="16">
+        <v>678</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="17" t="str">
+        <f>IF(G23&lt;&gt;"",VLOOKUP(G23,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>1527</v>
+      </c>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="22" t="s">
+        <v>1529</v>
+      </c>
+      <c r="P23" s="24" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="119" x14ac:dyDescent="0.2">
+      <c r="B25" t="b">
+        <v>1</v>
+      </c>
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" t="str">
+        <f>IF(G25&lt;&gt;"",VLOOKUP(G25,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>2014</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>2015</v>
       </c>
     </row>
   </sheetData>
@@ -55975,19 +56068,19 @@
         <v>1623</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="S1" s="16" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="T1" s="16" t="s">
         <v>9</v>
@@ -56026,7 +56119,7 @@
         <v>1521</v>
       </c>
       <c r="Q2" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T2" t="s">
         <v>1524</v>
@@ -56050,7 +56143,7 @@
         <v>1096</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>127</v>
@@ -56072,7 +56165,7 @@
         <v>1098</v>
       </c>
       <c r="Q3" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T3" s="28"/>
     </row>
@@ -56112,7 +56205,7 @@
         <v>1520</v>
       </c>
       <c r="Q4" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T4" t="s">
         <v>1523</v>
@@ -56148,7 +56241,7 @@
         <v>1495</v>
       </c>
       <c r="Q5" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T5" s="18" t="s">
         <v>1498</v>
@@ -56195,7 +56288,7 @@
         <v>1496</v>
       </c>
       <c r="Q6" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T6" s="18" t="s">
         <v>1498</v>
@@ -56234,7 +56327,7 @@
         <v>1503</v>
       </c>
       <c r="Q7" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T7" s="18" t="s">
         <v>1504</v>
@@ -56261,7 +56354,7 @@
         <v>1096</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="H8" s="28" t="s">
         <v>127</v>
@@ -56282,7 +56375,7 @@
         <v>1522</v>
       </c>
       <c r="Q8" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
@@ -56311,22 +56404,22 @@
         <v>1910</v>
       </c>
       <c r="J10" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="L10" s="28" t="s">
+        <v>2019</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>2019</v>
+      </c>
+      <c r="P10" t="s">
+        <v>2018</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>2024</v>
+      </c>
+      <c r="R10" t="s">
         <v>2021</v>
-      </c>
-      <c r="O10" s="28" t="s">
-        <v>2021</v>
-      </c>
-      <c r="P10" t="s">
-        <v>2020</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>2026</v>
-      </c>
-      <c r="R10" t="s">
-        <v>2023</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
@@ -56352,22 +56445,22 @@
         <v>1910</v>
       </c>
       <c r="J11" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="L11" s="28" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="O11" s="28" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="P11" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="Q11" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="R11" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
@@ -57992,7 +58085,7 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{098C5693-7744-414E-A1CB-7D8D34C0B793}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -58121,7 +58214,7 @@
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
     </row>
-    <row r="4" spans="1:16" ht="170" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
         <v>287</v>
       </c>
@@ -58149,62 +58242,46 @@
         <v>1101</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>1151</v>
+        <v>2115</v>
       </c>
       <c r="K4" s="15"/>
-      <c r="L4" s="69" t="s">
-        <v>2113</v>
-      </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="15">
-        <v>287</v>
-      </c>
+    <row r="5" spans="1:16" ht="187" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
       <c r="B5" s="15" t="b">
         <v>1</v>
       </c>
       <c r="C5" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" t="str">
-        <f>IF(G5&lt;&gt;"",VLOOKUP(G5,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D5" s="15"/>
       <c r="F5" s="15" t="s">
         <v>1650</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>1680</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>207</v>
-      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
       <c r="I5" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J5" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="K5" s="15" t="s">
-        <v>1587</v>
+      <c r="K5" s="15"/>
+      <c r="L5" s="69" t="s">
+        <v>2116</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
-      <c r="P5" s="15" t="s">
-        <v>1658</v>
-      </c>
+      <c r="P5" s="15"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B6" s="15" t="b">
         <v>1</v>
@@ -58226,18 +58303,17 @@
         <v>1680</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>1588</v>
-      </c>
-      <c r="L6" s="15"/>
+        <v>1587</v>
+      </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
@@ -58247,7 +58323,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B7" s="15" t="b">
         <v>1</v>
@@ -58269,16 +58345,16 @@
         <v>1680</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
@@ -58290,7 +58366,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B8" s="15" t="b">
         <v>1</v>
@@ -58312,16 +58388,16 @@
         <v>1680</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
@@ -58333,7 +58409,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B9" s="15" t="b">
         <v>1</v>
@@ -58355,16 +58431,16 @@
         <v>1680</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
@@ -58376,7 +58452,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B10" s="15" t="b">
         <v>1</v>
@@ -58398,16 +58474,16 @@
         <v>1680</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
@@ -58419,7 +58495,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B11" s="15" t="b">
         <v>1</v>
@@ -58441,16 +58517,16 @@
         <v>1680</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
@@ -58462,7 +58538,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B12" s="15" t="b">
         <v>1</v>
@@ -58484,16 +58560,16 @@
         <v>1680</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
@@ -58505,7 +58581,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B13" s="15" t="b">
         <v>1</v>
@@ -58527,16 +58603,16 @@
         <v>1680</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
@@ -58548,7 +58624,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B14" s="15" t="b">
         <v>1</v>
@@ -58570,16 +58646,16 @@
         <v>1680</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
@@ -58591,7 +58667,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B15" s="15" t="b">
         <v>1</v>
@@ -58613,16 +58689,16 @@
         <v>1680</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
@@ -58634,7 +58710,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="15">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B16" s="15" t="b">
         <v>1</v>
@@ -58656,16 +58732,16 @@
         <v>1680</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
@@ -58677,7 +58753,7 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B17" s="15" t="b">
         <v>1</v>
@@ -58699,16 +58775,16 @@
         <v>1680</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
@@ -58720,7 +58796,7 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B18" s="15" t="b">
         <v>1</v>
@@ -58742,16 +58818,16 @@
         <v>1680</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
@@ -58763,7 +58839,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B19" s="15" t="b">
         <v>1</v>
@@ -58785,16 +58861,16 @@
         <v>1680</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
@@ -58806,7 +58882,7 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B20" s="15" t="b">
         <v>1</v>
@@ -58828,16 +58904,16 @@
         <v>1680</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
@@ -58849,7 +58925,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B21" s="15" t="b">
         <v>1</v>
@@ -58871,16 +58947,16 @@
         <v>1680</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="L21" s="15"/>
       <c r="M21" s="15"/>
@@ -58892,7 +58968,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B22" s="15" t="b">
         <v>1</v>
@@ -58914,16 +58990,16 @@
         <v>1680</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J22" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
@@ -58935,7 +59011,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="15">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B23" s="15" t="b">
         <v>1</v>
@@ -58957,16 +59033,16 @@
         <v>1680</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="L23" s="15"/>
       <c r="M23" s="15"/>
@@ -58978,7 +59054,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B24" s="15" t="b">
         <v>1</v>
@@ -59000,16 +59076,16 @@
         <v>1680</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
@@ -59021,7 +59097,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="15">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B25" s="15" t="b">
         <v>1</v>
@@ -59043,16 +59119,16 @@
         <v>1680</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
@@ -59064,7 +59140,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B26" s="15" t="b">
         <v>1</v>
@@ -59086,16 +59162,16 @@
         <v>1680</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
@@ -59107,7 +59183,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B27" s="15" t="b">
         <v>1</v>
@@ -59129,16 +59205,16 @@
         <v>1680</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J27" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="L27" s="15"/>
       <c r="M27" s="15"/>
@@ -59150,7 +59226,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B28" s="15" t="b">
         <v>1</v>
@@ -59172,16 +59248,16 @@
         <v>1680</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J28" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
@@ -59193,7 +59269,7 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B29" s="15" t="b">
         <v>1</v>
@@ -59215,16 +59291,16 @@
         <v>1680</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
@@ -59236,7 +59312,7 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B30" s="15" t="b">
         <v>1</v>
@@ -59258,16 +59334,16 @@
         <v>1680</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
@@ -59279,7 +59355,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="15">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B31" s="15" t="b">
         <v>1</v>
@@ -59301,16 +59377,16 @@
         <v>1680</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
@@ -59322,7 +59398,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="15">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B32" s="15" t="b">
         <v>1</v>
@@ -59344,16 +59420,16 @@
         <v>1680</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J32" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="L32" s="15"/>
       <c r="M32" s="15"/>
@@ -59365,7 +59441,7 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B33" s="15" t="b">
         <v>1</v>
@@ -59387,16 +59463,16 @@
         <v>1680</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="15"/>
@@ -59408,7 +59484,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B34" s="15" t="b">
         <v>1</v>
@@ -59430,16 +59506,16 @@
         <v>1680</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J34" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="L34" s="15"/>
       <c r="M34" s="15"/>
@@ -59451,7 +59527,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B35" s="15" t="b">
         <v>1</v>
@@ -59473,16 +59549,16 @@
         <v>1680</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>1881</v>
+        <v>236</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="L35" s="15"/>
       <c r="M35" s="15"/>
@@ -59494,7 +59570,7 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B36" s="15" t="b">
         <v>1</v>
@@ -59516,16 +59592,16 @@
         <v>1680</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>1057</v>
+        <v>1881</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="L36" s="15"/>
       <c r="M36" s="15"/>
@@ -59537,7 +59613,7 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B37" s="15" t="b">
         <v>1</v>
@@ -59559,16 +59635,16 @@
         <v>1680</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>237</v>
+        <v>1057</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
@@ -59580,7 +59656,7 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B38" s="15" t="b">
         <v>1</v>
@@ -59602,16 +59678,16 @@
         <v>1680</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J38" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="L38" s="15"/>
       <c r="M38" s="15"/>
@@ -59623,7 +59699,7 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" s="15">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B39" s="15" t="b">
         <v>1</v>
@@ -59645,16 +59721,16 @@
         <v>1680</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="L39" s="15"/>
       <c r="M39" s="15"/>
@@ -59666,7 +59742,7 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" s="15">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B40" s="15" t="b">
         <v>1</v>
@@ -59688,16 +59764,16 @@
         <v>1680</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
@@ -59708,6 +59784,9 @@
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" s="15">
+        <v>322</v>
+      </c>
       <c r="B41" s="15" t="b">
         <v>1</v>
       </c>
@@ -59727,20 +59806,24 @@
       <c r="G41" s="15" t="s">
         <v>1680</v>
       </c>
-      <c r="H41" t="s">
-        <v>1759</v>
+      <c r="H41" s="15" t="s">
+        <v>240</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>1151</v>
-      </c>
-      <c r="K41" t="s">
-        <v>1773</v>
-      </c>
+        <v>2111</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>1622</v>
+      </c>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
       <c r="P41" s="15" t="s">
-        <v>1755</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
@@ -59764,16 +59847,16 @@
         <v>1680</v>
       </c>
       <c r="H42" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K42" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="P42" s="15" t="s">
         <v>1755</v>
@@ -59800,16 +59883,16 @@
         <v>1680</v>
       </c>
       <c r="H43" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K43" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="P43" s="15" t="s">
         <v>1755</v>
@@ -59836,16 +59919,16 @@
         <v>1680</v>
       </c>
       <c r="H44" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K44" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="P44" s="15" t="s">
         <v>1755</v>
@@ -59872,16 +59955,16 @@
         <v>1680</v>
       </c>
       <c r="H45" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K45" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="P45" s="15" t="s">
         <v>1755</v>
@@ -59908,16 +59991,16 @@
         <v>1680</v>
       </c>
       <c r="H46" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K46" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="P46" s="15" t="s">
         <v>1755</v>
@@ -59944,16 +60027,16 @@
         <v>1680</v>
       </c>
       <c r="H47" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K47" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="P47" s="15" t="s">
         <v>1755</v>
@@ -59980,16 +60063,16 @@
         <v>1680</v>
       </c>
       <c r="H48" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K48" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="P48" s="15" t="s">
         <v>1755</v>
@@ -60016,16 +60099,16 @@
         <v>1680</v>
       </c>
       <c r="H49" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K49" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="P49" s="15" t="s">
         <v>1755</v>
@@ -60052,16 +60135,16 @@
         <v>1680</v>
       </c>
       <c r="H50" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K50" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="P50" s="15" t="s">
         <v>1755</v>
@@ -60088,16 +60171,16 @@
         <v>1680</v>
       </c>
       <c r="H51" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K51" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="P51" s="15" t="s">
         <v>1755</v>
@@ -60124,16 +60207,16 @@
         <v>1680</v>
       </c>
       <c r="H52" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K52" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="P52" s="15" t="s">
         <v>1755</v>
@@ -60160,16 +60243,16 @@
         <v>1680</v>
       </c>
       <c r="H53" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K53" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="P53" s="15" t="s">
         <v>1755</v>
@@ -60196,123 +60279,118 @@
         <v>1680</v>
       </c>
       <c r="H54" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>1101</v>
       </c>
       <c r="J54" s="15" t="s">
-        <v>1151</v>
+        <v>2111</v>
       </c>
       <c r="K54" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="P54" s="15" t="s">
         <v>1755</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
+      <c r="B55" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C55" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="E55" t="str">
         <f>IF(G55&lt;&gt;"",VLOOKUP(G55,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G55" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1772</v>
+      </c>
+      <c r="I55" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>2111</v>
+      </c>
+      <c r="K55" t="s">
+        <v>1786</v>
+      </c>
+      <c r="P55" s="15" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" t="str">
+        <f>IF(G56&lt;&gt;"",VLOOKUP(G56,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-      <c r="K55" s="15"/>
-      <c r="L55" s="15"/>
-      <c r="M55" s="15"/>
-      <c r="N55" s="15"/>
-      <c r="O55" s="15"/>
-      <c r="P55" s="15"/>
-    </row>
-    <row r="56" spans="1:16" ht="136" x14ac:dyDescent="0.2">
-      <c r="A56" s="15"/>
-      <c r="B56" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C56" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" s="15"/>
-      <c r="F56" s="15" t="s">
-        <v>1650</v>
-      </c>
+      <c r="F56" s="15"/>
       <c r="G56" s="15"/>
       <c r="H56" s="15"/>
-      <c r="I56" s="15" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J56" s="15" t="s">
-        <v>1152</v>
-      </c>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="69" t="s">
-        <v>2111</v>
-      </c>
+      <c r="L56" s="15"/>
       <c r="M56" s="15"/>
       <c r="N56" s="15"/>
       <c r="O56" s="15"/>
       <c r="P56" s="15"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
+      <c r="B57" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C57" s="15" t="b">
+        <v>0</v>
+      </c>
       <c r="D57" s="15"/>
-      <c r="F57" s="15"/>
+      <c r="F57" s="15" t="s">
+        <v>1650</v>
+      </c>
       <c r="G57" s="15"/>
       <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
+      <c r="I57" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J57" s="15" t="s">
+        <v>1152</v>
+      </c>
       <c r="K57" s="15"/>
-      <c r="L57" s="15"/>
+      <c r="L57" s="69" t="s">
+        <v>2109</v>
+      </c>
       <c r="M57" s="15"/>
       <c r="N57" s="15"/>
       <c r="O57" s="15"/>
       <c r="P57" s="15"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A58" s="15">
-        <v>333</v>
-      </c>
-      <c r="B58" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C58" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E58" t="str">
-        <f>IF(G58&lt;&gt;"",VLOOKUP(G58,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G58" s="15" t="s">
-        <v>1004</v>
-      </c>
-      <c r="H58" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J58" s="15" t="s">
-        <v>1190</v>
-      </c>
-      <c r="K58" s="15" t="s">
-        <v>1192</v>
-      </c>
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
       <c r="L58" s="15"/>
       <c r="M58" s="15"/>
       <c r="N58" s="15"/>
@@ -60321,7 +60399,7 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" s="15">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B59" s="15" t="b">
         <v>1</v>
@@ -60340,7 +60418,7 @@
         <v>1650</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H59" s="15" t="s">
         <v>368</v>
@@ -60349,10 +60427,10 @@
         <v>1101</v>
       </c>
       <c r="J59" s="15" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="L59" s="15"/>
       <c r="M59" s="15"/>
@@ -60362,7 +60440,7 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" s="15">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B60" s="15" t="b">
         <v>1</v>
@@ -60381,7 +60459,7 @@
         <v>1650</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>1675</v>
+        <v>1005</v>
       </c>
       <c r="H60" s="15" t="s">
         <v>368</v>
@@ -60390,10 +60468,10 @@
         <v>1101</v>
       </c>
       <c r="J60" s="15" t="s">
-        <v>1071</v>
+        <v>1191</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>1120</v>
+        <v>1193</v>
       </c>
       <c r="L60" s="15"/>
       <c r="M60" s="15"/>
@@ -60402,74 +60480,70 @@
       <c r="P60" s="15"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" s="15"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
+      <c r="A61" s="15">
+        <v>336</v>
+      </c>
+      <c r="B61" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C61" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="E61" t="str">
         <f>IF(G61&lt;&gt;"",VLOOKUP(G61,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="15"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J61" s="15" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K61" s="15" t="s">
+        <v>1120</v>
+      </c>
       <c r="L61" s="15"/>
       <c r="M61" s="15"/>
       <c r="N61" s="15"/>
       <c r="O61" s="15"/>
       <c r="P61" s="15"/>
     </row>
-    <row r="62" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="16">
-        <v>680</v>
-      </c>
-      <c r="B62" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C62" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E62" s="17" t="str">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" t="str">
         <f>IF(G62&lt;&gt;"",VLOOKUP(G62,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
-        <v>Sample collection and processing</v>
-      </c>
-      <c r="F62" s="16" t="s">
-        <v>1650</v>
-      </c>
-      <c r="G62" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="H62" s="16" t="s">
-        <v>1423</v>
-      </c>
-      <c r="I62" s="16" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J62" s="16" t="s">
-        <v>1152</v>
-      </c>
-      <c r="K62" s="16" t="s">
-        <v>1153</v>
-      </c>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="16"/>
-      <c r="O62" s="22" t="s">
-        <v>1433</v>
-      </c>
-      <c r="P62" s="16" t="s">
-        <v>1583</v>
-      </c>
+        <v/>
+      </c>
+      <c r="F62" s="15"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="15"/>
     </row>
     <row r="63" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B63" s="15" t="b">
         <v>1</v>
@@ -60491,7 +60565,7 @@
         <v>143</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="I63" s="16" t="s">
         <v>1101</v>
@@ -60500,7 +60574,7 @@
         <v>1152</v>
       </c>
       <c r="K63" s="16" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
@@ -60514,7 +60588,7 @@
     </row>
     <row r="64" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B64" s="15" t="b">
         <v>1</v>
@@ -60536,7 +60610,7 @@
         <v>143</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>1882</v>
+        <v>1424</v>
       </c>
       <c r="I64" s="16" t="s">
         <v>1101</v>
@@ -60545,7 +60619,7 @@
         <v>1152</v>
       </c>
       <c r="K64" s="16" t="s">
-        <v>1429</v>
+        <v>1154</v>
       </c>
       <c r="L64" s="16"/>
       <c r="M64" s="16"/>
@@ -60559,7 +60633,7 @@
     </row>
     <row r="65" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B65" s="15" t="b">
         <v>1</v>
@@ -60581,7 +60655,7 @@
         <v>143</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>1056</v>
+        <v>1882</v>
       </c>
       <c r="I65" s="16" t="s">
         <v>1101</v>
@@ -60590,7 +60664,7 @@
         <v>1152</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>1150</v>
+        <v>1429</v>
       </c>
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
@@ -60604,7 +60678,7 @@
     </row>
     <row r="66" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B66" s="15" t="b">
         <v>1</v>
@@ -60626,7 +60700,7 @@
         <v>143</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>1425</v>
+        <v>1056</v>
       </c>
       <c r="I66" s="16" t="s">
         <v>1101</v>
@@ -60635,7 +60709,7 @@
         <v>1152</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>1430</v>
+        <v>1150</v>
       </c>
       <c r="L66" s="16"/>
       <c r="M66" s="16"/>
@@ -60649,7 +60723,7 @@
     </row>
     <row r="67" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="16">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B67" s="15" t="b">
         <v>1</v>
@@ -60671,7 +60745,7 @@
         <v>143</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="I67" s="16" t="s">
         <v>1101</v>
@@ -60680,7 +60754,7 @@
         <v>1152</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>1155</v>
+        <v>1430</v>
       </c>
       <c r="L67" s="16"/>
       <c r="M67" s="16"/>
@@ -60694,7 +60768,7 @@
     </row>
     <row r="68" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="16">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B68" s="15" t="b">
         <v>1</v>
@@ -60716,7 +60790,7 @@
         <v>143</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="I68" s="16" t="s">
         <v>1101</v>
@@ -60725,7 +60799,7 @@
         <v>1152</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>1431</v>
+        <v>1155</v>
       </c>
       <c r="L68" s="16"/>
       <c r="M68" s="16"/>
@@ -60739,7 +60813,7 @@
     </row>
     <row r="69" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="16">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B69" s="15" t="b">
         <v>1</v>
@@ -60761,7 +60835,7 @@
         <v>143</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="I69" s="16" t="s">
         <v>1101</v>
@@ -60770,7 +60844,7 @@
         <v>1152</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
@@ -60782,24 +60856,49 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B71" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C71" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="I71" s="15" t="s">
+    <row r="70" spans="1:16" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="16">
+        <v>687</v>
+      </c>
+      <c r="B70" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C70" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="17" t="str">
+        <f>IF(G70&lt;&gt;"",VLOOKUP(G70,PHA4GEVars!$A$7:$B$241,2,FALSE),"")</f>
+        <v>Sample collection and processing</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>1650</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>1428</v>
+      </c>
+      <c r="I70" s="16" t="s">
         <v>1101</v>
       </c>
-      <c r="J71" s="15" t="s">
-        <v>1863</v>
-      </c>
-      <c r="L71" t="s">
-        <v>1911</v>
+      <c r="J70" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>1432</v>
+      </c>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+      <c r="N70" s="16"/>
+      <c r="O70" s="22" t="s">
+        <v>1433</v>
+      </c>
+      <c r="P70" s="16" t="s">
+        <v>1583</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
@@ -60816,9 +60915,29 @@
         <v>1101</v>
       </c>
       <c r="J72" s="15" t="s">
+        <v>1863</v>
+      </c>
+      <c r="L72" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B73" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C73" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="I73" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J73" s="15" t="s">
         <v>1866</v>
       </c>
-      <c r="L72" t="s">
+      <c r="L73" t="s">
         <v>1911</v>
       </c>
     </row>
@@ -67600,10 +67719,10 @@
         <v>1854</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>1860</v>
@@ -67802,7 +67921,7 @@
       </c>
       <c r="L2" s="15"/>
       <c r="M2" s="15" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
@@ -67840,7 +67959,7 @@
       </c>
       <c r="L3" s="15"/>
       <c r="M3" s="15" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="N3" s="15"/>
       <c r="O3" s="18" t="s">
@@ -67880,7 +67999,7 @@
       </c>
       <c r="L4" s="15"/>
       <c r="M4" s="15" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="N4" s="15"/>
       <c r="O4" s="18" t="s">
